--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="1128">
   <si>
     <t>Fornitore</t>
   </si>
@@ -3320,6 +3320,9 @@
   </si>
   <si>
     <t>Isolab9002</t>
+  </si>
+  <si>
+    <t>2.1</t>
   </si>
   <si>
     <t>KWEL</t>
@@ -3726,7 +3729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I546"/>
+  <dimension ref="A1:I547"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -16632,22 +16635,22 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D538" t="s">
         <v>1102</v>
       </c>
-      <c r="C538" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D538" t="s">
-        <v>1104</v>
-      </c>
       <c r="F538" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G538" t="s">
         <v>14</v>
       </c>
       <c r="H538">
-        <v>46035</v>
+        <v>46078</v>
       </c>
       <c r="I538" t="s">
         <v>12</v>
@@ -16655,22 +16658,22 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D539" t="s">
         <v>1105</v>
       </c>
-      <c r="C539" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D539" t="s">
-        <v>98</v>
-      </c>
       <c r="F539" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G539" t="s">
         <v>14</v>
       </c>
       <c r="H539">
-        <v>45985</v>
+        <v>46035</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16678,22 +16681,22 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C540" t="s">
         <v>1107</v>
       </c>
-      <c r="C540" t="s">
-        <v>1108</v>
-      </c>
       <c r="D540" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F540" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G540" t="s">
         <v>14</v>
       </c>
       <c r="H540">
-        <v>45190</v>
+        <v>45985</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16701,22 +16704,22 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C541" t="s">
         <v>1109</v>
       </c>
-      <c r="C541" t="s">
-        <v>1110</v>
-      </c>
       <c r="D541" t="s">
-        <v>1111</v>
+        <v>12</v>
       </c>
       <c r="F541" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
       </c>
       <c r="H541">
-        <v>45029</v>
+        <v>45190</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16724,25 +16727,22 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D542" t="s">
         <v>1112</v>
       </c>
-      <c r="C542" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D542" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1115</v>
-      </c>
       <c r="F542" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G542" t="s">
         <v>14</v>
       </c>
       <c r="H542">
-        <v>45376</v>
+        <v>45029</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16750,25 +16750,25 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E543" t="s">
         <v>1116</v>
       </c>
-      <c r="B543" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D543" t="s">
-        <v>1119</v>
-      </c>
       <c r="F543" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G543" t="s">
         <v>14</v>
       </c>
       <c r="H543">
-        <v>45085</v>
+        <v>45376</v>
       </c>
       <c r="I543" t="s">
         <v>12</v>
@@ -16776,16 +16776,16 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B544" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C544" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D544" t="s">
         <v>1120</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1121</v>
       </c>
       <c r="F544" t="s">
         <v>22</v>
@@ -16794,7 +16794,7 @@
         <v>14</v>
       </c>
       <c r="H544">
-        <v>45387</v>
+        <v>45085</v>
       </c>
       <c r="I544" t="s">
         <v>12</v>
@@ -16802,25 +16802,25 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B545" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C545" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D545" t="s">
         <v>1122</v>
       </c>
-      <c r="D545" t="s">
-        <v>1123</v>
-      </c>
       <c r="F545" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G545" t="s">
         <v>14</v>
       </c>
       <c r="H545">
-        <v>45764</v>
+        <v>45387</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -16828,24 +16828,50 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C546" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D546" t="s">
         <v>1124</v>
       </c>
-      <c r="C546" t="s">
+      <c r="F546" t="s">
+        <v>60</v>
+      </c>
+      <c r="G546" t="s">
+        <v>14</v>
+      </c>
+      <c r="H546">
+        <v>45764</v>
+      </c>
+      <c r="I546" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9">
+      <c r="A547" t="s">
         <v>1125</v>
       </c>
-      <c r="D546" t="s">
+      <c r="C547" t="s">
         <v>1126</v>
       </c>
-      <c r="F546" t="s">
+      <c r="D547" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F547" t="s">
         <v>18</v>
       </c>
-      <c r="G546" t="s">
-        <v>14</v>
-      </c>
-      <c r="H546">
+      <c r="G547" t="s">
+        <v>14</v>
+      </c>
+      <c r="H547">
         <v>45477</v>
       </c>
-      <c r="I546" t="s">
+      <c r="I547" t="s">
         <v>12</v>
       </c>
     </row>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1130">
   <si>
     <t>Fornitore</t>
   </si>
@@ -2957,6 +2957,12 @@
   </si>
   <si>
     <t>AUSYLIA</t>
+  </si>
+  <si>
+    <t>SDSINFORMATICA</t>
+  </si>
+  <si>
+    <t>RIABILITIODIAGNO</t>
   </si>
   <si>
     <t>SID SRL</t>
@@ -3729,7 +3735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I547"/>
+  <dimension ref="A1:I548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -15156,16 +15162,16 @@
         <v>982</v>
       </c>
       <c r="D475" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F475" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G475" t="s">
         <v>14</v>
       </c>
       <c r="H475">
-        <v>45061</v>
+        <v>46079</v>
       </c>
       <c r="I475" t="s">
         <v>12</v>
@@ -15173,22 +15179,22 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C476" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D476" t="s">
         <v>216</v>
       </c>
       <c r="F476" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G476" t="s">
         <v>14</v>
       </c>
       <c r="H476">
-        <v>45638</v>
+        <v>45061</v>
       </c>
       <c r="I476" t="s">
         <v>12</v>
@@ -15202,16 +15208,16 @@
         <v>984</v>
       </c>
       <c r="D477" t="s">
-        <v>985</v>
+        <v>216</v>
       </c>
       <c r="F477" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G477" t="s">
         <v>14</v>
       </c>
       <c r="H477">
-        <v>45016</v>
+        <v>45638</v>
       </c>
       <c r="I477" t="s">
         <v>12</v>
@@ -15219,25 +15225,22 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" t="s">
+        <v>985</v>
+      </c>
+      <c r="C478" t="s">
         <v>986</v>
       </c>
-      <c r="B478" t="s">
+      <c r="D478" t="s">
         <v>987</v>
       </c>
-      <c r="C478" t="s">
-        <v>988</v>
-      </c>
-      <c r="D478" t="s">
-        <v>989</v>
-      </c>
       <c r="F478" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G478" t="s">
         <v>14</v>
       </c>
       <c r="H478">
-        <v>45051</v>
+        <v>45016</v>
       </c>
       <c r="I478" t="s">
         <v>12</v>
@@ -15245,22 +15248,25 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479" t="s">
+        <v>988</v>
+      </c>
+      <c r="B479" t="s">
+        <v>989</v>
+      </c>
+      <c r="C479" t="s">
         <v>990</v>
       </c>
-      <c r="C479" t="s">
+      <c r="D479" t="s">
         <v>991</v>
       </c>
-      <c r="D479" t="s">
-        <v>98</v>
-      </c>
       <c r="F479" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G479" t="s">
         <v>14</v>
       </c>
       <c r="H479">
-        <v>45093</v>
+        <v>45051</v>
       </c>
       <c r="I479" t="s">
         <v>12</v>
@@ -15274,16 +15280,16 @@
         <v>993</v>
       </c>
       <c r="D480" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F480" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G480" t="s">
         <v>14</v>
       </c>
       <c r="H480">
-        <v>45376</v>
+        <v>45093</v>
       </c>
       <c r="I480" t="s">
         <v>12</v>
@@ -15291,22 +15297,22 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C481" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D481" t="s">
         <v>39</v>
       </c>
       <c r="F481" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G481" t="s">
         <v>14</v>
       </c>
       <c r="H481">
-        <v>45400</v>
+        <v>45376</v>
       </c>
       <c r="I481" t="s">
         <v>12</v>
@@ -15314,7 +15320,7 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C482" t="s">
         <v>996</v>
@@ -15323,13 +15329,13 @@
         <v>39</v>
       </c>
       <c r="F482" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="G482" t="s">
         <v>14</v>
       </c>
       <c r="H482">
-        <v>45133</v>
+        <v>45400</v>
       </c>
       <c r="I482" t="s">
         <v>12</v>
@@ -15337,22 +15343,22 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C483" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D483" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F483" t="s">
-        <v>361</v>
+        <v>123</v>
       </c>
       <c r="G483" t="s">
         <v>14</v>
       </c>
       <c r="H483">
-        <v>45443</v>
+        <v>45133</v>
       </c>
       <c r="I483" t="s">
         <v>12</v>
@@ -15360,22 +15366,22 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C484" t="s">
         <v>999</v>
       </c>
       <c r="D484" t="s">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="F484" t="s">
-        <v>138</v>
+        <v>361</v>
       </c>
       <c r="G484" t="s">
         <v>14</v>
       </c>
       <c r="H484">
-        <v>45126</v>
+        <v>45443</v>
       </c>
       <c r="I484" t="s">
         <v>12</v>
@@ -15383,22 +15389,22 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C485" t="s">
         <v>1001</v>
       </c>
-      <c r="C485" t="s">
+      <c r="D485" t="s">
         <v>1002</v>
       </c>
-      <c r="D485" t="s">
-        <v>12</v>
-      </c>
       <c r="F485" t="s">
-        <v>1003</v>
+        <v>138</v>
       </c>
       <c r="G485" t="s">
         <v>14</v>
       </c>
       <c r="H485">
-        <v>45317</v>
+        <v>45126</v>
       </c>
       <c r="I485" t="s">
         <v>12</v>
@@ -15406,22 +15412,22 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C486" t="s">
         <v>1004</v>
       </c>
-      <c r="C486" t="s">
+      <c r="D486" t="s">
+        <v>12</v>
+      </c>
+      <c r="F486" t="s">
         <v>1005</v>
       </c>
-      <c r="D486" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F486" t="s">
-        <v>19</v>
-      </c>
       <c r="G486" t="s">
         <v>14</v>
       </c>
       <c r="H486">
-        <v>45404</v>
+        <v>45317</v>
       </c>
       <c r="I486" t="s">
         <v>12</v>
@@ -15429,22 +15435,22 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C487" t="s">
         <v>1007</v>
       </c>
-      <c r="C487" t="s">
+      <c r="D487" t="s">
         <v>1008</v>
       </c>
-      <c r="D487" t="s">
-        <v>29</v>
-      </c>
       <c r="F487" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G487" t="s">
         <v>14</v>
       </c>
       <c r="H487">
-        <v>46010</v>
+        <v>45404</v>
       </c>
       <c r="I487" t="s">
         <v>12</v>
@@ -15458,16 +15464,16 @@
         <v>1010</v>
       </c>
       <c r="D488" t="s">
-        <v>1011</v>
+        <v>29</v>
       </c>
       <c r="F488" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G488" t="s">
         <v>14</v>
       </c>
       <c r="H488">
-        <v>45593</v>
+        <v>46010</v>
       </c>
       <c r="I488" t="s">
         <v>12</v>
@@ -15475,22 +15481,22 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C489" t="s">
         <v>1012</v>
       </c>
-      <c r="C489" t="s">
+      <c r="D489" t="s">
         <v>1013</v>
       </c>
-      <c r="D489" t="s">
-        <v>493</v>
-      </c>
       <c r="F489" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G489" t="s">
         <v>14</v>
       </c>
       <c r="H489">
-        <v>45329</v>
+        <v>45593</v>
       </c>
       <c r="I489" t="s">
         <v>12</v>
@@ -15498,10 +15504,10 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C490" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D490" t="s">
         <v>493</v>
@@ -15513,7 +15519,7 @@
         <v>14</v>
       </c>
       <c r="H490">
-        <v>46065</v>
+        <v>45329</v>
       </c>
       <c r="I490" t="s">
         <v>12</v>
@@ -15527,7 +15533,7 @@
         <v>1015</v>
       </c>
       <c r="D491" t="s">
-        <v>1016</v>
+        <v>493</v>
       </c>
       <c r="F491" t="s">
         <v>35</v>
@@ -15536,7 +15542,7 @@
         <v>14</v>
       </c>
       <c r="H491">
-        <v>45720</v>
+        <v>46065</v>
       </c>
       <c r="I491" t="s">
         <v>12</v>
@@ -15544,22 +15550,22 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C492" t="s">
         <v>1017</v>
       </c>
-      <c r="C492" t="s">
+      <c r="D492" t="s">
         <v>1018</v>
       </c>
-      <c r="D492" t="s">
-        <v>12</v>
-      </c>
       <c r="F492" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="G492" t="s">
         <v>14</v>
       </c>
       <c r="H492">
-        <v>45190</v>
+        <v>45720</v>
       </c>
       <c r="I492" t="s">
         <v>12</v>
@@ -15573,16 +15579,16 @@
         <v>1020</v>
       </c>
       <c r="D493" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F493" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G493" t="s">
         <v>14</v>
       </c>
       <c r="H493">
-        <v>45565</v>
+        <v>45190</v>
       </c>
       <c r="I493" t="s">
         <v>12</v>
@@ -15596,16 +15602,16 @@
         <v>1022</v>
       </c>
       <c r="D494" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="F494" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
       </c>
       <c r="H494">
-        <v>46000</v>
+        <v>45565</v>
       </c>
       <c r="I494" t="s">
         <v>12</v>
@@ -15613,22 +15619,22 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C495" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D495" t="s">
         <v>208</v>
       </c>
       <c r="F495" t="s">
-        <v>1023</v>
+        <v>202</v>
       </c>
       <c r="G495" t="s">
         <v>14</v>
       </c>
       <c r="H495">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="I495" t="s">
         <v>12</v>
@@ -15636,22 +15642,22 @@
     </row>
     <row r="496" spans="1:9">
       <c r="A496" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C496" t="s">
         <v>1024</v>
       </c>
-      <c r="C496" t="s">
+      <c r="D496" t="s">
+        <v>208</v>
+      </c>
+      <c r="F496" t="s">
         <v>1025</v>
       </c>
-      <c r="D496" t="s">
-        <v>12</v>
-      </c>
-      <c r="F496" t="s">
-        <v>35</v>
-      </c>
       <c r="G496" t="s">
         <v>14</v>
       </c>
       <c r="H496">
-        <v>46059</v>
+        <v>46044</v>
       </c>
       <c r="I496" t="s">
         <v>12</v>
@@ -15665,16 +15671,16 @@
         <v>1027</v>
       </c>
       <c r="D497" t="s">
-        <v>1028</v>
+        <v>12</v>
       </c>
       <c r="F497" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G497" t="s">
         <v>14</v>
       </c>
       <c r="H497">
-        <v>45083</v>
+        <v>46059</v>
       </c>
       <c r="I497" t="s">
         <v>12</v>
@@ -15682,22 +15688,22 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C498" t="s">
         <v>1029</v>
       </c>
-      <c r="C498" t="s">
+      <c r="D498" t="s">
         <v>1030</v>
       </c>
-      <c r="D498" t="s">
-        <v>372</v>
-      </c>
       <c r="F498" t="s">
-        <v>246</v>
+        <v>42</v>
       </c>
       <c r="G498" t="s">
         <v>14</v>
       </c>
       <c r="H498">
-        <v>45593</v>
+        <v>45083</v>
       </c>
       <c r="I498" t="s">
         <v>12</v>
@@ -15711,16 +15717,16 @@
         <v>1032</v>
       </c>
       <c r="D499" t="s">
-        <v>1033</v>
+        <v>372</v>
       </c>
       <c r="F499" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="G499" t="s">
         <v>14</v>
       </c>
       <c r="H499">
-        <v>46006</v>
+        <v>45593</v>
       </c>
       <c r="I499" t="s">
         <v>12</v>
@@ -15728,22 +15734,22 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C500" t="s">
         <v>1034</v>
       </c>
-      <c r="C500" t="s">
+      <c r="D500" t="s">
         <v>1035</v>
       </c>
-      <c r="D500" t="s">
-        <v>1036</v>
-      </c>
       <c r="F500" t="s">
-        <v>1037</v>
+        <v>22</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
       </c>
       <c r="H500">
-        <v>45573</v>
+        <v>46006</v>
       </c>
       <c r="I500" t="s">
         <v>12</v>
@@ -15751,22 +15757,22 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D501" t="s">
         <v>1038</v>
       </c>
-      <c r="C501" t="s">
+      <c r="F501" t="s">
         <v>1039</v>
       </c>
-      <c r="D501" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F501" t="s">
-        <v>24</v>
-      </c>
       <c r="G501" t="s">
         <v>14</v>
       </c>
       <c r="H501">
-        <v>45049</v>
+        <v>45573</v>
       </c>
       <c r="I501" t="s">
         <v>12</v>
@@ -15774,22 +15780,22 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C502" t="s">
         <v>1041</v>
       </c>
       <c r="D502" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F502" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
       </c>
       <c r="H502">
-        <v>45114</v>
+        <v>45049</v>
       </c>
       <c r="I502" t="s">
         <v>12</v>
@@ -15797,25 +15803,22 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C503" t="s">
         <v>1043</v>
       </c>
       <c r="D503" t="s">
-        <v>285</v>
-      </c>
-      <c r="E503" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F503" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
       </c>
       <c r="H503">
-        <v>45727</v>
+        <v>45114</v>
       </c>
       <c r="I503" t="s">
         <v>12</v>
@@ -15823,25 +15826,25 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C504" t="s">
         <v>1045</v>
       </c>
       <c r="D504" t="s">
+        <v>285</v>
+      </c>
+      <c r="E504" t="s">
         <v>1046</v>
       </c>
-      <c r="E504" t="s">
-        <v>1047</v>
-      </c>
       <c r="F504" t="s">
-        <v>1048</v>
+        <v>22</v>
       </c>
       <c r="G504" t="s">
         <v>14</v>
       </c>
       <c r="H504">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="I504" t="s">
         <v>12</v>
@@ -15849,25 +15852,25 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C505" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E505" t="s">
         <v>1049</v>
       </c>
-      <c r="D505" t="s">
-        <v>146</v>
-      </c>
-      <c r="E505" t="s">
+      <c r="F505" t="s">
         <v>1050</v>
       </c>
-      <c r="F505" t="s">
-        <v>60</v>
-      </c>
       <c r="G505" t="s">
         <v>14</v>
       </c>
       <c r="H505">
-        <v>45747</v>
+        <v>45797</v>
       </c>
       <c r="I505" t="s">
         <v>12</v>
@@ -15875,25 +15878,25 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C506" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="D506" t="s">
         <v>146</v>
       </c>
       <c r="E506" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F506" t="s">
-        <v>1051</v>
+        <v>60</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
       </c>
       <c r="H506">
-        <v>45813</v>
+        <v>45747</v>
       </c>
       <c r="I506" t="s">
         <v>12</v>
@@ -15901,25 +15904,25 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C507" t="s">
-        <v>159</v>
+        <v>1051</v>
       </c>
       <c r="D507" t="s">
-        <v>587</v>
+        <v>146</v>
       </c>
       <c r="E507" t="s">
-        <v>173</v>
+        <v>1052</v>
       </c>
       <c r="F507" t="s">
-        <v>22</v>
+        <v>1053</v>
       </c>
       <c r="G507" t="s">
         <v>14</v>
       </c>
       <c r="H507">
-        <v>45043</v>
+        <v>45813</v>
       </c>
       <c r="I507" t="s">
         <v>12</v>
@@ -15927,16 +15930,16 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C508" t="s">
-        <v>1052</v>
+        <v>159</v>
       </c>
       <c r="D508" t="s">
-        <v>98</v>
+        <v>587</v>
       </c>
       <c r="E508" t="s">
-        <v>1053</v>
+        <v>173</v>
       </c>
       <c r="F508" t="s">
         <v>22</v>
@@ -15953,25 +15956,25 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C509" t="s">
         <v>1054</v>
       </c>
       <c r="D509" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="E509" t="s">
         <v>1055</v>
       </c>
       <c r="F509" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G509" t="s">
         <v>14</v>
       </c>
       <c r="H509">
-        <v>45184</v>
+        <v>45043</v>
       </c>
       <c r="I509" t="s">
         <v>12</v>
@@ -15979,7 +15982,7 @@
     </row>
     <row r="510" spans="1:9">
       <c r="A510" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C510" t="s">
         <v>1056</v>
@@ -15988,7 +15991,7 @@
         <v>208</v>
       </c>
       <c r="E510" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F510" t="s">
         <v>13</v>
@@ -15997,7 +16000,7 @@
         <v>14</v>
       </c>
       <c r="H510">
-        <v>45219</v>
+        <v>45184</v>
       </c>
       <c r="I510" t="s">
         <v>12</v>
@@ -16005,16 +16008,16 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C511" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D511" t="s">
+        <v>208</v>
+      </c>
+      <c r="E511" t="s">
         <v>1057</v>
-      </c>
-      <c r="D511" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E511" t="s">
-        <v>1059</v>
       </c>
       <c r="F511" t="s">
         <v>13</v>
@@ -16023,7 +16026,7 @@
         <v>14</v>
       </c>
       <c r="H511">
-        <v>45303</v>
+        <v>45219</v>
       </c>
       <c r="I511" t="s">
         <v>12</v>
@@ -16031,12 +16034,15 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C512" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D512" t="s">
         <v>1060</v>
       </c>
-      <c r="D512" t="s">
+      <c r="E512" t="s">
         <v>1061</v>
       </c>
       <c r="F512" t="s">
@@ -16046,7 +16052,7 @@
         <v>14</v>
       </c>
       <c r="H512">
-        <v>45327</v>
+        <v>45303</v>
       </c>
       <c r="I512" t="s">
         <v>12</v>
@@ -16054,16 +16060,13 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C513" t="s">
         <v>1062</v>
       </c>
       <c r="D513" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E513" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F513" t="s">
         <v>13</v>
@@ -16080,12 +16083,15 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C514" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D514" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E514" t="s">
         <v>1061</v>
       </c>
       <c r="F514" t="s">
@@ -16103,16 +16109,13 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C515" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D515" t="s">
-        <v>54</v>
-      </c>
-      <c r="E515" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F515" t="s">
         <v>13</v>
@@ -16121,7 +16124,7 @@
         <v>14</v>
       </c>
       <c r="H515">
-        <v>45439</v>
+        <v>45327</v>
       </c>
       <c r="I515" t="s">
         <v>12</v>
@@ -16129,22 +16132,25 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C516" t="s">
         <v>1066</v>
       </c>
       <c r="D516" t="s">
-        <v>329</v>
+        <v>54</v>
+      </c>
+      <c r="E516" t="s">
+        <v>1067</v>
       </c>
       <c r="F516" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
       </c>
       <c r="H516">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="I516" t="s">
         <v>12</v>
@@ -16152,22 +16158,22 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1067</v>
+        <v>1044</v>
       </c>
       <c r="C517" t="s">
         <v>1068</v>
       </c>
       <c r="D517" t="s">
-        <v>1069</v>
+        <v>329</v>
       </c>
       <c r="F517" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G517" t="s">
         <v>14</v>
       </c>
       <c r="H517">
-        <v>45022</v>
+        <v>45951</v>
       </c>
       <c r="I517" t="s">
         <v>12</v>
@@ -16175,22 +16181,22 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C518" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D518" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F518" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="G518" t="s">
         <v>14</v>
       </c>
       <c r="H518">
-        <v>45275</v>
+        <v>45022</v>
       </c>
       <c r="I518" t="s">
         <v>12</v>
@@ -16198,22 +16204,22 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C519" t="s">
         <v>1070</v>
       </c>
-      <c r="C519" t="s">
+      <c r="D519" t="s">
         <v>1071</v>
       </c>
-      <c r="D519" t="s">
-        <v>1072</v>
-      </c>
       <c r="F519" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G519" t="s">
         <v>14</v>
       </c>
       <c r="H519">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="I519" t="s">
         <v>12</v>
@@ -16221,13 +16227,13 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C520" t="s">
         <v>1073</v>
       </c>
-      <c r="C520" t="s">
+      <c r="D520" t="s">
         <v>1074</v>
-      </c>
-      <c r="D520" t="s">
-        <v>98</v>
       </c>
       <c r="F520" t="s">
         <v>13</v>
@@ -16236,7 +16242,7 @@
         <v>14</v>
       </c>
       <c r="H520">
-        <v>45722</v>
+        <v>45792</v>
       </c>
       <c r="I520" t="s">
         <v>12</v>
@@ -16250,16 +16256,16 @@
         <v>1076</v>
       </c>
       <c r="D521" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F521" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G521" t="s">
         <v>14</v>
       </c>
       <c r="H521">
-        <v>45107</v>
+        <v>45722</v>
       </c>
       <c r="I521" t="s">
         <v>12</v>
@@ -16276,13 +16282,13 @@
         <v>12</v>
       </c>
       <c r="F522" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
       </c>
       <c r="H522">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="I522" t="s">
         <v>12</v>
@@ -16290,22 +16296,22 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C523" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D523" t="s">
         <v>12</v>
       </c>
       <c r="F523" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G523" t="s">
         <v>14</v>
       </c>
       <c r="H523">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="I523" t="s">
         <v>12</v>
@@ -16313,22 +16319,22 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C524" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D524" t="s">
         <v>12</v>
       </c>
       <c r="F524" t="s">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
       </c>
       <c r="H524">
-        <v>45141</v>
+        <v>45107</v>
       </c>
       <c r="I524" t="s">
         <v>12</v>
@@ -16336,22 +16342,22 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C525" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D525" t="s">
         <v>12</v>
       </c>
       <c r="F525" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="G525" t="s">
         <v>14</v>
       </c>
       <c r="H525">
-        <v>45194</v>
+        <v>45141</v>
       </c>
       <c r="I525" t="s">
         <v>12</v>
@@ -16359,22 +16365,22 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C526" t="s">
         <v>1082</v>
       </c>
       <c r="D526" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="F526" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G526" t="s">
         <v>14</v>
       </c>
       <c r="H526">
-        <v>45856</v>
+        <v>45194</v>
       </c>
       <c r="I526" t="s">
         <v>12</v>
@@ -16382,16 +16388,16 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C527" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D527" t="s">
         <v>245</v>
       </c>
       <c r="F527" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
@@ -16405,22 +16411,22 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C528" t="s">
         <v>1085</v>
       </c>
       <c r="D528" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="F528" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
       </c>
       <c r="H528">
-        <v>45392</v>
+        <v>45856</v>
       </c>
       <c r="I528" t="s">
         <v>12</v>
@@ -16428,13 +16434,13 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C529" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D529" t="s">
-        <v>1086</v>
+        <v>77</v>
       </c>
       <c r="F529" t="s">
         <v>35</v>
@@ -16443,7 +16449,7 @@
         <v>14</v>
       </c>
       <c r="H529">
-        <v>45792</v>
+        <v>45392</v>
       </c>
       <c r="I529" t="s">
         <v>12</v>
@@ -16451,13 +16457,13 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C530" t="s">
         <v>1087</v>
       </c>
-      <c r="C530" t="s">
+      <c r="D530" t="s">
         <v>1088</v>
-      </c>
-      <c r="D530" t="s">
-        <v>1089</v>
       </c>
       <c r="F530" t="s">
         <v>35</v>
@@ -16466,7 +16472,7 @@
         <v>14</v>
       </c>
       <c r="H530">
-        <v>45495</v>
+        <v>45792</v>
       </c>
       <c r="I530" t="s">
         <v>12</v>
@@ -16474,22 +16480,22 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C531" t="s">
         <v>1090</v>
       </c>
-      <c r="C531" t="s">
+      <c r="D531" t="s">
         <v>1091</v>
       </c>
-      <c r="D531" t="s">
-        <v>1092</v>
-      </c>
       <c r="F531" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
       </c>
       <c r="H531">
-        <v>45223</v>
+        <v>45495</v>
       </c>
       <c r="I531" t="s">
         <v>12</v>
@@ -16497,22 +16503,22 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C532" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D532" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="F532" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
       </c>
       <c r="H532">
-        <v>45254</v>
+        <v>45223</v>
       </c>
       <c r="I532" t="s">
         <v>12</v>
@@ -16520,22 +16526,22 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C533" t="s">
         <v>1093</v>
       </c>
-      <c r="C533" t="s">
+      <c r="D533" t="s">
         <v>1094</v>
       </c>
-      <c r="D533" t="s">
-        <v>12</v>
-      </c>
       <c r="F533" t="s">
-        <v>693</v>
+        <v>19</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
       </c>
       <c r="H533">
-        <v>45807</v>
+        <v>45254</v>
       </c>
       <c r="I533" t="s">
         <v>12</v>
@@ -16552,13 +16558,13 @@
         <v>12</v>
       </c>
       <c r="F534" t="s">
-        <v>13</v>
+        <v>693</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
       </c>
       <c r="H534">
-        <v>45849</v>
+        <v>45807</v>
       </c>
       <c r="I534" t="s">
         <v>12</v>
@@ -16572,7 +16578,7 @@
         <v>1098</v>
       </c>
       <c r="D535" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F535" t="s">
         <v>13</v>
@@ -16581,7 +16587,7 @@
         <v>14</v>
       </c>
       <c r="H535">
-        <v>46000</v>
+        <v>45849</v>
       </c>
       <c r="I535" t="s">
         <v>12</v>
@@ -16589,10 +16595,10 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C536" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D536" t="s">
         <v>29</v>
@@ -16604,7 +16610,7 @@
         <v>14</v>
       </c>
       <c r="H536">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="I536" t="s">
         <v>12</v>
@@ -16612,22 +16618,22 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C537" t="s">
         <v>1101</v>
       </c>
       <c r="D537" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="F537" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G537" t="s">
         <v>14</v>
       </c>
       <c r="H537">
-        <v>45825</v>
+        <v>46010</v>
       </c>
       <c r="I537" t="s">
         <v>12</v>
@@ -16635,22 +16641,22 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C538" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D538" t="s">
-        <v>1102</v>
+        <v>98</v>
       </c>
       <c r="F538" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="G538" t="s">
         <v>14</v>
       </c>
       <c r="H538">
-        <v>46078</v>
+        <v>45825</v>
       </c>
       <c r="I538" t="s">
         <v>12</v>
@@ -16658,22 +16664,22 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C539" t="s">
         <v>1103</v>
       </c>
-      <c r="C539" t="s">
+      <c r="D539" t="s">
         <v>1104</v>
       </c>
-      <c r="D539" t="s">
-        <v>1105</v>
-      </c>
       <c r="F539" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G539" t="s">
         <v>14</v>
       </c>
       <c r="H539">
-        <v>46035</v>
+        <v>46078</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16681,22 +16687,22 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C540" t="s">
         <v>1106</v>
       </c>
-      <c r="C540" t="s">
+      <c r="D540" t="s">
         <v>1107</v>
       </c>
-      <c r="D540" t="s">
-        <v>98</v>
-      </c>
       <c r="F540" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G540" t="s">
         <v>14</v>
       </c>
       <c r="H540">
-        <v>45985</v>
+        <v>46035</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16710,16 +16716,16 @@
         <v>1109</v>
       </c>
       <c r="D541" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F541" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
       </c>
       <c r="H541">
-        <v>45190</v>
+        <v>45985</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16733,16 +16739,16 @@
         <v>1111</v>
       </c>
       <c r="D542" t="s">
-        <v>1112</v>
+        <v>12</v>
       </c>
       <c r="F542" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G542" t="s">
         <v>14</v>
       </c>
       <c r="H542">
-        <v>45029</v>
+        <v>45190</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16750,25 +16756,22 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C543" t="s">
         <v>1113</v>
       </c>
-      <c r="C543" t="s">
+      <c r="D543" t="s">
         <v>1114</v>
       </c>
-      <c r="D543" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1116</v>
-      </c>
       <c r="F543" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G543" t="s">
         <v>14</v>
       </c>
       <c r="H543">
-        <v>45376</v>
+        <v>45029</v>
       </c>
       <c r="I543" t="s">
         <v>12</v>
@@ -16776,25 +16779,25 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C544" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D544" t="s">
         <v>1117</v>
       </c>
-      <c r="B544" t="s">
+      <c r="E544" t="s">
         <v>1118</v>
       </c>
-      <c r="C544" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1120</v>
-      </c>
       <c r="F544" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
       </c>
       <c r="H544">
-        <v>45085</v>
+        <v>45376</v>
       </c>
       <c r="I544" t="s">
         <v>12</v>
@@ -16802,10 +16805,10 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B545" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C545" t="s">
         <v>1121</v>
@@ -16820,7 +16823,7 @@
         <v>14</v>
       </c>
       <c r="H545">
-        <v>45387</v>
+        <v>45085</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -16828,10 +16831,10 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B546" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C546" t="s">
         <v>1123</v>
@@ -16840,13 +16843,13 @@
         <v>1124</v>
       </c>
       <c r="F546" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G546" t="s">
         <v>14</v>
       </c>
       <c r="H546">
-        <v>45764</v>
+        <v>45387</v>
       </c>
       <c r="I546" t="s">
         <v>12</v>
@@ -16854,24 +16857,50 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C547" t="s">
         <v>1125</v>
       </c>
-      <c r="C547" t="s">
+      <c r="D547" t="s">
         <v>1126</v>
       </c>
-      <c r="D547" t="s">
+      <c r="F547" t="s">
+        <v>60</v>
+      </c>
+      <c r="G547" t="s">
+        <v>14</v>
+      </c>
+      <c r="H547">
+        <v>45764</v>
+      </c>
+      <c r="I547" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9">
+      <c r="A548" t="s">
         <v>1127</v>
       </c>
-      <c r="F547" t="s">
+      <c r="C548" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F548" t="s">
         <v>18</v>
       </c>
-      <c r="G547" t="s">
-        <v>14</v>
-      </c>
-      <c r="H547">
+      <c r="G548" t="s">
+        <v>14</v>
+      </c>
+      <c r="H548">
         <v>45477</v>
       </c>
-      <c r="I547" t="s">
+      <c r="I548" t="s">
         <v>12</v>
       </c>
     </row>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="1132">
   <si>
     <t>Fornitore</t>
   </si>
@@ -3134,6 +3134,12 @@
   </si>
   <si>
     <t>LDO,RAD,LAB,RSA</t>
+  </si>
+  <si>
+    <t>tarasoft_</t>
+  </si>
+  <si>
+    <t>45801</t>
   </si>
   <si>
     <t>TES</t>
@@ -3735,7 +3741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I548"/>
+  <dimension ref="A1:I549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -15786,16 +15792,16 @@
         <v>1041</v>
       </c>
       <c r="D502" t="s">
-        <v>1042</v>
+        <v>98</v>
       </c>
       <c r="F502" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
       </c>
       <c r="H502">
-        <v>45049</v>
+        <v>46080</v>
       </c>
       <c r="I502" t="s">
         <v>12</v>
@@ -15803,22 +15809,22 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C503" t="s">
         <v>1043</v>
       </c>
       <c r="D503" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F503" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
       </c>
       <c r="H503">
-        <v>45114</v>
+        <v>45049</v>
       </c>
       <c r="I503" t="s">
         <v>12</v>
@@ -15826,25 +15832,22 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C504" t="s">
         <v>1045</v>
       </c>
       <c r="D504" t="s">
-        <v>285</v>
-      </c>
-      <c r="E504" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F504" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G504" t="s">
         <v>14</v>
       </c>
       <c r="H504">
-        <v>45727</v>
+        <v>45114</v>
       </c>
       <c r="I504" t="s">
         <v>12</v>
@@ -15852,25 +15855,25 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C505" t="s">
         <v>1047</v>
       </c>
       <c r="D505" t="s">
+        <v>285</v>
+      </c>
+      <c r="E505" t="s">
         <v>1048</v>
       </c>
-      <c r="E505" t="s">
-        <v>1049</v>
-      </c>
       <c r="F505" t="s">
-        <v>1050</v>
+        <v>22</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
       </c>
       <c r="H505">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="I505" t="s">
         <v>12</v>
@@ -15878,25 +15881,25 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C506" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E506" t="s">
         <v>1051</v>
       </c>
-      <c r="D506" t="s">
-        <v>146</v>
-      </c>
-      <c r="E506" t="s">
+      <c r="F506" t="s">
         <v>1052</v>
       </c>
-      <c r="F506" t="s">
-        <v>60</v>
-      </c>
       <c r="G506" t="s">
         <v>14</v>
       </c>
       <c r="H506">
-        <v>45747</v>
+        <v>45797</v>
       </c>
       <c r="I506" t="s">
         <v>12</v>
@@ -15904,25 +15907,25 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C507" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D507" t="s">
         <v>146</v>
       </c>
       <c r="E507" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F507" t="s">
-        <v>1053</v>
+        <v>60</v>
       </c>
       <c r="G507" t="s">
         <v>14</v>
       </c>
       <c r="H507">
-        <v>45813</v>
+        <v>45747</v>
       </c>
       <c r="I507" t="s">
         <v>12</v>
@@ -15930,25 +15933,25 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C508" t="s">
-        <v>159</v>
+        <v>1053</v>
       </c>
       <c r="D508" t="s">
-        <v>587</v>
+        <v>146</v>
       </c>
       <c r="E508" t="s">
-        <v>173</v>
+        <v>1054</v>
       </c>
       <c r="F508" t="s">
-        <v>22</v>
+        <v>1055</v>
       </c>
       <c r="G508" t="s">
         <v>14</v>
       </c>
       <c r="H508">
-        <v>45043</v>
+        <v>45813</v>
       </c>
       <c r="I508" t="s">
         <v>12</v>
@@ -15956,16 +15959,16 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C509" t="s">
-        <v>1054</v>
+        <v>159</v>
       </c>
       <c r="D509" t="s">
-        <v>98</v>
+        <v>587</v>
       </c>
       <c r="E509" t="s">
-        <v>1055</v>
+        <v>173</v>
       </c>
       <c r="F509" t="s">
         <v>22</v>
@@ -15982,25 +15985,25 @@
     </row>
     <row r="510" spans="1:9">
       <c r="A510" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C510" t="s">
         <v>1056</v>
       </c>
       <c r="D510" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="E510" t="s">
         <v>1057</v>
       </c>
       <c r="F510" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G510" t="s">
         <v>14</v>
       </c>
       <c r="H510">
-        <v>45184</v>
+        <v>45043</v>
       </c>
       <c r="I510" t="s">
         <v>12</v>
@@ -16008,7 +16011,7 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C511" t="s">
         <v>1058</v>
@@ -16017,7 +16020,7 @@
         <v>208</v>
       </c>
       <c r="E511" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F511" t="s">
         <v>13</v>
@@ -16026,7 +16029,7 @@
         <v>14</v>
       </c>
       <c r="H511">
-        <v>45219</v>
+        <v>45184</v>
       </c>
       <c r="I511" t="s">
         <v>12</v>
@@ -16034,16 +16037,16 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C512" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D512" t="s">
+        <v>208</v>
+      </c>
+      <c r="E512" t="s">
         <v>1059</v>
-      </c>
-      <c r="D512" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1061</v>
       </c>
       <c r="F512" t="s">
         <v>13</v>
@@ -16052,7 +16055,7 @@
         <v>14</v>
       </c>
       <c r="H512">
-        <v>45303</v>
+        <v>45219</v>
       </c>
       <c r="I512" t="s">
         <v>12</v>
@@ -16060,12 +16063,15 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C513" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D513" t="s">
         <v>1062</v>
       </c>
-      <c r="D513" t="s">
+      <c r="E513" t="s">
         <v>1063</v>
       </c>
       <c r="F513" t="s">
@@ -16075,7 +16081,7 @@
         <v>14</v>
       </c>
       <c r="H513">
-        <v>45327</v>
+        <v>45303</v>
       </c>
       <c r="I513" t="s">
         <v>12</v>
@@ -16083,16 +16089,13 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C514" t="s">
         <v>1064</v>
       </c>
       <c r="D514" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E514" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="F514" t="s">
         <v>13</v>
@@ -16109,12 +16112,15 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C515" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D515" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E515" t="s">
         <v>1063</v>
       </c>
       <c r="F515" t="s">
@@ -16132,16 +16138,13 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C516" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D516" t="s">
-        <v>54</v>
-      </c>
-      <c r="E516" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F516" t="s">
         <v>13</v>
@@ -16150,7 +16153,7 @@
         <v>14</v>
       </c>
       <c r="H516">
-        <v>45439</v>
+        <v>45327</v>
       </c>
       <c r="I516" t="s">
         <v>12</v>
@@ -16158,22 +16161,25 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C517" t="s">
         <v>1068</v>
       </c>
       <c r="D517" t="s">
-        <v>329</v>
+        <v>54</v>
+      </c>
+      <c r="E517" t="s">
+        <v>1069</v>
       </c>
       <c r="F517" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G517" t="s">
         <v>14</v>
       </c>
       <c r="H517">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="I517" t="s">
         <v>12</v>
@@ -16181,22 +16187,22 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1069</v>
+        <v>1046</v>
       </c>
       <c r="C518" t="s">
         <v>1070</v>
       </c>
       <c r="D518" t="s">
-        <v>1071</v>
+        <v>329</v>
       </c>
       <c r="F518" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G518" t="s">
         <v>14</v>
       </c>
       <c r="H518">
-        <v>45022</v>
+        <v>45951</v>
       </c>
       <c r="I518" t="s">
         <v>12</v>
@@ -16204,22 +16210,22 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C519" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D519" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F519" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="G519" t="s">
         <v>14</v>
       </c>
       <c r="H519">
-        <v>45275</v>
+        <v>45022</v>
       </c>
       <c r="I519" t="s">
         <v>12</v>
@@ -16227,22 +16233,22 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C520" t="s">
         <v>1072</v>
       </c>
-      <c r="C520" t="s">
+      <c r="D520" t="s">
         <v>1073</v>
       </c>
-      <c r="D520" t="s">
-        <v>1074</v>
-      </c>
       <c r="F520" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G520" t="s">
         <v>14</v>
       </c>
       <c r="H520">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="I520" t="s">
         <v>12</v>
@@ -16250,13 +16256,13 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C521" t="s">
         <v>1075</v>
       </c>
-      <c r="C521" t="s">
+      <c r="D521" t="s">
         <v>1076</v>
-      </c>
-      <c r="D521" t="s">
-        <v>98</v>
       </c>
       <c r="F521" t="s">
         <v>13</v>
@@ -16265,7 +16271,7 @@
         <v>14</v>
       </c>
       <c r="H521">
-        <v>45722</v>
+        <v>45792</v>
       </c>
       <c r="I521" t="s">
         <v>12</v>
@@ -16279,16 +16285,16 @@
         <v>1078</v>
       </c>
       <c r="D522" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F522" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
       </c>
       <c r="H522">
-        <v>45107</v>
+        <v>45722</v>
       </c>
       <c r="I522" t="s">
         <v>12</v>
@@ -16305,13 +16311,13 @@
         <v>12</v>
       </c>
       <c r="F523" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G523" t="s">
         <v>14</v>
       </c>
       <c r="H523">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="I523" t="s">
         <v>12</v>
@@ -16319,22 +16325,22 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="C524" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D524" t="s">
         <v>12</v>
       </c>
       <c r="F524" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
       </c>
       <c r="H524">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="I524" t="s">
         <v>12</v>
@@ -16342,22 +16348,22 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C525" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D525" t="s">
         <v>12</v>
       </c>
       <c r="F525" t="s">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="G525" t="s">
         <v>14</v>
       </c>
       <c r="H525">
-        <v>45141</v>
+        <v>45107</v>
       </c>
       <c r="I525" t="s">
         <v>12</v>
@@ -16365,22 +16371,22 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C526" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D526" t="s">
         <v>12</v>
       </c>
       <c r="F526" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="G526" t="s">
         <v>14</v>
       </c>
       <c r="H526">
-        <v>45194</v>
+        <v>45141</v>
       </c>
       <c r="I526" t="s">
         <v>12</v>
@@ -16388,22 +16394,22 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C527" t="s">
         <v>1084</v>
       </c>
       <c r="D527" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="F527" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
       </c>
       <c r="H527">
-        <v>45856</v>
+        <v>45194</v>
       </c>
       <c r="I527" t="s">
         <v>12</v>
@@ -16411,16 +16417,16 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C528" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D528" t="s">
         <v>245</v>
       </c>
       <c r="F528" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
@@ -16434,22 +16440,22 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C529" t="s">
         <v>1087</v>
       </c>
       <c r="D529" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="F529" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G529" t="s">
         <v>14</v>
       </c>
       <c r="H529">
-        <v>45392</v>
+        <v>45856</v>
       </c>
       <c r="I529" t="s">
         <v>12</v>
@@ -16457,13 +16463,13 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C530" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D530" t="s">
-        <v>1088</v>
+        <v>77</v>
       </c>
       <c r="F530" t="s">
         <v>35</v>
@@ -16472,7 +16478,7 @@
         <v>14</v>
       </c>
       <c r="H530">
-        <v>45792</v>
+        <v>45392</v>
       </c>
       <c r="I530" t="s">
         <v>12</v>
@@ -16480,13 +16486,13 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C531" t="s">
         <v>1089</v>
       </c>
-      <c r="C531" t="s">
+      <c r="D531" t="s">
         <v>1090</v>
-      </c>
-      <c r="D531" t="s">
-        <v>1091</v>
       </c>
       <c r="F531" t="s">
         <v>35</v>
@@ -16495,7 +16501,7 @@
         <v>14</v>
       </c>
       <c r="H531">
-        <v>45495</v>
+        <v>45792</v>
       </c>
       <c r="I531" t="s">
         <v>12</v>
@@ -16503,22 +16509,22 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C532" t="s">
         <v>1092</v>
       </c>
-      <c r="C532" t="s">
+      <c r="D532" t="s">
         <v>1093</v>
       </c>
-      <c r="D532" t="s">
-        <v>1094</v>
-      </c>
       <c r="F532" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
       </c>
       <c r="H532">
-        <v>45223</v>
+        <v>45495</v>
       </c>
       <c r="I532" t="s">
         <v>12</v>
@@ -16526,22 +16532,22 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C533" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D533" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F533" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
       </c>
       <c r="H533">
-        <v>45254</v>
+        <v>45223</v>
       </c>
       <c r="I533" t="s">
         <v>12</v>
@@ -16549,22 +16555,22 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C534" t="s">
         <v>1095</v>
       </c>
-      <c r="C534" t="s">
+      <c r="D534" t="s">
         <v>1096</v>
       </c>
-      <c r="D534" t="s">
-        <v>12</v>
-      </c>
       <c r="F534" t="s">
-        <v>693</v>
+        <v>19</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
       </c>
       <c r="H534">
-        <v>45807</v>
+        <v>45254</v>
       </c>
       <c r="I534" t="s">
         <v>12</v>
@@ -16581,13 +16587,13 @@
         <v>12</v>
       </c>
       <c r="F535" t="s">
-        <v>13</v>
+        <v>693</v>
       </c>
       <c r="G535" t="s">
         <v>14</v>
       </c>
       <c r="H535">
-        <v>45849</v>
+        <v>45807</v>
       </c>
       <c r="I535" t="s">
         <v>12</v>
@@ -16601,7 +16607,7 @@
         <v>1100</v>
       </c>
       <c r="D536" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F536" t="s">
         <v>13</v>
@@ -16610,7 +16616,7 @@
         <v>14</v>
       </c>
       <c r="H536">
-        <v>46000</v>
+        <v>45849</v>
       </c>
       <c r="I536" t="s">
         <v>12</v>
@@ -16618,10 +16624,10 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C537" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D537" t="s">
         <v>29</v>
@@ -16633,7 +16639,7 @@
         <v>14</v>
       </c>
       <c r="H537">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="I537" t="s">
         <v>12</v>
@@ -16641,22 +16647,22 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C538" t="s">
         <v>1103</v>
       </c>
       <c r="D538" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="F538" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G538" t="s">
         <v>14</v>
       </c>
       <c r="H538">
-        <v>45825</v>
+        <v>46010</v>
       </c>
       <c r="I538" t="s">
         <v>12</v>
@@ -16664,22 +16670,22 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C539" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D539" t="s">
-        <v>1104</v>
+        <v>98</v>
       </c>
       <c r="F539" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="G539" t="s">
         <v>14</v>
       </c>
       <c r="H539">
-        <v>46078</v>
+        <v>45825</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16687,22 +16693,22 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C540" t="s">
         <v>1105</v>
       </c>
-      <c r="C540" t="s">
+      <c r="D540" t="s">
         <v>1106</v>
       </c>
-      <c r="D540" t="s">
-        <v>1107</v>
-      </c>
       <c r="F540" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G540" t="s">
         <v>14</v>
       </c>
       <c r="H540">
-        <v>46035</v>
+        <v>46078</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16710,22 +16716,22 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C541" t="s">
         <v>1108</v>
       </c>
-      <c r="C541" t="s">
+      <c r="D541" t="s">
         <v>1109</v>
       </c>
-      <c r="D541" t="s">
-        <v>98</v>
-      </c>
       <c r="F541" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
       </c>
       <c r="H541">
-        <v>45985</v>
+        <v>46035</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16739,16 +16745,16 @@
         <v>1111</v>
       </c>
       <c r="D542" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F542" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G542" t="s">
         <v>14</v>
       </c>
       <c r="H542">
-        <v>45190</v>
+        <v>45985</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16762,16 +16768,16 @@
         <v>1113</v>
       </c>
       <c r="D543" t="s">
-        <v>1114</v>
+        <v>12</v>
       </c>
       <c r="F543" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G543" t="s">
         <v>14</v>
       </c>
       <c r="H543">
-        <v>45029</v>
+        <v>45190</v>
       </c>
       <c r="I543" t="s">
         <v>12</v>
@@ -16779,25 +16785,22 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C544" t="s">
         <v>1115</v>
       </c>
-      <c r="C544" t="s">
+      <c r="D544" t="s">
         <v>1116</v>
       </c>
-      <c r="D544" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1118</v>
-      </c>
       <c r="F544" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
       </c>
       <c r="H544">
-        <v>45376</v>
+        <v>45029</v>
       </c>
       <c r="I544" t="s">
         <v>12</v>
@@ -16805,25 +16808,25 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D545" t="s">
         <v>1119</v>
       </c>
-      <c r="B545" t="s">
+      <c r="E545" t="s">
         <v>1120</v>
       </c>
-      <c r="C545" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D545" t="s">
-        <v>1122</v>
-      </c>
       <c r="F545" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G545" t="s">
         <v>14</v>
       </c>
       <c r="H545">
-        <v>45085</v>
+        <v>45376</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -16831,10 +16834,10 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B546" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C546" t="s">
         <v>1123</v>
@@ -16849,7 +16852,7 @@
         <v>14</v>
       </c>
       <c r="H546">
-        <v>45387</v>
+        <v>45085</v>
       </c>
       <c r="I546" t="s">
         <v>12</v>
@@ -16857,10 +16860,10 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B547" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C547" t="s">
         <v>1125</v>
@@ -16869,13 +16872,13 @@
         <v>1126</v>
       </c>
       <c r="F547" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G547" t="s">
         <v>14</v>
       </c>
       <c r="H547">
-        <v>45764</v>
+        <v>45387</v>
       </c>
       <c r="I547" t="s">
         <v>12</v>
@@ -16883,24 +16886,50 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C548" t="s">
         <v>1127</v>
       </c>
-      <c r="C548" t="s">
+      <c r="D548" t="s">
         <v>1128</v>
       </c>
-      <c r="D548" t="s">
+      <c r="F548" t="s">
+        <v>60</v>
+      </c>
+      <c r="G548" t="s">
+        <v>14</v>
+      </c>
+      <c r="H548">
+        <v>45764</v>
+      </c>
+      <c r="I548" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9">
+      <c r="A549" t="s">
         <v>1129</v>
       </c>
-      <c r="F548" t="s">
+      <c r="C549" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F549" t="s">
         <v>18</v>
       </c>
-      <c r="G548" t="s">
-        <v>14</v>
-      </c>
-      <c r="H548">
+      <c r="G549" t="s">
+        <v>14</v>
+      </c>
+      <c r="H549">
         <v>45477</v>
       </c>
-      <c r="I548" t="s">
+      <c r="I549" t="s">
         <v>12</v>
       </c>
     </row>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -937,7 +937,7 @@
     <t>6.6.0</t>
   </si>
   <si>
-    <t>6.7.0</t>
+    <t>6.7.0, 6.8.0</t>
   </si>
   <si>
     <t>WHOSPITAL</t>
@@ -1045,7 +1045,7 @@
     <t>22.1.1</t>
   </si>
   <si>
-    <t>23.0.0, 22.1.2, 23.0.1, 23.1.0, 23.2.0</t>
+    <t>23.0.0, 22.1.2, 23.0.1, 23.1.0, 23.2.0, 23.2.1</t>
   </si>
   <si>
     <t>ELEKTRA</t>
@@ -1552,10 +1552,10 @@
     <t>1.6</t>
   </si>
   <si>
-    <t>2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0</t>
-  </si>
-  <si>
-    <t>2.0.0, 2.1.0, 2.1.1, 2.1.2, 2.1.2.1, 2.1.2.2, 2.1.2.3, 2.1.3, 2.1.3.1, 2.1.4, 2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0</t>
+    <t>2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1</t>
+  </si>
+  <si>
+    <t>2.0.0, 2.1.0, 2.1.1, 2.1.2, 2.1.2.1, 2.1.2.2, 2.1.2.3, 2.1.3, 2.1.3.1, 2.1.4, 2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1</t>
   </si>
   <si>
     <t>Synapse Workflow</t>
@@ -2191,7 +2191,7 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>13.0.0, 13.0.1, 13.0.2, 13.0.3, 13.0.4, 13.0.5, 13.0.6</t>
+    <t>13.0.0, 13.0.1, 13.0.2, 13.0.3, 13.0.4, 13.0.5, 13.0.6, 13.0.7</t>
   </si>
   <si>
     <t>KG Partners s.r.l.</t>
@@ -2506,7 +2506,7 @@
     <t>20.0.55.0</t>
   </si>
   <si>
-    <t>20.0.61.0, 20.0.63.0, 20.0.65.0, 20.0.66.0, 20.0.67.0</t>
+    <t>20.0.61.0, 20.0.63.0, 20.0.65.0, 20.0.66.0, 20.0.67.0, 20.0.68.0</t>
   </si>
   <si>
     <t>MILLEWEB</t>
@@ -2644,7 +2644,7 @@
     <t>7.0.0</t>
   </si>
   <si>
-    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28</t>
+    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30</t>
   </si>
   <si>
     <t>cis</t>
@@ -3748,7 +3748,7 @@
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="987.7109375" customWidth="1"/>
+    <col min="5" max="5" width="1011.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="9" width="16.7109375" customWidth="1"/>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3486" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="1133">
   <si>
     <t>Fornitore</t>
   </si>
@@ -1012,7 +1012,7 @@
     <t>2303.05.01.00</t>
   </si>
   <si>
-    <t>2308.06.00.00, 2311.07.00.00, 2402.07.05.02, 2403.07.07.00, 2405.01.03.04, 2405.07.11.00, 2406.07.11.01, 2406.07.11.00, 2507.07.31.00, 2511.07.36.00</t>
+    <t>2308.06.00.00, 2311.07.00.00, 2402.07.05.02, 2403.07.07.00, 2405.01.03.04, 2405.07.11.00, 2406.07.11.01, 2406.07.11.00, 2507.07.31.00, 2511.07.36.00, 2603.09.00.00</t>
   </si>
   <si>
     <t>P4PVACCINAZIONI</t>
@@ -1480,6 +1480,9 @@
     <t>5</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>aurora</t>
   </si>
   <si>
@@ -2647,7 +2650,7 @@
     <t>7.0.0</t>
   </si>
   <si>
-    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30</t>
+    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31</t>
   </si>
   <si>
     <t>cis</t>
@@ -3023,9 +3026,6 @@
   </si>
   <si>
     <t>GIAVA</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>sincronet</t>
@@ -3751,7 +3751,7 @@
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="1011.7109375" customWidth="1"/>
+    <col min="5" max="5" width="1035.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="9" width="16.7109375" customWidth="1"/>
@@ -9290,6 +9290,9 @@
       <c r="D229" t="s">
         <v>487</v>
       </c>
+      <c r="E229" t="s">
+        <v>488</v>
+      </c>
       <c r="F229" t="s">
         <v>24</v>
       </c>
@@ -9308,7 +9311,7 @@
         <v>485</v>
       </c>
       <c r="C230" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D230" t="s">
         <v>65</v>
@@ -9331,10 +9334,10 @@
         <v>485</v>
       </c>
       <c r="C231" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D231" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F231" t="s">
         <v>13</v>
@@ -9354,7 +9357,7 @@
         <v>485</v>
       </c>
       <c r="C232" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D232" t="s">
         <v>39</v>
@@ -9377,7 +9380,7 @@
         <v>482</v>
       </c>
       <c r="C233" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D233" t="s">
         <v>39</v>
@@ -9397,13 +9400,13 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C234" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D234" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E234" t="s">
         <v>115</v>
@@ -9426,7 +9429,7 @@
         <v>485</v>
       </c>
       <c r="C235" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D235" t="s">
         <v>487</v>
@@ -9446,16 +9449,16 @@
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B236" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F236" t="s">
         <v>60</v>
@@ -9472,13 +9475,13 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C237" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D237" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F237" t="s">
         <v>18</v>
@@ -9495,13 +9498,13 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -9518,13 +9521,13 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C239" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D239" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F239" t="s">
         <v>18</v>
@@ -9541,13 +9544,13 @@
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F240" t="s">
         <v>19</v>
@@ -9564,16 +9567,16 @@
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C241" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F241" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G241" t="s">
         <v>14</v>
@@ -9587,10 +9590,10 @@
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C242" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D242" t="s">
         <v>12</v>
@@ -9610,10 +9613,10 @@
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C243" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D243" t="s">
         <v>12</v>
@@ -9633,16 +9636,16 @@
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C244" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D244" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E244" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F244" t="s">
         <v>24</v>
@@ -9659,16 +9662,16 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C245" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E245" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F245" t="s">
         <v>42</v>
@@ -9685,13 +9688,13 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C246" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D246" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F246" t="s">
         <v>24</v>
@@ -9708,13 +9711,13 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C247" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D247" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F247" t="s">
         <v>42</v>
@@ -9731,16 +9734,16 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C248" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D248" t="s">
         <v>12</v>
       </c>
       <c r="E248" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F248" t="s">
         <v>13</v>
@@ -9757,16 +9760,16 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C249" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D249" t="s">
         <v>12</v>
       </c>
       <c r="F249" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G249" t="s">
         <v>14</v>
@@ -9780,10 +9783,10 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C250" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D250" t="s">
         <v>12</v>
@@ -9803,13 +9806,13 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C251" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D251" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F251" t="s">
         <v>13</v>
@@ -9826,10 +9829,10 @@
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C252" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D252" t="s">
         <v>146</v>
@@ -9849,13 +9852,13 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C253" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D253" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F253" t="s">
         <v>24</v>
@@ -9872,13 +9875,13 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C254" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D254" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F254" t="s">
         <v>24</v>
@@ -9895,10 +9898,10 @@
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C255" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D255" t="s">
         <v>149</v>
@@ -9918,13 +9921,13 @@
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C256" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D256" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F256" t="s">
         <v>42</v>
@@ -9941,10 +9944,10 @@
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C257" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D257" t="s">
         <v>36</v>
@@ -9964,10 +9967,10 @@
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C258" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D258" t="s">
         <v>36</v>
@@ -9987,10 +9990,10 @@
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C259" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D259" t="s">
         <v>36</v>
@@ -10010,10 +10013,10 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C260" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D260" t="s">
         <v>36</v>
@@ -10033,10 +10036,10 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C261" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D261" t="s">
         <v>36</v>
@@ -10056,10 +10059,10 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C262" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D262" t="s">
         <v>98</v>
@@ -10079,13 +10082,13 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C263" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D263" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F263" t="s">
         <v>22</v>
@@ -10102,13 +10105,13 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C264" t="s">
+        <v>549</v>
+      </c>
+      <c r="D264" t="s">
         <v>548</v>
-      </c>
-      <c r="D264" t="s">
-        <v>547</v>
       </c>
       <c r="F264" t="s">
         <v>24</v>
@@ -10125,13 +10128,13 @@
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C265" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D265" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F265" t="s">
         <v>13</v>
@@ -10148,10 +10151,10 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C266" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D266" t="s">
         <v>12</v>
@@ -10171,16 +10174,16 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C267" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D267" t="s">
         <v>12</v>
       </c>
       <c r="F267" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G267" t="s">
         <v>14</v>
@@ -10194,10 +10197,10 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C268" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D268" t="s">
         <v>29</v>
@@ -10217,13 +10220,13 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C269" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D269" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F269" t="s">
         <v>22</v>
@@ -10240,13 +10243,13 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C270" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D270" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F270" t="s">
         <v>24</v>
@@ -10263,16 +10266,16 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B271" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C271" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D271" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F271" t="s">
         <v>18</v>
@@ -10289,16 +10292,16 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
+        <v>563</v>
+      </c>
+      <c r="B272" t="s">
         <v>562</v>
       </c>
-      <c r="B272" t="s">
-        <v>561</v>
-      </c>
       <c r="C272" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D272" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F272" t="s">
         <v>19</v>
@@ -10315,19 +10318,19 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B273" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C273" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D273" t="s">
         <v>208</v>
       </c>
       <c r="E273" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F273" t="s">
         <v>123</v>
@@ -10344,19 +10347,19 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B274" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C274" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D274" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E274" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F274" t="s">
         <v>18</v>
@@ -10373,16 +10376,16 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B275" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C275" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D275" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F275" t="s">
         <v>123</v>
@@ -10399,16 +10402,16 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B276" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C276" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D276" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F276" t="s">
         <v>18</v>
@@ -10425,16 +10428,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C277" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D277" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F277" t="s">
         <v>18</v>
@@ -10451,16 +10454,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B278" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C278" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D278" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F278" t="s">
         <v>30</v>
@@ -10477,16 +10480,16 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
+        <v>563</v>
+      </c>
+      <c r="B279" t="s">
         <v>562</v>
       </c>
-      <c r="B279" t="s">
-        <v>561</v>
-      </c>
       <c r="C279" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D279" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F279" t="s">
         <v>31</v>
@@ -10503,16 +10506,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B280" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C280" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D280" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F280" t="s">
         <v>123</v>
@@ -10529,16 +10532,16 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B281" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C281" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D281" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F281" t="s">
         <v>123</v>
@@ -10555,19 +10558,19 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B282" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C282" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D282" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E282" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F282" t="s">
         <v>18</v>
@@ -10584,16 +10587,16 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B283" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C283" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D283" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E283" t="s">
         <v>223</v>
@@ -10613,19 +10616,19 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
+        <v>563</v>
+      </c>
+      <c r="B284" t="s">
         <v>562</v>
       </c>
-      <c r="B284" t="s">
-        <v>561</v>
-      </c>
       <c r="C284" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D284" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E284" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F284" t="s">
         <v>30</v>
@@ -10642,19 +10645,19 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
+        <v>563</v>
+      </c>
+      <c r="B285" t="s">
         <v>562</v>
       </c>
-      <c r="B285" t="s">
-        <v>561</v>
-      </c>
       <c r="C285" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D285" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E285" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F285" t="s">
         <v>31</v>
@@ -10671,16 +10674,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
+        <v>563</v>
+      </c>
+      <c r="B286" t="s">
         <v>562</v>
       </c>
-      <c r="B286" t="s">
-        <v>561</v>
-      </c>
       <c r="C286" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D286" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F286" t="s">
         <v>18</v>
@@ -10697,19 +10700,19 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
+        <v>563</v>
+      </c>
+      <c r="B287" t="s">
         <v>562</v>
       </c>
-      <c r="B287" t="s">
-        <v>561</v>
-      </c>
       <c r="C287" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D287" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E287" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F287" t="s">
         <v>18</v>
@@ -10726,19 +10729,19 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
+        <v>563</v>
+      </c>
+      <c r="B288" t="s">
         <v>562</v>
       </c>
-      <c r="B288" t="s">
-        <v>561</v>
-      </c>
       <c r="C288" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D288" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E288" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F288" t="s">
         <v>19</v>
@@ -10755,16 +10758,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
+        <v>563</v>
+      </c>
+      <c r="B289" t="s">
         <v>562</v>
       </c>
-      <c r="B289" t="s">
-        <v>561</v>
-      </c>
       <c r="C289" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D289" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F289" t="s">
         <v>30</v>
@@ -10781,16 +10784,16 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
+        <v>563</v>
+      </c>
+      <c r="B290" t="s">
         <v>562</v>
       </c>
-      <c r="B290" t="s">
-        <v>561</v>
-      </c>
       <c r="C290" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D290" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -10807,19 +10810,19 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
+        <v>563</v>
+      </c>
+      <c r="B291" t="s">
         <v>562</v>
       </c>
-      <c r="B291" t="s">
-        <v>561</v>
-      </c>
       <c r="C291" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D291" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E291" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F291" t="s">
         <v>13</v>
@@ -10836,16 +10839,16 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
+        <v>563</v>
+      </c>
+      <c r="B292" t="s">
         <v>562</v>
       </c>
-      <c r="B292" t="s">
-        <v>561</v>
-      </c>
       <c r="C292" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D292" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F292" t="s">
         <v>18</v>
@@ -10862,13 +10865,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
+        <v>563</v>
+      </c>
+      <c r="B293" t="s">
         <v>562</v>
       </c>
-      <c r="B293" t="s">
-        <v>561</v>
-      </c>
       <c r="C293" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D293" t="s">
         <v>441</v>
@@ -10888,13 +10891,13 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
+        <v>563</v>
+      </c>
+      <c r="B294" t="s">
         <v>562</v>
       </c>
-      <c r="B294" t="s">
-        <v>561</v>
-      </c>
       <c r="C294" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D294" t="s">
         <v>98</v>
@@ -10914,16 +10917,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
+        <v>563</v>
+      </c>
+      <c r="B295" t="s">
         <v>562</v>
       </c>
-      <c r="B295" t="s">
-        <v>561</v>
-      </c>
       <c r="C295" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D295" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F295" t="s">
         <v>13</v>
@@ -10940,16 +10943,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
+        <v>563</v>
+      </c>
+      <c r="B296" t="s">
         <v>562</v>
       </c>
-      <c r="B296" t="s">
-        <v>561</v>
-      </c>
       <c r="C296" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D296" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F296" t="s">
         <v>13</v>
@@ -10966,16 +10969,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
+        <v>563</v>
+      </c>
+      <c r="B297" t="s">
         <v>562</v>
       </c>
-      <c r="B297" t="s">
-        <v>561</v>
-      </c>
       <c r="C297" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D297" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F297" t="s">
         <v>447</v>
@@ -10992,16 +10995,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
+        <v>563</v>
+      </c>
+      <c r="B298" t="s">
         <v>562</v>
       </c>
-      <c r="B298" t="s">
-        <v>561</v>
-      </c>
       <c r="C298" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D298" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F298" t="s">
         <v>447</v>
@@ -11018,16 +11021,16 @@
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
+        <v>563</v>
+      </c>
+      <c r="B299" t="s">
         <v>562</v>
       </c>
-      <c r="B299" t="s">
-        <v>561</v>
-      </c>
       <c r="C299" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D299" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F299" t="s">
         <v>13</v>
@@ -11044,19 +11047,19 @@
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
+        <v>563</v>
+      </c>
+      <c r="B300" t="s">
         <v>562</v>
       </c>
-      <c r="B300" t="s">
-        <v>561</v>
-      </c>
       <c r="C300" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D300" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E300" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F300" t="s">
         <v>13</v>
@@ -11073,13 +11076,13 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C301" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D301" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F301" t="s">
         <v>13</v>
@@ -11096,16 +11099,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C302" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D302" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F302" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G302" t="s">
         <v>14</v>
@@ -11119,16 +11122,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C303" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D303" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F303" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G303" t="s">
         <v>14</v>
@@ -11142,13 +11145,13 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C304" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D304" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F304" t="s">
         <v>42</v>
@@ -11165,10 +11168,10 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C305" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D305" t="s">
         <v>34</v>
@@ -11188,13 +11191,13 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C306" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D306" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F306" t="s">
         <v>13</v>
@@ -11211,10 +11214,10 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C307" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D307" t="s">
         <v>223</v>
@@ -11234,13 +11237,13 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C308" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D308" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F308" t="s">
         <v>24</v>
@@ -11257,10 +11260,10 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C309" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D309" t="s">
         <v>303</v>
@@ -11280,13 +11283,13 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C310" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D310" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F310" t="s">
         <v>18</v>
@@ -11303,13 +11306,13 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C311" t="s">
+        <v>639</v>
+      </c>
+      <c r="D311" t="s">
         <v>638</v>
-      </c>
-      <c r="D311" t="s">
-        <v>637</v>
       </c>
       <c r="F311" t="s">
         <v>13</v>
@@ -11326,10 +11329,10 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C312" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D312" t="s">
         <v>345</v>
@@ -11349,16 +11352,16 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C313" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D313" t="s">
         <v>345</v>
       </c>
       <c r="F313" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G313" t="s">
         <v>14</v>
@@ -11372,10 +11375,10 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C314" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D314" t="s">
         <v>12</v>
@@ -11395,10 +11398,10 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C315" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D315" t="s">
         <v>351</v>
@@ -11418,10 +11421,10 @@
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C316" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D316" t="s">
         <v>128</v>
@@ -11441,16 +11444,16 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C317" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D317" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F317" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G317" t="s">
         <v>14</v>
@@ -11464,16 +11467,16 @@
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B318" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C318" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D318" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F318" t="s">
         <v>13</v>
@@ -11490,19 +11493,19 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B319" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C319" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D319" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E319" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F319" t="s">
         <v>361</v>
@@ -11519,16 +11522,16 @@
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C320" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D320" t="s">
         <v>208</v>
       </c>
       <c r="F320" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G320" t="s">
         <v>14</v>
@@ -11542,16 +11545,16 @@
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C321" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D321" t="s">
         <v>208</v>
       </c>
       <c r="F321" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G321" t="s">
         <v>14</v>
@@ -11565,10 +11568,10 @@
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C322" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D322" t="s">
         <v>208</v>
@@ -11588,10 +11591,10 @@
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C323" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D323" t="s">
         <v>12</v>
@@ -11611,10 +11614,10 @@
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C324" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D324" t="s">
         <v>12</v>
@@ -11634,10 +11637,10 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C325" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D325" t="s">
         <v>12</v>
@@ -11657,10 +11660,10 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C326" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D326" t="s">
         <v>12</v>
@@ -11680,10 +11683,10 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C327" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D327" t="s">
         <v>98</v>
@@ -11703,16 +11706,16 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C328" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D328" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E328" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F328" t="s">
         <v>13</v>
@@ -11729,13 +11732,13 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C329" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D329" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F329" t="s">
         <v>13</v>
@@ -11752,10 +11755,10 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C330" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D330" t="s">
         <v>303</v>
@@ -11775,13 +11778,13 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C331" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D331" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F331" t="s">
         <v>22</v>
@@ -11798,13 +11801,13 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C332" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D332" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F332" t="s">
         <v>202</v>
@@ -11821,10 +11824,10 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C333" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D333" t="s">
         <v>98</v>
@@ -11844,19 +11847,19 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C334" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D334" t="s">
         <v>98</v>
       </c>
       <c r="E334" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F334" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G334" t="s">
         <v>14</v>
@@ -11870,16 +11873,16 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C335" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D335" t="s">
         <v>487</v>
       </c>
       <c r="E335" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F335" t="s">
         <v>13</v>
@@ -11896,13 +11899,13 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C336" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D336" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F336" t="s">
         <v>18</v>
@@ -11919,13 +11922,13 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C337" t="s">
+        <v>692</v>
+      </c>
+      <c r="D337" t="s">
         <v>691</v>
-      </c>
-      <c r="D337" t="s">
-        <v>690</v>
       </c>
       <c r="F337" t="s">
         <v>13</v>
@@ -11942,16 +11945,16 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D338" t="s">
         <v>12</v>
       </c>
       <c r="F338" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G338" t="s">
         <v>14</v>
@@ -11965,13 +11968,13 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C339" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D339" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F339" t="s">
         <v>246</v>
@@ -11988,13 +11991,13 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C340" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D340" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F340" t="s">
         <v>60</v>
@@ -12011,13 +12014,13 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C341" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D341" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F341" t="s">
         <v>19</v>
@@ -12034,16 +12037,16 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C342" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D342" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F342" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G342" t="s">
         <v>14</v>
@@ -12057,13 +12060,13 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C343" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D343" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F343" t="s">
         <v>123</v>
@@ -12080,13 +12083,13 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C344" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D344" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F344" t="s">
         <v>246</v>
@@ -12103,10 +12106,10 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C345" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D345" t="s">
         <v>29</v>
@@ -12126,16 +12129,16 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C346" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D346" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F346" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G346" t="s">
         <v>14</v>
@@ -12149,16 +12152,16 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C347" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D347" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F347" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G347" t="s">
         <v>14</v>
@@ -12172,10 +12175,10 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C348" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D348" t="s">
         <v>12</v>
@@ -12195,10 +12198,10 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C349" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D349" t="s">
         <v>39</v>
@@ -12218,10 +12221,10 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C350" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D350" t="s">
         <v>12</v>
@@ -12241,16 +12244,16 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C351" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D351" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E351" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F351" t="s">
         <v>35</v>
@@ -12267,10 +12270,10 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C352" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D352" t="s">
         <v>12</v>
@@ -12290,13 +12293,13 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C353" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D353" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F353" t="s">
         <v>13</v>
@@ -12313,13 +12316,13 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C354" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D354" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F354" t="s">
         <v>19</v>
@@ -12336,16 +12339,16 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C355" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D355" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E355" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F355" t="s">
         <v>42</v>
@@ -12362,16 +12365,16 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C356" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D356" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F356" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G356" t="s">
         <v>14</v>
@@ -12385,10 +12388,10 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C357" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D357" t="s">
         <v>34</v>
@@ -12408,13 +12411,13 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C358" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D358" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F358" t="s">
         <v>22</v>
@@ -12431,16 +12434,16 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C359" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D359" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F359" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G359" t="s">
         <v>14</v>
@@ -12454,10 +12457,10 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C360" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D360" t="s">
         <v>12</v>
@@ -12477,13 +12480,13 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C361" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D361" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F361" t="s">
         <v>13</v>
@@ -12500,10 +12503,10 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C362" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D362" t="s">
         <v>12</v>
@@ -12523,10 +12526,10 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C363" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D363" t="s">
         <v>29</v>
@@ -12546,16 +12549,16 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C364" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D364" t="s">
         <v>149</v>
       </c>
       <c r="F364" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G364" t="s">
         <v>14</v>
@@ -12569,16 +12572,16 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C365" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D365" t="s">
         <v>190</v>
       </c>
       <c r="F365" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G365" t="s">
         <v>14</v>
@@ -12592,10 +12595,10 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C366" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D366" t="s">
         <v>98</v>
@@ -12615,10 +12618,10 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C367" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D367" t="s">
         <v>98</v>
@@ -12638,10 +12641,10 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C368" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D368" t="s">
         <v>12</v>
@@ -12661,10 +12664,10 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C369" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D369" t="s">
         <v>12</v>
@@ -12684,10 +12687,10 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C370" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D370" t="s">
         <v>12</v>
@@ -12707,10 +12710,10 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C371" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D371" t="s">
         <v>98</v>
@@ -12733,13 +12736,13 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C372" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D372" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F372" t="s">
         <v>35</v>
@@ -12756,13 +12759,13 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B373" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C373" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D373" t="s">
         <v>98</v>
@@ -12782,16 +12785,16 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C374" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D374" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F374" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G374" t="s">
         <v>14</v>
@@ -12805,13 +12808,13 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C375" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D375" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F375" t="s">
         <v>60</v>
@@ -12828,13 +12831,13 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C376" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D376" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F376" t="s">
         <v>18</v>
@@ -12851,13 +12854,13 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C377" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D377" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F377" t="s">
         <v>19</v>
@@ -12874,16 +12877,16 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C378" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D378" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F378" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G378" t="s">
         <v>14</v>
@@ -12897,13 +12900,13 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C379" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D379" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F379" t="s">
         <v>22</v>
@@ -12920,13 +12923,13 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C380" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D380" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F380" t="s">
         <v>24</v>
@@ -12943,13 +12946,13 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C381" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D381" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F381" t="s">
         <v>13</v>
@@ -12966,10 +12969,10 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C382" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D382" t="s">
         <v>29</v>
@@ -12989,16 +12992,16 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C383" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D383" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E383" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F383" t="s">
         <v>13</v>
@@ -13015,16 +13018,16 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C384" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D384" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E384" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F384" t="s">
         <v>18</v>
@@ -13041,13 +13044,13 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C385" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D385" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F385" t="s">
         <v>13</v>
@@ -13064,13 +13067,13 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C386" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F386" t="s">
         <v>13</v>
@@ -13087,13 +13090,13 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C387" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D387" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F387" t="s">
         <v>35</v>
@@ -13110,13 +13113,13 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C388" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D388" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F388" t="s">
         <v>35</v>
@@ -13133,10 +13136,10 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C389" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D389" t="s">
         <v>12</v>
@@ -13156,10 +13159,10 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C390" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D390" t="s">
         <v>98</v>
@@ -13179,13 +13182,13 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C391" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D391" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F391" t="s">
         <v>13</v>
@@ -13202,13 +13205,13 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C392" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D392" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F392" t="s">
         <v>361</v>
@@ -13225,13 +13228,13 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C393" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D393" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F393" t="s">
         <v>35</v>
@@ -13248,16 +13251,16 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C394" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D394" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E394" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F394" t="s">
         <v>35</v>
@@ -13274,13 +13277,13 @@
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C395" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D395" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F395" t="s">
         <v>35</v>
@@ -13297,16 +13300,16 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C396" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D396" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F396" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G396" t="s">
         <v>14</v>
@@ -13320,10 +13323,10 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C397" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D397" t="s">
         <v>128</v>
@@ -13343,16 +13346,16 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C398" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D398" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F398" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G398" t="s">
         <v>14</v>
@@ -13366,16 +13369,16 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C399" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D399" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E399" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F399" t="s">
         <v>13</v>
@@ -13392,19 +13395,19 @@
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B400" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C400" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D400" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E400" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F400" t="s">
         <v>35</v>
@@ -13421,19 +13424,19 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
+        <v>827</v>
+      </c>
+      <c r="B401" t="s">
         <v>826</v>
       </c>
-      <c r="B401" t="s">
-        <v>825</v>
-      </c>
       <c r="C401" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D401" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E401" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F401" t="s">
         <v>35</v>
@@ -13450,16 +13453,16 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
+        <v>827</v>
+      </c>
+      <c r="B402" t="s">
         <v>826</v>
       </c>
-      <c r="B402" t="s">
-        <v>825</v>
-      </c>
       <c r="C402" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D402" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F402" t="s">
         <v>35</v>
@@ -13476,13 +13479,13 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C403" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D403" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F403" t="s">
         <v>24</v>
@@ -13499,13 +13502,13 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C404" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D404" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F404" t="s">
         <v>13</v>
@@ -13522,13 +13525,13 @@
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C405" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D405" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F405" t="s">
         <v>429</v>
@@ -13545,10 +13548,10 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C406" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D406" t="s">
         <v>201</v>
@@ -13568,10 +13571,10 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C407" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D407" t="s">
         <v>12</v>
@@ -13591,19 +13594,19 @@
     </row>
     <row r="408" spans="1:9">
       <c r="A408" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C408" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D408" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E408" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F408" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G408" t="s">
         <v>14</v>
@@ -13617,10 +13620,10 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C409" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D409" t="s">
         <v>98</v>
@@ -13640,10 +13643,10 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C410" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D410" t="s">
         <v>98</v>
@@ -13663,10 +13666,10 @@
     </row>
     <row r="411" spans="1:9">
       <c r="A411" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C411" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D411" t="s">
         <v>12</v>
@@ -13686,10 +13689,10 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C412" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D412" t="s">
         <v>34</v>
@@ -13709,10 +13712,10 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C413" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D413" t="s">
         <v>34</v>
@@ -13732,10 +13735,10 @@
     </row>
     <row r="414" spans="1:9">
       <c r="A414" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C414" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D414" t="s">
         <v>12</v>
@@ -13755,13 +13758,13 @@
     </row>
     <row r="415" spans="1:9">
       <c r="A415" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C415" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D415" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F415" t="s">
         <v>13</v>
@@ -13778,10 +13781,10 @@
     </row>
     <row r="416" spans="1:9">
       <c r="A416" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C416" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D416" t="s">
         <v>98</v>
@@ -13801,13 +13804,13 @@
     </row>
     <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C417" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D417" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F417" t="s">
         <v>24</v>
@@ -13824,13 +13827,13 @@
     </row>
     <row r="418" spans="1:9">
       <c r="A418" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C418" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D418" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F418" t="s">
         <v>13</v>
@@ -13847,13 +13850,13 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C419" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D419" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F419" t="s">
         <v>18</v>
@@ -13870,13 +13873,13 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C420" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D420" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F420" t="s">
         <v>22</v>
@@ -13893,16 +13896,16 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C421" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D421" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E421" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F421" t="s">
         <v>19</v>
@@ -13919,13 +13922,13 @@
     </row>
     <row r="422" spans="1:9">
       <c r="A422" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C422" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D422" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F422" t="s">
         <v>24</v>
@@ -13942,16 +13945,16 @@
     </row>
     <row r="423" spans="1:9">
       <c r="A423" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C423" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D423" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E423" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F423" t="s">
         <v>24</v>
@@ -13968,13 +13971,13 @@
     </row>
     <row r="424" spans="1:9">
       <c r="A424" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C424" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D424" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F424" t="s">
         <v>13</v>
@@ -13991,10 +13994,10 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C425" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D425" t="s">
         <v>12</v>
@@ -14014,16 +14017,16 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C426" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D426" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F426" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G426" t="s">
         <v>14</v>
@@ -14037,13 +14040,13 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C427" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D427" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F427" t="s">
         <v>13</v>
@@ -14060,13 +14063,13 @@
     </row>
     <row r="428" spans="1:9">
       <c r="A428" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C428" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D428" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F428" t="s">
         <v>138</v>
@@ -14083,16 +14086,16 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C429" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D429" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E429" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F429" t="s">
         <v>138</v>
@@ -14109,16 +14112,16 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C430" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D430" t="s">
         <v>257</v>
       </c>
       <c r="E430" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F430" t="s">
         <v>138</v>
@@ -14135,10 +14138,10 @@
     </row>
     <row r="431" spans="1:9">
       <c r="A431" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C431" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D431" t="s">
         <v>257</v>
@@ -14158,10 +14161,10 @@
     </row>
     <row r="432" spans="1:9">
       <c r="A432" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C432" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D432" t="s">
         <v>257</v>
@@ -14181,13 +14184,13 @@
     </row>
     <row r="433" spans="1:9">
       <c r="A433" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C433" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D433" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F433" t="s">
         <v>246</v>
@@ -14204,13 +14207,13 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C434" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D434" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F434" t="s">
         <v>246</v>
@@ -14227,10 +14230,10 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C435" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D435" t="s">
         <v>12</v>
@@ -14250,10 +14253,10 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C436" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D436" t="s">
         <v>29</v>
@@ -14273,10 +14276,10 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C437" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D437" t="s">
         <v>29</v>
@@ -14296,10 +14299,10 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C438" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D438" t="s">
         <v>29</v>
@@ -14319,13 +14322,13 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C439" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D439" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F439" t="s">
         <v>186</v>
@@ -14342,10 +14345,10 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C440" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D440" t="s">
         <v>12</v>
@@ -14365,10 +14368,10 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C441" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D441" t="s">
         <v>12</v>
@@ -14388,10 +14391,10 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C442" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D442" t="s">
         <v>12</v>
@@ -14411,13 +14414,13 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C443" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D443" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F443" t="s">
         <v>24</v>
@@ -14434,13 +14437,13 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C444" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D444" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F444" t="s">
         <v>18</v>
@@ -14457,13 +14460,13 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C445" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D445" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F445" t="s">
         <v>19</v>
@@ -14480,16 +14483,16 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C446" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D446" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F446" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G446" t="s">
         <v>14</v>
@@ -14503,13 +14506,13 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C447" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D447" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F447" t="s">
         <v>202</v>
@@ -14526,16 +14529,16 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C448" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D448" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F448" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G448" t="s">
         <v>14</v>
@@ -14549,16 +14552,16 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C449" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D449" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F449" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G449" t="s">
         <v>14</v>
@@ -14572,13 +14575,13 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C450" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D450" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F450" t="s">
         <v>19</v>
@@ -14595,13 +14598,13 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C451" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D451" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F451" t="s">
         <v>22</v>
@@ -14618,13 +14621,13 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C452" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D452" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F452" t="s">
         <v>202</v>
@@ -14641,13 +14644,13 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C453" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D453" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F453" t="s">
         <v>35</v>
@@ -14664,10 +14667,10 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C454" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D454" t="s">
         <v>39</v>
@@ -14687,10 +14690,10 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C455" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D455" t="s">
         <v>39</v>
@@ -14710,16 +14713,16 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C456" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D456" t="s">
         <v>39</v>
       </c>
       <c r="F456" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G456" t="s">
         <v>14</v>
@@ -14733,16 +14736,16 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B457" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C457" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D457" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F457" t="s">
         <v>18</v>
@@ -14759,16 +14762,16 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B458" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C458" t="s">
+        <v>947</v>
+      </c>
+      <c r="D458" t="s">
         <v>946</v>
-      </c>
-      <c r="D458" t="s">
-        <v>945</v>
       </c>
       <c r="F458" t="s">
         <v>123</v>
@@ -14785,16 +14788,16 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B459" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C459" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D459" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F459" t="s">
         <v>13</v>
@@ -14811,16 +14814,16 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B460" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C460" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D460" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F460" t="s">
         <v>447</v>
@@ -14837,10 +14840,10 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C461" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D461" t="s">
         <v>102</v>
@@ -14860,16 +14863,16 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C462" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D462" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E462" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F462" t="s">
         <v>13</v>
@@ -14886,10 +14889,10 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C463" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D463" t="s">
         <v>12</v>
@@ -14909,10 +14912,10 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C464" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D464" t="s">
         <v>149</v>
@@ -14932,7 +14935,7 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C465" t="s">
         <v>276</v>
@@ -14955,7 +14958,7 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C466" t="s">
         <v>276</v>
@@ -14964,7 +14967,7 @@
         <v>223</v>
       </c>
       <c r="F466" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G466" t="s">
         <v>14</v>
@@ -14978,7 +14981,7 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C467" t="s">
         <v>276</v>
@@ -14987,7 +14990,7 @@
         <v>223</v>
       </c>
       <c r="F467" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G467" t="s">
         <v>14</v>
@@ -15001,16 +15004,16 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C468" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D468" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F468" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G468" t="s">
         <v>14</v>
@@ -15024,13 +15027,13 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C469" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D469" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F469" t="s">
         <v>326</v>
@@ -15047,16 +15050,16 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C470" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F470" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G470" t="s">
         <v>14</v>
@@ -15070,16 +15073,16 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C471" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D471" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F471" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G471" t="s">
         <v>14</v>
@@ -15093,10 +15096,10 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C472" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D472" t="s">
         <v>98</v>
@@ -15116,16 +15119,16 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C473" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D473" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F473" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
@@ -15139,16 +15142,16 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B474" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C474" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D474" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F474" t="s">
         <v>22</v>
@@ -15165,16 +15168,16 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B475" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C475" t="s">
+        <v>982</v>
+      </c>
+      <c r="D475" t="s">
         <v>981</v>
-      </c>
-      <c r="D475" t="s">
-        <v>980</v>
       </c>
       <c r="F475" t="s">
         <v>30</v>
@@ -15191,10 +15194,10 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C476" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D476" t="s">
         <v>208</v>
@@ -15214,10 +15217,10 @@
     </row>
     <row r="477" spans="1:9">
       <c r="A477" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C477" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D477" t="s">
         <v>216</v>
@@ -15237,10 +15240,10 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C478" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D478" t="s">
         <v>216</v>
@@ -15260,13 +15263,13 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C479" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D479" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F479" t="s">
         <v>24</v>
@@ -15283,16 +15286,16 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B480" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C480" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D480" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F480" t="s">
         <v>22</v>
@@ -15309,10 +15312,10 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C481" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D481" t="s">
         <v>98</v>
@@ -15332,10 +15335,10 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C482" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D482" t="s">
         <v>39</v>
@@ -15355,10 +15358,10 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C483" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D483" t="s">
         <v>39</v>
@@ -15378,10 +15381,10 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C484" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D484" t="s">
         <v>39</v>
@@ -15401,10 +15404,10 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C485" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D485" t="s">
         <v>12</v>
@@ -15424,13 +15427,13 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C486" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D486" t="s">
-        <v>1003</v>
+        <v>488</v>
       </c>
       <c r="F486" t="s">
         <v>138</v>
@@ -15545,7 +15548,7 @@
         <v>1016</v>
       </c>
       <c r="D491" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F491" t="s">
         <v>35</v>
@@ -15568,7 +15571,7 @@
         <v>1016</v>
       </c>
       <c r="D492" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F492" t="s">
         <v>35</v>
@@ -15994,7 +15997,7 @@
         <v>159</v>
       </c>
       <c r="D510" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E510" t="s">
         <v>173</v>
@@ -16616,7 +16619,7 @@
         <v>12</v>
       </c>
       <c r="F536" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G536" t="s">
         <v>14</v>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3506" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="1138">
   <si>
     <t>Fornitore</t>
   </si>
@@ -3080,6 +3080,15 @@
   </si>
   <si>
     <t>FSE-2.0</t>
+  </si>
+  <si>
+    <t>SOUTHMEDICALIMPORT</t>
+  </si>
+  <si>
+    <t>Refertazio</t>
+  </si>
+  <si>
+    <t>V1.2</t>
   </si>
   <si>
     <t>SPE.IT s.r.l.</t>
@@ -3750,7 +3759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I553"/>
+  <dimension ref="A1:I555"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -15695,16 +15704,16 @@
         <v>1023</v>
       </c>
       <c r="D497" t="s">
-        <v>12</v>
+        <v>1024</v>
       </c>
       <c r="F497" t="s">
-        <v>187</v>
+        <v>24</v>
       </c>
       <c r="G497" t="s">
         <v>14</v>
       </c>
       <c r="H497">
-        <v>45190</v>
+        <v>46097</v>
       </c>
       <c r="I497" t="s">
         <v>12</v>
@@ -15712,22 +15721,22 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C498" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D498" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F498" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G498" t="s">
         <v>14</v>
       </c>
       <c r="H498">
-        <v>45565</v>
+        <v>45190</v>
       </c>
       <c r="I498" t="s">
         <v>12</v>
@@ -15735,22 +15744,22 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C499" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D499" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="F499" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G499" t="s">
         <v>14</v>
       </c>
       <c r="H499">
-        <v>46000</v>
+        <v>45565</v>
       </c>
       <c r="I499" t="s">
         <v>12</v>
@@ -15758,22 +15767,22 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C500" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D500" t="s">
         <v>208</v>
       </c>
       <c r="F500" t="s">
-        <v>1028</v>
+        <v>202</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
       </c>
       <c r="H500">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="I500" t="s">
         <v>12</v>
@@ -15787,16 +15796,16 @@
         <v>1030</v>
       </c>
       <c r="D501" t="s">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="F501" t="s">
-        <v>35</v>
+        <v>1031</v>
       </c>
       <c r="G501" t="s">
         <v>14</v>
       </c>
       <c r="H501">
-        <v>46059</v>
+        <v>46044</v>
       </c>
       <c r="I501" t="s">
         <v>12</v>
@@ -15804,22 +15813,22 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C502" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D502" t="s">
-        <v>1033</v>
+        <v>12</v>
       </c>
       <c r="F502" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
       </c>
       <c r="H502">
-        <v>45083</v>
+        <v>46059</v>
       </c>
       <c r="I502" t="s">
         <v>12</v>
@@ -15833,16 +15842,16 @@
         <v>1035</v>
       </c>
       <c r="D503" t="s">
-        <v>372</v>
+        <v>1036</v>
       </c>
       <c r="F503" t="s">
-        <v>246</v>
+        <v>42</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
       </c>
       <c r="H503">
-        <v>45593</v>
+        <v>45083</v>
       </c>
       <c r="I503" t="s">
         <v>12</v>
@@ -15850,22 +15859,22 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C504" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D504" t="s">
-        <v>1038</v>
+        <v>372</v>
       </c>
       <c r="F504" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="G504" t="s">
         <v>14</v>
       </c>
       <c r="H504">
-        <v>46006</v>
+        <v>45593</v>
       </c>
       <c r="I504" t="s">
         <v>12</v>
@@ -15882,13 +15891,13 @@
         <v>1041</v>
       </c>
       <c r="F505" t="s">
-        <v>1042</v>
+        <v>22</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
       </c>
       <c r="H505">
-        <v>45573</v>
+        <v>46006</v>
       </c>
       <c r="I505" t="s">
         <v>12</v>
@@ -15896,22 +15905,22 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C506" t="s">
         <v>1043</v>
       </c>
-      <c r="C506" t="s">
+      <c r="D506" t="s">
         <v>1044</v>
       </c>
-      <c r="D506" t="s">
-        <v>98</v>
-      </c>
       <c r="F506" t="s">
-        <v>42</v>
+        <v>1045</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
       </c>
       <c r="H506">
-        <v>46080</v>
+        <v>45573</v>
       </c>
       <c r="I506" t="s">
         <v>12</v>
@@ -15919,22 +15928,22 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C507" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D507" t="s">
-        <v>1047</v>
+        <v>98</v>
       </c>
       <c r="F507" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G507" t="s">
         <v>14</v>
       </c>
       <c r="H507">
-        <v>45049</v>
+        <v>46080</v>
       </c>
       <c r="I507" t="s">
         <v>12</v>
@@ -15942,22 +15951,22 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C508" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D508" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="F508" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G508" t="s">
         <v>14</v>
       </c>
       <c r="H508">
-        <v>45114</v>
+        <v>45049</v>
       </c>
       <c r="I508" t="s">
         <v>12</v>
@@ -15965,25 +15974,22 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C509" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D509" t="s">
         <v>1050</v>
       </c>
-      <c r="D509" t="s">
-        <v>285</v>
-      </c>
-      <c r="E509" t="s">
-        <v>1051</v>
-      </c>
       <c r="F509" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G509" t="s">
         <v>14</v>
       </c>
       <c r="H509">
-        <v>45727</v>
+        <v>45114</v>
       </c>
       <c r="I509" t="s">
         <v>12</v>
@@ -15991,25 +15997,25 @@
     </row>
     <row r="510" spans="1:9">
       <c r="A510" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C510" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D510" t="s">
-        <v>1053</v>
+        <v>285</v>
       </c>
       <c r="E510" t="s">
         <v>1054</v>
       </c>
       <c r="F510" t="s">
-        <v>1055</v>
+        <v>22</v>
       </c>
       <c r="G510" t="s">
         <v>14</v>
       </c>
       <c r="H510">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="I510" t="s">
         <v>12</v>
@@ -16017,25 +16023,25 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C511" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D511" t="s">
         <v>1056</v>
-      </c>
-      <c r="D511" t="s">
-        <v>146</v>
       </c>
       <c r="E511" t="s">
         <v>1057</v>
       </c>
       <c r="F511" t="s">
-        <v>60</v>
+        <v>1058</v>
       </c>
       <c r="G511" t="s">
         <v>14</v>
       </c>
       <c r="H511">
-        <v>45747</v>
+        <v>45797</v>
       </c>
       <c r="I511" t="s">
         <v>12</v>
@@ -16043,25 +16049,25 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C512" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D512" t="s">
         <v>146</v>
       </c>
       <c r="E512" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F512" t="s">
-        <v>1058</v>
+        <v>60</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
       </c>
       <c r="H512">
-        <v>45813</v>
+        <v>45747</v>
       </c>
       <c r="I512" t="s">
         <v>12</v>
@@ -16069,25 +16075,25 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C513" t="s">
-        <v>159</v>
+        <v>1059</v>
       </c>
       <c r="D513" t="s">
-        <v>590</v>
+        <v>146</v>
       </c>
       <c r="E513" t="s">
-        <v>173</v>
+        <v>1060</v>
       </c>
       <c r="F513" t="s">
-        <v>22</v>
+        <v>1061</v>
       </c>
       <c r="G513" t="s">
         <v>14</v>
       </c>
       <c r="H513">
-        <v>45043</v>
+        <v>45813</v>
       </c>
       <c r="I513" t="s">
         <v>12</v>
@@ -16095,16 +16101,16 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C514" t="s">
-        <v>1059</v>
+        <v>159</v>
       </c>
       <c r="D514" t="s">
-        <v>98</v>
+        <v>590</v>
       </c>
       <c r="E514" t="s">
-        <v>1060</v>
+        <v>173</v>
       </c>
       <c r="F514" t="s">
         <v>22</v>
@@ -16121,25 +16127,25 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C515" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D515" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="E515" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F515" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G515" t="s">
         <v>14</v>
       </c>
       <c r="H515">
-        <v>45184</v>
+        <v>45043</v>
       </c>
       <c r="I515" t="s">
         <v>12</v>
@@ -16147,16 +16153,16 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C516" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D516" t="s">
         <v>208</v>
       </c>
       <c r="E516" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="F516" t="s">
         <v>13</v>
@@ -16165,7 +16171,7 @@
         <v>14</v>
       </c>
       <c r="H516">
-        <v>45219</v>
+        <v>45184</v>
       </c>
       <c r="I516" t="s">
         <v>12</v>
@@ -16173,16 +16179,16 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C517" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D517" t="s">
+        <v>208</v>
+      </c>
+      <c r="E517" t="s">
         <v>1065</v>
-      </c>
-      <c r="E517" t="s">
-        <v>1066</v>
       </c>
       <c r="F517" t="s">
         <v>13</v>
@@ -16191,7 +16197,7 @@
         <v>14</v>
       </c>
       <c r="H517">
-        <v>45303</v>
+        <v>45219</v>
       </c>
       <c r="I517" t="s">
         <v>12</v>
@@ -16199,7 +16205,7 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C518" t="s">
         <v>1067</v>
@@ -16207,6 +16213,9 @@
       <c r="D518" t="s">
         <v>1068</v>
       </c>
+      <c r="E518" t="s">
+        <v>1069</v>
+      </c>
       <c r="F518" t="s">
         <v>13</v>
       </c>
@@ -16214,7 +16223,7 @@
         <v>14</v>
       </c>
       <c r="H518">
-        <v>45327</v>
+        <v>45303</v>
       </c>
       <c r="I518" t="s">
         <v>12</v>
@@ -16222,16 +16231,13 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C519" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D519" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E519" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="F519" t="s">
         <v>13</v>
@@ -16248,14 +16254,17 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C520" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D520" t="s">
         <v>1068</v>
       </c>
+      <c r="E520" t="s">
+        <v>1069</v>
+      </c>
       <c r="F520" t="s">
         <v>13</v>
       </c>
@@ -16271,16 +16280,13 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C521" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D521" t="s">
         <v>1071</v>
-      </c>
-      <c r="D521" t="s">
-        <v>54</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1072</v>
       </c>
       <c r="F521" t="s">
         <v>13</v>
@@ -16289,7 +16295,7 @@
         <v>14</v>
       </c>
       <c r="H521">
-        <v>45439</v>
+        <v>45327</v>
       </c>
       <c r="I521" t="s">
         <v>12</v>
@@ -16297,22 +16303,25 @@
     </row>
     <row r="522" spans="1:9">
       <c r="A522" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C522" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D522" t="s">
-        <v>329</v>
+        <v>54</v>
+      </c>
+      <c r="E522" t="s">
+        <v>1075</v>
       </c>
       <c r="F522" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
       </c>
       <c r="H522">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="I522" t="s">
         <v>12</v>
@@ -16320,22 +16329,22 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>1074</v>
+        <v>1052</v>
       </c>
       <c r="C523" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D523" t="s">
-        <v>1076</v>
+        <v>329</v>
       </c>
       <c r="F523" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G523" t="s">
         <v>14</v>
       </c>
       <c r="H523">
-        <v>45022</v>
+        <v>45951</v>
       </c>
       <c r="I523" t="s">
         <v>12</v>
@@ -16343,22 +16352,22 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="C524" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D524" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F524" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
       </c>
       <c r="H524">
-        <v>45275</v>
+        <v>45022</v>
       </c>
       <c r="I524" t="s">
         <v>12</v>
@@ -16375,13 +16384,13 @@
         <v>1079</v>
       </c>
       <c r="F525" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G525" t="s">
         <v>14</v>
       </c>
       <c r="H525">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="I525" t="s">
         <v>12</v>
@@ -16395,7 +16404,7 @@
         <v>1081</v>
       </c>
       <c r="D526" t="s">
-        <v>98</v>
+        <v>1082</v>
       </c>
       <c r="F526" t="s">
         <v>13</v>
@@ -16404,7 +16413,7 @@
         <v>14</v>
       </c>
       <c r="H526">
-        <v>45722</v>
+        <v>45792</v>
       </c>
       <c r="I526" t="s">
         <v>12</v>
@@ -16412,22 +16421,22 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C527" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D527" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F527" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
       </c>
       <c r="H527">
-        <v>45107</v>
+        <v>45722</v>
       </c>
       <c r="I527" t="s">
         <v>12</v>
@@ -16435,22 +16444,22 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C528" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D528" t="s">
         <v>12</v>
       </c>
       <c r="F528" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
       </c>
       <c r="H528">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="I528" t="s">
         <v>12</v>
@@ -16458,22 +16467,22 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="C529" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D529" t="s">
         <v>12</v>
       </c>
       <c r="F529" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G529" t="s">
         <v>14</v>
       </c>
       <c r="H529">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="I529" t="s">
         <v>12</v>
@@ -16481,22 +16490,22 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C530" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D530" t="s">
         <v>12</v>
       </c>
       <c r="F530" t="s">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="G530" t="s">
         <v>14</v>
       </c>
       <c r="H530">
-        <v>45141</v>
+        <v>45107</v>
       </c>
       <c r="I530" t="s">
         <v>12</v>
@@ -16504,22 +16513,22 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C531" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D531" t="s">
         <v>12</v>
       </c>
       <c r="F531" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
       </c>
       <c r="H531">
-        <v>45194</v>
+        <v>45141</v>
       </c>
       <c r="I531" t="s">
         <v>12</v>
@@ -16527,22 +16536,22 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C532" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D532" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="F532" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
       </c>
       <c r="H532">
-        <v>45856</v>
+        <v>45194</v>
       </c>
       <c r="I532" t="s">
         <v>12</v>
@@ -16550,16 +16559,16 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C533" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D533" t="s">
         <v>245</v>
       </c>
       <c r="F533" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
@@ -16576,19 +16585,19 @@
         <v>1091</v>
       </c>
       <c r="C534" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D534" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="F534" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
       </c>
       <c r="H534">
-        <v>45392</v>
+        <v>45856</v>
       </c>
       <c r="I534" t="s">
         <v>12</v>
@@ -16596,13 +16605,13 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="C535" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D535" t="s">
-        <v>1093</v>
+        <v>77</v>
       </c>
       <c r="F535" t="s">
         <v>35</v>
@@ -16611,7 +16620,7 @@
         <v>14</v>
       </c>
       <c r="H535">
-        <v>45792</v>
+        <v>45392</v>
       </c>
       <c r="I535" t="s">
         <v>12</v>
@@ -16634,7 +16643,7 @@
         <v>14</v>
       </c>
       <c r="H536">
-        <v>45495</v>
+        <v>45792</v>
       </c>
       <c r="I536" t="s">
         <v>12</v>
@@ -16651,13 +16660,13 @@
         <v>1099</v>
       </c>
       <c r="F537" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G537" t="s">
         <v>14</v>
       </c>
       <c r="H537">
-        <v>45223</v>
+        <v>45495</v>
       </c>
       <c r="I537" t="s">
         <v>12</v>
@@ -16674,13 +16683,13 @@
         <v>1099</v>
       </c>
       <c r="F538" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G538" t="s">
         <v>14</v>
       </c>
       <c r="H538">
-        <v>45254</v>
+        <v>46097</v>
       </c>
       <c r="I538" t="s">
         <v>12</v>
@@ -16694,16 +16703,16 @@
         <v>1101</v>
       </c>
       <c r="D539" t="s">
-        <v>12</v>
+        <v>1102</v>
       </c>
       <c r="F539" t="s">
-        <v>696</v>
+        <v>18</v>
       </c>
       <c r="G539" t="s">
         <v>14</v>
       </c>
       <c r="H539">
-        <v>45807</v>
+        <v>45223</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16711,22 +16720,22 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D540" t="s">
         <v>1102</v>
       </c>
-      <c r="C540" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D540" t="s">
-        <v>12</v>
-      </c>
       <c r="F540" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G540" t="s">
         <v>14</v>
       </c>
       <c r="H540">
-        <v>45849</v>
+        <v>45254</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16734,22 +16743,22 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C541" t="s">
         <v>1104</v>
       </c>
-      <c r="C541" t="s">
-        <v>1105</v>
-      </c>
       <c r="D541" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F541" t="s">
-        <v>13</v>
+        <v>696</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
       </c>
       <c r="H541">
-        <v>46000</v>
+        <v>45807</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16757,13 +16766,13 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C542" t="s">
         <v>1106</v>
       </c>
       <c r="D542" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F542" t="s">
         <v>13</v>
@@ -16772,7 +16781,7 @@
         <v>14</v>
       </c>
       <c r="H542">
-        <v>46010</v>
+        <v>45849</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16786,16 +16795,16 @@
         <v>1108</v>
       </c>
       <c r="D543" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="F543" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G543" t="s">
         <v>14</v>
       </c>
       <c r="H543">
-        <v>45825</v>
+        <v>46000</v>
       </c>
       <c r="I543" t="s">
         <v>12</v>
@@ -16806,19 +16815,19 @@
         <v>1107</v>
       </c>
       <c r="C544" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D544" t="s">
-        <v>1109</v>
+        <v>29</v>
       </c>
       <c r="F544" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
       </c>
       <c r="H544">
-        <v>46078</v>
+        <v>46010</v>
       </c>
       <c r="I544" t="s">
         <v>12</v>
@@ -16832,16 +16841,16 @@
         <v>1111</v>
       </c>
       <c r="D545" t="s">
-        <v>1112</v>
+        <v>98</v>
       </c>
       <c r="F545" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G545" t="s">
         <v>14</v>
       </c>
       <c r="H545">
-        <v>46035</v>
+        <v>45825</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -16849,22 +16858,22 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C546" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D546" t="s">
-        <v>98</v>
+        <v>1112</v>
       </c>
       <c r="F546" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="G546" t="s">
         <v>14</v>
       </c>
       <c r="H546">
-        <v>45985</v>
+        <v>46078</v>
       </c>
       <c r="I546" t="s">
         <v>12</v>
@@ -16872,22 +16881,22 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C547" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D547" t="s">
         <v>1115</v>
       </c>
-      <c r="C547" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D547" t="s">
-        <v>12</v>
-      </c>
       <c r="F547" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G547" t="s">
         <v>14</v>
       </c>
       <c r="H547">
-        <v>45190</v>
+        <v>46035</v>
       </c>
       <c r="I547" t="s">
         <v>12</v>
@@ -16895,22 +16904,22 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C548" t="s">
         <v>1117</v>
       </c>
-      <c r="C548" t="s">
-        <v>1118</v>
-      </c>
       <c r="D548" t="s">
-        <v>1119</v>
+        <v>98</v>
       </c>
       <c r="F548" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G548" t="s">
         <v>14</v>
       </c>
       <c r="H548">
-        <v>45029</v>
+        <v>45985</v>
       </c>
       <c r="I548" t="s">
         <v>12</v>
@@ -16918,25 +16927,22 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C549" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D549" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1123</v>
+        <v>12</v>
       </c>
       <c r="F549" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G549" t="s">
         <v>14</v>
       </c>
       <c r="H549">
-        <v>45376</v>
+        <v>45190</v>
       </c>
       <c r="I549" t="s">
         <v>12</v>
@@ -16944,16 +16950,13 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="C550" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="D550" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="F550" t="s">
         <v>22</v>
@@ -16962,7 +16965,7 @@
         <v>14</v>
       </c>
       <c r="H550">
-        <v>45085</v>
+        <v>45029</v>
       </c>
       <c r="I550" t="s">
         <v>12</v>
@@ -16970,25 +16973,25 @@
     </row>
     <row r="551" spans="1:9">
       <c r="A551" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C551" t="s">
         <v>1124</v>
       </c>
-      <c r="B551" t="s">
+      <c r="D551" t="s">
         <v>1125</v>
       </c>
-      <c r="C551" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1129</v>
+      <c r="E551" t="s">
+        <v>1126</v>
       </c>
       <c r="F551" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G551" t="s">
         <v>14</v>
       </c>
       <c r="H551">
-        <v>45387</v>
+        <v>45376</v>
       </c>
       <c r="I551" t="s">
         <v>12</v>
@@ -16996,25 +16999,25 @@
     </row>
     <row r="552" spans="1:9">
       <c r="A552" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B552" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C552" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D552" t="s">
         <v>1130</v>
       </c>
-      <c r="D552" t="s">
-        <v>1131</v>
-      </c>
       <c r="F552" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G552" t="s">
         <v>14</v>
       </c>
       <c r="H552">
-        <v>45764</v>
+        <v>45085</v>
       </c>
       <c r="I552" t="s">
         <v>12</v>
@@ -17022,24 +17025,76 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C553" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D553" t="s">
         <v>1132</v>
       </c>
-      <c r="C553" t="s">
+      <c r="F553" t="s">
+        <v>22</v>
+      </c>
+      <c r="G553" t="s">
+        <v>14</v>
+      </c>
+      <c r="H553">
+        <v>45387</v>
+      </c>
+      <c r="I553" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9">
+      <c r="A554" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C554" t="s">
         <v>1133</v>
       </c>
-      <c r="D553" t="s">
+      <c r="D554" t="s">
         <v>1134</v>
       </c>
-      <c r="F553" t="s">
+      <c r="F554" t="s">
+        <v>60</v>
+      </c>
+      <c r="G554" t="s">
+        <v>14</v>
+      </c>
+      <c r="H554">
+        <v>45764</v>
+      </c>
+      <c r="I554" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9">
+      <c r="A555" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F555" t="s">
         <v>18</v>
       </c>
-      <c r="G553" t="s">
-        <v>14</v>
-      </c>
-      <c r="H553">
+      <c r="G555" t="s">
+        <v>14</v>
+      </c>
+      <c r="H555">
         <v>45477</v>
       </c>
-      <c r="I553" t="s">
+      <c r="I555" t="s">
         <v>12</v>
       </c>
     </row>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3531" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="1145">
   <si>
     <t>Fornitore</t>
   </si>
@@ -3076,6 +3076,12 @@
     <t>V.3.1.0</t>
   </si>
   <si>
+    <t>SOLUTIONMED SRL</t>
+  </si>
+  <si>
+    <t>SPHERE</t>
+  </si>
+  <si>
     <t>SOSEPE S.R.L.</t>
   </si>
   <si>
@@ -3371,6 +3377,12 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>WebComNet</t>
+  </si>
+  <si>
+    <t>GesFisioInCloud</t>
   </si>
   <si>
     <t>We BiNar S.r.l.</t>
@@ -3768,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I557"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -15693,16 +15705,16 @@
         <v>1021</v>
       </c>
       <c r="D496" t="s">
-        <v>496</v>
+        <v>208</v>
       </c>
       <c r="F496" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G496" t="s">
         <v>14</v>
       </c>
       <c r="H496">
-        <v>45329</v>
+        <v>46101</v>
       </c>
       <c r="I496" t="s">
         <v>12</v>
@@ -15710,10 +15722,10 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C497" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D497" t="s">
         <v>496</v>
@@ -15725,7 +15737,7 @@
         <v>14</v>
       </c>
       <c r="H497">
-        <v>46065</v>
+        <v>45329</v>
       </c>
       <c r="I497" t="s">
         <v>12</v>
@@ -15739,7 +15751,7 @@
         <v>1023</v>
       </c>
       <c r="D498" t="s">
-        <v>1024</v>
+        <v>496</v>
       </c>
       <c r="F498" t="s">
         <v>35</v>
@@ -15748,7 +15760,7 @@
         <v>14</v>
       </c>
       <c r="H498">
-        <v>45720</v>
+        <v>46065</v>
       </c>
       <c r="I498" t="s">
         <v>12</v>
@@ -15756,22 +15768,22 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C499" t="s">
         <v>1025</v>
       </c>
-      <c r="C499" t="s">
+      <c r="D499" t="s">
         <v>1026</v>
       </c>
-      <c r="D499" t="s">
-        <v>1027</v>
-      </c>
       <c r="F499" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G499" t="s">
         <v>14</v>
       </c>
       <c r="H499">
-        <v>46097</v>
+        <v>45720</v>
       </c>
       <c r="I499" t="s">
         <v>12</v>
@@ -15779,22 +15791,22 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C500" t="s">
         <v>1028</v>
       </c>
-      <c r="C500" t="s">
+      <c r="D500" t="s">
         <v>1029</v>
       </c>
-      <c r="D500" t="s">
-        <v>12</v>
-      </c>
       <c r="F500" t="s">
-        <v>187</v>
+        <v>24</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
       </c>
       <c r="H500">
-        <v>45190</v>
+        <v>46097</v>
       </c>
       <c r="I500" t="s">
         <v>12</v>
@@ -15808,16 +15820,16 @@
         <v>1031</v>
       </c>
       <c r="D501" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F501" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G501" t="s">
         <v>14</v>
       </c>
       <c r="H501">
-        <v>45565</v>
+        <v>45190</v>
       </c>
       <c r="I501" t="s">
         <v>12</v>
@@ -15831,16 +15843,16 @@
         <v>1033</v>
       </c>
       <c r="D502" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="F502" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
       </c>
       <c r="H502">
-        <v>46000</v>
+        <v>45565</v>
       </c>
       <c r="I502" t="s">
         <v>12</v>
@@ -15848,22 +15860,22 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C503" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D503" t="s">
         <v>208</v>
       </c>
       <c r="F503" t="s">
-        <v>1034</v>
+        <v>202</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
       </c>
       <c r="H503">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="I503" t="s">
         <v>12</v>
@@ -15871,22 +15883,22 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C504" t="s">
         <v>1035</v>
       </c>
-      <c r="C504" t="s">
+      <c r="D504" t="s">
+        <v>208</v>
+      </c>
+      <c r="F504" t="s">
         <v>1036</v>
       </c>
-      <c r="D504" t="s">
-        <v>12</v>
-      </c>
-      <c r="F504" t="s">
-        <v>35</v>
-      </c>
       <c r="G504" t="s">
         <v>14</v>
       </c>
       <c r="H504">
-        <v>46059</v>
+        <v>46044</v>
       </c>
       <c r="I504" t="s">
         <v>12</v>
@@ -15900,16 +15912,16 @@
         <v>1038</v>
       </c>
       <c r="D505" t="s">
-        <v>1039</v>
+        <v>12</v>
       </c>
       <c r="F505" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
       </c>
       <c r="H505">
-        <v>45083</v>
+        <v>46059</v>
       </c>
       <c r="I505" t="s">
         <v>12</v>
@@ -15917,22 +15929,22 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C506" t="s">
         <v>1040</v>
       </c>
-      <c r="C506" t="s">
+      <c r="D506" t="s">
         <v>1041</v>
       </c>
-      <c r="D506" t="s">
-        <v>373</v>
-      </c>
       <c r="F506" t="s">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
       </c>
       <c r="H506">
-        <v>45593</v>
+        <v>45083</v>
       </c>
       <c r="I506" t="s">
         <v>12</v>
@@ -15946,16 +15958,16 @@
         <v>1043</v>
       </c>
       <c r="D507" t="s">
-        <v>1044</v>
+        <v>373</v>
       </c>
       <c r="F507" t="s">
-        <v>22</v>
+        <v>247</v>
       </c>
       <c r="G507" t="s">
         <v>14</v>
       </c>
       <c r="H507">
-        <v>46006</v>
+        <v>45593</v>
       </c>
       <c r="I507" t="s">
         <v>12</v>
@@ -15963,22 +15975,22 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C508" t="s">
         <v>1045</v>
       </c>
-      <c r="C508" t="s">
+      <c r="D508" t="s">
         <v>1046</v>
       </c>
-      <c r="D508" t="s">
-        <v>1047</v>
-      </c>
       <c r="F508" t="s">
-        <v>1048</v>
+        <v>22</v>
       </c>
       <c r="G508" t="s">
         <v>14</v>
       </c>
       <c r="H508">
-        <v>45573</v>
+        <v>46006</v>
       </c>
       <c r="I508" t="s">
         <v>12</v>
@@ -15986,22 +15998,22 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D509" t="s">
         <v>1049</v>
       </c>
-      <c r="C509" t="s">
+      <c r="F509" t="s">
         <v>1050</v>
       </c>
-      <c r="D509" t="s">
-        <v>98</v>
-      </c>
-      <c r="F509" t="s">
-        <v>42</v>
-      </c>
       <c r="G509" t="s">
         <v>14</v>
       </c>
       <c r="H509">
-        <v>46080</v>
+        <v>45573</v>
       </c>
       <c r="I509" t="s">
         <v>12</v>
@@ -16015,16 +16027,16 @@
         <v>1052</v>
       </c>
       <c r="D510" t="s">
-        <v>1053</v>
+        <v>98</v>
       </c>
       <c r="F510" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G510" t="s">
         <v>14</v>
       </c>
       <c r="H510">
-        <v>45049</v>
+        <v>46080</v>
       </c>
       <c r="I510" t="s">
         <v>12</v>
@@ -16032,22 +16044,22 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C511" t="s">
         <v>1054</v>
       </c>
       <c r="D511" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F511" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G511" t="s">
         <v>14</v>
       </c>
       <c r="H511">
-        <v>45114</v>
+        <v>45049</v>
       </c>
       <c r="I511" t="s">
         <v>12</v>
@@ -16055,25 +16067,22 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C512" t="s">
         <v>1056</v>
       </c>
       <c r="D512" t="s">
-        <v>286</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F512" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
       </c>
       <c r="H512">
-        <v>45727</v>
+        <v>45114</v>
       </c>
       <c r="I512" t="s">
         <v>12</v>
@@ -16081,25 +16090,25 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C513" t="s">
         <v>1058</v>
       </c>
       <c r="D513" t="s">
+        <v>286</v>
+      </c>
+      <c r="E513" t="s">
         <v>1059</v>
       </c>
-      <c r="E513" t="s">
-        <v>1060</v>
-      </c>
       <c r="F513" t="s">
-        <v>1061</v>
+        <v>22</v>
       </c>
       <c r="G513" t="s">
         <v>14</v>
       </c>
       <c r="H513">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="I513" t="s">
         <v>12</v>
@@ -16107,25 +16116,25 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C514" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E514" t="s">
         <v>1062</v>
       </c>
-      <c r="D514" t="s">
-        <v>146</v>
-      </c>
-      <c r="E514" t="s">
+      <c r="F514" t="s">
         <v>1063</v>
       </c>
-      <c r="F514" t="s">
-        <v>60</v>
-      </c>
       <c r="G514" t="s">
         <v>14</v>
       </c>
       <c r="H514">
-        <v>45747</v>
+        <v>45797</v>
       </c>
       <c r="I514" t="s">
         <v>12</v>
@@ -16133,25 +16142,25 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C515" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D515" t="s">
         <v>146</v>
       </c>
       <c r="E515" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F515" t="s">
-        <v>1064</v>
+        <v>60</v>
       </c>
       <c r="G515" t="s">
         <v>14</v>
       </c>
       <c r="H515">
-        <v>45813</v>
+        <v>45747</v>
       </c>
       <c r="I515" t="s">
         <v>12</v>
@@ -16159,25 +16168,25 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C516" t="s">
-        <v>159</v>
+        <v>1064</v>
       </c>
       <c r="D516" t="s">
-        <v>591</v>
+        <v>146</v>
       </c>
       <c r="E516" t="s">
-        <v>173</v>
+        <v>1065</v>
       </c>
       <c r="F516" t="s">
-        <v>22</v>
+        <v>1066</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
       </c>
       <c r="H516">
-        <v>45043</v>
+        <v>45813</v>
       </c>
       <c r="I516" t="s">
         <v>12</v>
@@ -16185,16 +16194,16 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C517" t="s">
-        <v>1065</v>
+        <v>159</v>
       </c>
       <c r="D517" t="s">
-        <v>98</v>
+        <v>591</v>
       </c>
       <c r="E517" t="s">
-        <v>1066</v>
+        <v>173</v>
       </c>
       <c r="F517" t="s">
         <v>22</v>
@@ -16211,25 +16220,25 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C518" t="s">
         <v>1067</v>
       </c>
       <c r="D518" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="E518" t="s">
         <v>1068</v>
       </c>
       <c r="F518" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G518" t="s">
         <v>14</v>
       </c>
       <c r="H518">
-        <v>45184</v>
+        <v>45043</v>
       </c>
       <c r="I518" t="s">
         <v>12</v>
@@ -16237,7 +16246,7 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C519" t="s">
         <v>1069</v>
@@ -16246,7 +16255,7 @@
         <v>208</v>
       </c>
       <c r="E519" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F519" t="s">
         <v>13</v>
@@ -16255,7 +16264,7 @@
         <v>14</v>
       </c>
       <c r="H519">
-        <v>45219</v>
+        <v>45184</v>
       </c>
       <c r="I519" t="s">
         <v>12</v>
@@ -16263,16 +16272,16 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C520" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D520" t="s">
+        <v>208</v>
+      </c>
+      <c r="E520" t="s">
         <v>1070</v>
-      </c>
-      <c r="D520" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E520" t="s">
-        <v>1072</v>
       </c>
       <c r="F520" t="s">
         <v>13</v>
@@ -16281,7 +16290,7 @@
         <v>14</v>
       </c>
       <c r="H520">
-        <v>45303</v>
+        <v>45219</v>
       </c>
       <c r="I520" t="s">
         <v>12</v>
@@ -16289,12 +16298,15 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C521" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D521" t="s">
         <v>1073</v>
       </c>
-      <c r="D521" t="s">
+      <c r="E521" t="s">
         <v>1074</v>
       </c>
       <c r="F521" t="s">
@@ -16304,7 +16316,7 @@
         <v>14</v>
       </c>
       <c r="H521">
-        <v>45327</v>
+        <v>45303</v>
       </c>
       <c r="I521" t="s">
         <v>12</v>
@@ -16312,16 +16324,13 @@
     </row>
     <row r="522" spans="1:9">
       <c r="A522" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C522" t="s">
         <v>1075</v>
       </c>
       <c r="D522" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E522" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -16338,12 +16347,15 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C523" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D523" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E523" t="s">
         <v>1074</v>
       </c>
       <c r="F523" t="s">
@@ -16361,16 +16373,13 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C524" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D524" t="s">
-        <v>54</v>
-      </c>
-      <c r="E524" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F524" t="s">
         <v>13</v>
@@ -16379,7 +16388,7 @@
         <v>14</v>
       </c>
       <c r="H524">
-        <v>45439</v>
+        <v>45327</v>
       </c>
       <c r="I524" t="s">
         <v>12</v>
@@ -16387,22 +16396,25 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C525" t="s">
         <v>1079</v>
       </c>
       <c r="D525" t="s">
-        <v>330</v>
+        <v>54</v>
+      </c>
+      <c r="E525" t="s">
+        <v>1080</v>
       </c>
       <c r="F525" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G525" t="s">
         <v>14</v>
       </c>
       <c r="H525">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="I525" t="s">
         <v>12</v>
@@ -16410,22 +16422,22 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="C526" t="s">
         <v>1081</v>
       </c>
       <c r="D526" t="s">
-        <v>1082</v>
+        <v>330</v>
       </c>
       <c r="F526" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G526" t="s">
         <v>14</v>
       </c>
       <c r="H526">
-        <v>45022</v>
+        <v>45951</v>
       </c>
       <c r="I526" t="s">
         <v>12</v>
@@ -16433,22 +16445,22 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C527" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D527" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F527" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
       </c>
       <c r="H527">
-        <v>45275</v>
+        <v>45022</v>
       </c>
       <c r="I527" t="s">
         <v>12</v>
@@ -16456,22 +16468,22 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C528" t="s">
         <v>1083</v>
       </c>
-      <c r="C528" t="s">
+      <c r="D528" t="s">
         <v>1084</v>
       </c>
-      <c r="D528" t="s">
-        <v>1085</v>
-      </c>
       <c r="F528" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
       </c>
       <c r="H528">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="I528" t="s">
         <v>12</v>
@@ -16479,13 +16491,13 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C529" t="s">
         <v>1086</v>
       </c>
-      <c r="C529" t="s">
+      <c r="D529" t="s">
         <v>1087</v>
-      </c>
-      <c r="D529" t="s">
-        <v>98</v>
       </c>
       <c r="F529" t="s">
         <v>13</v>
@@ -16494,7 +16506,7 @@
         <v>14</v>
       </c>
       <c r="H529">
-        <v>45722</v>
+        <v>45792</v>
       </c>
       <c r="I529" t="s">
         <v>12</v>
@@ -16508,16 +16520,16 @@
         <v>1089</v>
       </c>
       <c r="D530" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F530" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G530" t="s">
         <v>14</v>
       </c>
       <c r="H530">
-        <v>45107</v>
+        <v>45722</v>
       </c>
       <c r="I530" t="s">
         <v>12</v>
@@ -16534,13 +16546,13 @@
         <v>12</v>
       </c>
       <c r="F531" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
       </c>
       <c r="H531">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="I531" t="s">
         <v>12</v>
@@ -16548,22 +16560,22 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C532" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D532" t="s">
         <v>12</v>
       </c>
       <c r="F532" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
       </c>
       <c r="H532">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="I532" t="s">
         <v>12</v>
@@ -16571,22 +16583,22 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C533" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D533" t="s">
         <v>12</v>
       </c>
       <c r="F533" t="s">
-        <v>359</v>
+        <v>105</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
       </c>
       <c r="H533">
-        <v>45141</v>
+        <v>45107</v>
       </c>
       <c r="I533" t="s">
         <v>12</v>
@@ -16594,22 +16606,22 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C534" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D534" t="s">
         <v>12</v>
       </c>
       <c r="F534" t="s">
-        <v>13</v>
+        <v>359</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
       </c>
       <c r="H534">
-        <v>45194</v>
+        <v>45141</v>
       </c>
       <c r="I534" t="s">
         <v>12</v>
@@ -16617,22 +16629,22 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C535" t="s">
         <v>1095</v>
       </c>
       <c r="D535" t="s">
-        <v>246</v>
+        <v>12</v>
       </c>
       <c r="F535" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="G535" t="s">
         <v>14</v>
       </c>
       <c r="H535">
-        <v>45856</v>
+        <v>45194</v>
       </c>
       <c r="I535" t="s">
         <v>12</v>
@@ -16640,16 +16652,16 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C536" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D536" t="s">
         <v>246</v>
       </c>
       <c r="F536" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="G536" t="s">
         <v>14</v>
@@ -16663,22 +16675,22 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C537" t="s">
         <v>1098</v>
       </c>
       <c r="D537" t="s">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="F537" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G537" t="s">
         <v>14</v>
       </c>
       <c r="H537">
-        <v>45392</v>
+        <v>45856</v>
       </c>
       <c r="I537" t="s">
         <v>12</v>
@@ -16686,13 +16698,13 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C538" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D538" t="s">
-        <v>1099</v>
+        <v>77</v>
       </c>
       <c r="F538" t="s">
         <v>35</v>
@@ -16701,7 +16713,7 @@
         <v>14</v>
       </c>
       <c r="H538">
-        <v>45792</v>
+        <v>45392</v>
       </c>
       <c r="I538" t="s">
         <v>12</v>
@@ -16709,13 +16721,13 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C539" t="s">
         <v>1100</v>
       </c>
-      <c r="C539" t="s">
+      <c r="D539" t="s">
         <v>1101</v>
-      </c>
-      <c r="D539" t="s">
-        <v>1102</v>
       </c>
       <c r="F539" t="s">
         <v>35</v>
@@ -16724,7 +16736,7 @@
         <v>14</v>
       </c>
       <c r="H539">
-        <v>45495</v>
+        <v>45792</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16732,13 +16744,13 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C540" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D540" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F540" t="s">
         <v>35</v>
@@ -16747,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="H540">
-        <v>46097</v>
+        <v>45495</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16755,22 +16767,22 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C541" t="s">
         <v>1103</v>
       </c>
-      <c r="C541" t="s">
+      <c r="D541" t="s">
         <v>1104</v>
       </c>
-      <c r="D541" t="s">
-        <v>1105</v>
-      </c>
       <c r="F541" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
       </c>
       <c r="H541">
-        <v>45223</v>
+        <v>46097</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16778,22 +16790,22 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C542" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D542" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F542" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G542" t="s">
         <v>14</v>
       </c>
       <c r="H542">
-        <v>45254</v>
+        <v>45223</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16801,22 +16813,22 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C543" t="s">
         <v>1106</v>
       </c>
-      <c r="C543" t="s">
+      <c r="D543" t="s">
         <v>1107</v>
       </c>
-      <c r="D543" t="s">
-        <v>12</v>
-      </c>
       <c r="F543" t="s">
-        <v>697</v>
+        <v>19</v>
       </c>
       <c r="G543" t="s">
         <v>14</v>
       </c>
       <c r="H543">
-        <v>45807</v>
+        <v>45254</v>
       </c>
       <c r="I543" t="s">
         <v>12</v>
@@ -16833,13 +16845,13 @@
         <v>12</v>
       </c>
       <c r="F544" t="s">
-        <v>13</v>
+        <v>697</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
       </c>
       <c r="H544">
-        <v>45849</v>
+        <v>45807</v>
       </c>
       <c r="I544" t="s">
         <v>12</v>
@@ -16853,7 +16865,7 @@
         <v>1111</v>
       </c>
       <c r="D545" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -16862,7 +16874,7 @@
         <v>14</v>
       </c>
       <c r="H545">
-        <v>46000</v>
+        <v>45849</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -16870,10 +16882,10 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C546" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D546" t="s">
         <v>29</v>
@@ -16885,7 +16897,7 @@
         <v>14</v>
       </c>
       <c r="H546">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="I546" t="s">
         <v>12</v>
@@ -16893,22 +16905,22 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C547" t="s">
         <v>1114</v>
       </c>
       <c r="D547" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="F547" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G547" t="s">
         <v>14</v>
       </c>
       <c r="H547">
-        <v>45825</v>
+        <v>46010</v>
       </c>
       <c r="I547" t="s">
         <v>12</v>
@@ -16916,22 +16928,22 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C548" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D548" t="s">
-        <v>1115</v>
+        <v>98</v>
       </c>
       <c r="F548" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="G548" t="s">
         <v>14</v>
       </c>
       <c r="H548">
-        <v>46078</v>
+        <v>45825</v>
       </c>
       <c r="I548" t="s">
         <v>12</v>
@@ -16939,22 +16951,22 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C549" t="s">
         <v>1116</v>
       </c>
-      <c r="C549" t="s">
+      <c r="D549" t="s">
         <v>1117</v>
       </c>
-      <c r="D549" t="s">
-        <v>1118</v>
-      </c>
       <c r="F549" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="G549" t="s">
         <v>14</v>
       </c>
       <c r="H549">
-        <v>46035</v>
+        <v>46078</v>
       </c>
       <c r="I549" t="s">
         <v>12</v>
@@ -16962,22 +16974,22 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C550" t="s">
         <v>1119</v>
       </c>
-      <c r="C550" t="s">
+      <c r="D550" t="s">
         <v>1120</v>
       </c>
-      <c r="D550" t="s">
-        <v>98</v>
-      </c>
       <c r="F550" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G550" t="s">
         <v>14</v>
       </c>
       <c r="H550">
-        <v>45985</v>
+        <v>46035</v>
       </c>
       <c r="I550" t="s">
         <v>12</v>
@@ -16991,16 +17003,16 @@
         <v>1122</v>
       </c>
       <c r="D551" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F551" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G551" t="s">
         <v>14</v>
       </c>
       <c r="H551">
-        <v>45190</v>
+        <v>46101</v>
       </c>
       <c r="I551" t="s">
         <v>12</v>
@@ -17014,16 +17026,16 @@
         <v>1124</v>
       </c>
       <c r="D552" t="s">
-        <v>1125</v>
+        <v>98</v>
       </c>
       <c r="F552" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G552" t="s">
         <v>14</v>
       </c>
       <c r="H552">
-        <v>45029</v>
+        <v>45985</v>
       </c>
       <c r="I552" t="s">
         <v>12</v>
@@ -17031,25 +17043,22 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C553" t="s">
         <v>1126</v>
       </c>
-      <c r="C553" t="s">
-        <v>1127</v>
-      </c>
       <c r="D553" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E553" t="s">
-        <v>1129</v>
+        <v>12</v>
       </c>
       <c r="F553" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G553" t="s">
         <v>14</v>
       </c>
       <c r="H553">
-        <v>45376</v>
+        <v>45190</v>
       </c>
       <c r="I553" t="s">
         <v>12</v>
@@ -17057,16 +17066,13 @@
     </row>
     <row r="554" spans="1:9">
       <c r="A554" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="C554" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D554" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="F554" t="s">
         <v>22</v>
@@ -17075,7 +17081,7 @@
         <v>14</v>
       </c>
       <c r="H554">
-        <v>45085</v>
+        <v>45029</v>
       </c>
       <c r="I554" t="s">
         <v>12</v>
@@ -17085,23 +17091,23 @@
       <c r="A555" t="s">
         <v>1130</v>
       </c>
-      <c r="B555" t="s">
+      <c r="C555" t="s">
         <v>1131</v>
       </c>
-      <c r="C555" t="s">
-        <v>1134</v>
-      </c>
       <c r="D555" t="s">
-        <v>1135</v>
+        <v>1132</v>
+      </c>
+      <c r="E555" t="s">
+        <v>1133</v>
       </c>
       <c r="F555" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G555" t="s">
         <v>14</v>
       </c>
       <c r="H555">
-        <v>45387</v>
+        <v>45376</v>
       </c>
       <c r="I555" t="s">
         <v>12</v>
@@ -17109,10 +17115,10 @@
     </row>
     <row r="556" spans="1:9">
       <c r="A556" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B556" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C556" t="s">
         <v>1136</v>
@@ -17121,13 +17127,13 @@
         <v>1137</v>
       </c>
       <c r="F556" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G556" t="s">
         <v>14</v>
       </c>
       <c r="H556">
-        <v>45764</v>
+        <v>45085</v>
       </c>
       <c r="I556" t="s">
         <v>12</v>
@@ -17135,24 +17141,76 @@
     </row>
     <row r="557" spans="1:9">
       <c r="A557" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C557" t="s">
         <v>1138</v>
       </c>
-      <c r="C557" t="s">
+      <c r="D557" t="s">
         <v>1139</v>
       </c>
-      <c r="D557" t="s">
+      <c r="F557" t="s">
+        <v>22</v>
+      </c>
+      <c r="G557" t="s">
+        <v>14</v>
+      </c>
+      <c r="H557">
+        <v>45387</v>
+      </c>
+      <c r="I557" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="558" spans="1:9">
+      <c r="A558" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C558" t="s">
         <v>1140</v>
       </c>
-      <c r="F557" t="s">
+      <c r="D558" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F558" t="s">
+        <v>60</v>
+      </c>
+      <c r="G558" t="s">
+        <v>14</v>
+      </c>
+      <c r="H558">
+        <v>45764</v>
+      </c>
+      <c r="I558" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9">
+      <c r="A559" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F559" t="s">
         <v>18</v>
       </c>
-      <c r="G557" t="s">
-        <v>14</v>
-      </c>
-      <c r="H557">
+      <c r="G559" t="s">
+        <v>14</v>
+      </c>
+      <c r="H559">
         <v>45477</v>
       </c>
-      <c r="I557" t="s">
+      <c r="I559" t="s">
         <v>12</v>
       </c>
     </row>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="1154">
   <si>
     <t>Fornitore</t>
   </si>
@@ -1606,520 +1606,523 @@
     <t>SaniPocket</t>
   </si>
   <si>
+    <t>LAB,LDO,RAD,RSA,RAP</t>
+  </si>
+  <si>
+    <t>GE Medical Systems</t>
+  </si>
+  <si>
+    <t>MUSE</t>
+  </si>
+  <si>
+    <t>NX</t>
+  </si>
+  <si>
+    <t>CCW</t>
+  </si>
+  <si>
+    <t>GE_Medical_System_Italia_SPA</t>
+  </si>
+  <si>
+    <t>WEBCENTRYRIS</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>GEMSI</t>
+  </si>
+  <si>
+    <t>CENTRICITYRIS</t>
+  </si>
+  <si>
+    <t>GENESISOFT</t>
+  </si>
+  <si>
+    <t>TOMMY</t>
+  </si>
+  <si>
+    <t>GeniusSrl</t>
+  </si>
+  <si>
+    <t>Pocr</t>
+  </si>
+  <si>
+    <t>1.0.0.0</t>
+  </si>
+  <si>
+    <t>GESAN SRL</t>
+  </si>
+  <si>
+    <t>WLEXT-LIS</t>
+  </si>
+  <si>
+    <t>WLEXT-VPS</t>
+  </si>
+  <si>
+    <t>WLEXT-LDO</t>
+  </si>
+  <si>
+    <t>WLEXT-RIS</t>
+  </si>
+  <si>
+    <t>WLEXT-AMB</t>
+  </si>
+  <si>
+    <t>WLEXT-RAP</t>
+  </si>
+  <si>
+    <t>GESANTHCS SRL</t>
+  </si>
+  <si>
+    <t>ENERGY-LIS</t>
+  </si>
+  <si>
+    <t>V2.0</t>
+  </si>
+  <si>
+    <t>ENERGY-RIS</t>
+  </si>
+  <si>
+    <t>ENERGY-RSA</t>
+  </si>
+  <si>
+    <t>GESTIONE SALUTE SRL</t>
+  </si>
+  <si>
+    <t>GSD FSE Link</t>
+  </si>
+  <si>
+    <t>LDO,LAB</t>
+  </si>
+  <si>
+    <t>LDO,LAB,RSA</t>
+  </si>
+  <si>
+    <t>Ginevra Media Communication</t>
+  </si>
+  <si>
+    <t>GMC-Medical</t>
+  </si>
+  <si>
+    <t>Giotto Informatica</t>
+  </si>
+  <si>
+    <t>LeoLab</t>
+  </si>
+  <si>
+    <t>5.0/2023</t>
+  </si>
+  <si>
+    <t>Gmed S.r.l.</t>
+  </si>
+  <si>
+    <t>VIRTUHIS</t>
+  </si>
+  <si>
+    <t>22.0.3</t>
+  </si>
+  <si>
+    <t>GPI_SPA</t>
+  </si>
+  <si>
+    <t>GPI SPA</t>
+  </si>
+  <si>
+    <t>CCE_Cartella_Clinica_Elettronica</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>NGH PS</t>
+  </si>
+  <si>
+    <t>4.3, 4.5</t>
+  </si>
+  <si>
+    <t>NGH ADT</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>8.1, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8, 8.9, 8.10, 8.11</t>
+  </si>
+  <si>
+    <t>PSNET</t>
+  </si>
+  <si>
+    <t>PSW04.00.05.11</t>
+  </si>
+  <si>
+    <t>IM-LISA</t>
+  </si>
+  <si>
+    <t>3.21_b5</t>
+  </si>
+  <si>
+    <t>G2CLINICO</t>
+  </si>
+  <si>
+    <t>G2.0.01.011</t>
+  </si>
+  <si>
+    <t>HCSUITE</t>
+  </si>
+  <si>
+    <t>3.19.23</t>
+  </si>
+  <si>
+    <t>IE-DEA</t>
+  </si>
+  <si>
+    <t>8.112_b13</t>
+  </si>
+  <si>
+    <t>PIESSE</t>
+  </si>
+  <si>
+    <t>8832_b1</t>
+  </si>
+  <si>
+    <t>AMICO</t>
+  </si>
+  <si>
+    <t>2.21.2</t>
+  </si>
+  <si>
+    <t>2.22.0</t>
+  </si>
+  <si>
+    <t>NEOCARE</t>
+  </si>
+  <si>
+    <t>2.42</t>
+  </si>
+  <si>
+    <t>IE-OPERA</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>5.10, 5.11, 5.13, 5.13.3, 5.14, 5.22</t>
+  </si>
+  <si>
+    <t>IE-DEGENTI</t>
+  </si>
+  <si>
+    <t>9.98_b25</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>1.67</t>
+  </si>
+  <si>
+    <t>1.68, 1.69, 1.70, 1.71, 1.72, 1.73, 1.74, 1.75, 1.76, 1.77, 1.78, 1.79, 1.80, 1.81, 1.82</t>
+  </si>
+  <si>
+    <t>IM-PATIDOK</t>
+  </si>
+  <si>
+    <t>IT_10.0.1</t>
+  </si>
+  <si>
+    <t>NGH CCA</t>
+  </si>
+  <si>
+    <t>DEGENZA</t>
+  </si>
+  <si>
+    <t>20.86</t>
+  </si>
+  <si>
+    <t>AIRO</t>
+  </si>
+  <si>
+    <t>SSI</t>
+  </si>
+  <si>
+    <t>ARCA WEB</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>G2 WEB</t>
+  </si>
+  <si>
+    <t>2.7_b1</t>
+  </si>
+  <si>
+    <t>EMOLIFE</t>
+  </si>
+  <si>
+    <t>10.85.0.0</t>
+  </si>
+  <si>
+    <t>EMONET</t>
+  </si>
+  <si>
+    <t>9.6.3</t>
+  </si>
+  <si>
+    <t>PHI KLINIK</t>
+  </si>
+  <si>
+    <t>2.4.3</t>
+  </si>
+  <si>
+    <t>POHEMA</t>
+  </si>
+  <si>
+    <t>2.0.8</t>
+  </si>
+  <si>
+    <t>2.2.0</t>
+  </si>
+  <si>
+    <t>GRUPPOINFORMATICO</t>
+  </si>
+  <si>
+    <t>RESMEDICA</t>
+  </si>
+  <si>
+    <t>10.1.701</t>
+  </si>
+  <si>
+    <t>RSA,LAB,RAD</t>
+  </si>
+  <si>
+    <t>10.1.702</t>
+  </si>
+  <si>
+    <t>RSA,LAB,RAD,LDO</t>
+  </si>
+  <si>
+    <t>GRUPPO MAXED DI DANESI EMANUELE ALESSANDRO FABIO SNC</t>
+  </si>
+  <si>
+    <t>GMSoftFSE</t>
+  </si>
+  <si>
+    <t>V.1.1.0</t>
+  </si>
+  <si>
+    <t>HEALTH INSIDE</t>
+  </si>
+  <si>
+    <t>SADI HEALTH</t>
+  </si>
+  <si>
+    <t>HealthStrategy</t>
+  </si>
+  <si>
+    <t>HEasy</t>
+  </si>
+  <si>
+    <t>49.00.00</t>
+  </si>
+  <si>
+    <t>Health Telematic Network S.r.l.</t>
+  </si>
+  <si>
+    <t>HTN Virtual Hospital</t>
+  </si>
+  <si>
+    <t>HelioSistemiSrls</t>
+  </si>
+  <si>
+    <t>Lido_fse</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>Hi.Tech</t>
+  </si>
+  <si>
+    <t>PS3</t>
+  </si>
+  <si>
+    <t>AcceWeb</t>
+  </si>
+  <si>
+    <t>2.1.0</t>
+  </si>
+  <si>
+    <t>AmbWeb</t>
+  </si>
+  <si>
+    <t>HLT Management</t>
+  </si>
+  <si>
+    <t>HLT Central</t>
+  </si>
+  <si>
+    <t>LDO,RSA,RAD,LAB,VPS</t>
+  </si>
+  <si>
+    <t>HS INFORMATICA</t>
+  </si>
+  <si>
+    <t>HS LABO</t>
+  </si>
+  <si>
+    <t>HTINFORMATICA SRL</t>
+  </si>
+  <si>
+    <t>HTSANg</t>
+  </si>
+  <si>
+    <t>I.T. Svil Srl</t>
+  </si>
+  <si>
+    <t>4Heasy ADT</t>
+  </si>
+  <si>
+    <t>IASI S.r.l</t>
+  </si>
+  <si>
+    <t>SISWeb</t>
+  </si>
+  <si>
+    <t>2.4.8</t>
+  </si>
+  <si>
+    <t>LDO,VPS,RAD,RSA</t>
+  </si>
+  <si>
+    <t>Ianiri Informatica</t>
+  </si>
+  <si>
+    <t>DOCPLANNER, Ianiri_Informatica</t>
+  </si>
+  <si>
+    <t>GipoNext</t>
+  </si>
+  <si>
+    <t>v.5</t>
+  </si>
+  <si>
+    <t>5.87</t>
+  </si>
+  <si>
+    <t>5.114</t>
+  </si>
+  <si>
+    <t>IGCOM</t>
+  </si>
+  <si>
+    <t>IGSUITE</t>
+  </si>
+  <si>
+    <t>RAD,LDO,RSA,LAB</t>
+  </si>
+  <si>
+    <t>IG.PSO</t>
+  </si>
+  <si>
+    <t>IL MELOGRANO DATA SERVICES</t>
+  </si>
+  <si>
+    <t>FSE-VPS</t>
+  </si>
+  <si>
+    <t>FSE-RAD</t>
+  </si>
+  <si>
+    <t>FSE-RSA</t>
+  </si>
+  <si>
+    <t>FSE-LDO</t>
+  </si>
+  <si>
+    <t>ing_simone_scavizzi</t>
+  </si>
+  <si>
+    <t>clinilabNet</t>
+  </si>
+  <si>
+    <t>INFOGRAMMA</t>
+  </si>
+  <si>
+    <t>GALENUS</t>
+  </si>
+  <si>
+    <t>2024.1</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>infomatic.it</t>
+  </si>
+  <si>
+    <t>Demat190</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Infonext S.r.l.</t>
+  </si>
+  <si>
+    <t>eVac</t>
+  </si>
+  <si>
+    <t>Infordata Digital Health Solutions</t>
+  </si>
+  <si>
+    <t>AstroL@bI/O</t>
+  </si>
+  <si>
+    <t>11.231.650</t>
+  </si>
+  <si>
+    <t>11.252.694</t>
+  </si>
+  <si>
+    <t>INFOSERVICE DI FRANCESCO LEO</t>
+  </si>
+  <si>
+    <t>FLY</t>
+  </si>
+  <si>
+    <t>2.02, WEB, 3.0</t>
+  </si>
+  <si>
+    <t>RAD,RSA,LAB</t>
+  </si>
+  <si>
+    <t>GESCON</t>
+  </si>
+  <si>
+    <t>WEB</t>
+  </si>
+  <si>
+    <t>INFOSYS SRL</t>
+  </si>
+  <si>
+    <t>SIOWEB</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>SIOWEB-PAINT</t>
+  </si>
+  <si>
+    <t>Innogea srl</t>
+  </si>
+  <si>
+    <t>CareMed</t>
+  </si>
+  <si>
     <t>LAB,LDO,RAD,RSA</t>
-  </si>
-  <si>
-    <t>GE Medical Systems</t>
-  </si>
-  <si>
-    <t>MUSE</t>
-  </si>
-  <si>
-    <t>NX</t>
-  </si>
-  <si>
-    <t>CCW</t>
-  </si>
-  <si>
-    <t>GE_Medical_System_Italia_SPA</t>
-  </si>
-  <si>
-    <t>WEBCENTRYRIS</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>GEMSI</t>
-  </si>
-  <si>
-    <t>CENTRICITYRIS</t>
-  </si>
-  <si>
-    <t>GENESISOFT</t>
-  </si>
-  <si>
-    <t>TOMMY</t>
-  </si>
-  <si>
-    <t>GeniusSrl</t>
-  </si>
-  <si>
-    <t>Pocr</t>
-  </si>
-  <si>
-    <t>1.0.0.0</t>
-  </si>
-  <si>
-    <t>GESAN SRL</t>
-  </si>
-  <si>
-    <t>WLEXT-LIS</t>
-  </si>
-  <si>
-    <t>WLEXT-VPS</t>
-  </si>
-  <si>
-    <t>WLEXT-LDO</t>
-  </si>
-  <si>
-    <t>WLEXT-RIS</t>
-  </si>
-  <si>
-    <t>WLEXT-AMB</t>
-  </si>
-  <si>
-    <t>WLEXT-RAP</t>
-  </si>
-  <si>
-    <t>GESANTHCS SRL</t>
-  </si>
-  <si>
-    <t>ENERGY-LIS</t>
-  </si>
-  <si>
-    <t>V2.0</t>
-  </si>
-  <si>
-    <t>ENERGY-RIS</t>
-  </si>
-  <si>
-    <t>ENERGY-RSA</t>
-  </si>
-  <si>
-    <t>GESTIONE SALUTE SRL</t>
-  </si>
-  <si>
-    <t>GSD FSE Link</t>
-  </si>
-  <si>
-    <t>LDO,LAB</t>
-  </si>
-  <si>
-    <t>LDO,LAB,RSA</t>
-  </si>
-  <si>
-    <t>Ginevra Media Communication</t>
-  </si>
-  <si>
-    <t>GMC-Medical</t>
-  </si>
-  <si>
-    <t>Giotto Informatica</t>
-  </si>
-  <si>
-    <t>LeoLab</t>
-  </si>
-  <si>
-    <t>5.0/2023</t>
-  </si>
-  <si>
-    <t>Gmed S.r.l.</t>
-  </si>
-  <si>
-    <t>VIRTUHIS</t>
-  </si>
-  <si>
-    <t>22.0.3</t>
-  </si>
-  <si>
-    <t>GPI_SPA</t>
-  </si>
-  <si>
-    <t>GPI SPA</t>
-  </si>
-  <si>
-    <t>CCE_Cartella_Clinica_Elettronica</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>NGH PS</t>
-  </si>
-  <si>
-    <t>4.3, 4.5</t>
-  </si>
-  <si>
-    <t>NGH ADT</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>8.1, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8, 8.9, 8.10, 8.11</t>
-  </si>
-  <si>
-    <t>PSNET</t>
-  </si>
-  <si>
-    <t>PSW04.00.05.11</t>
-  </si>
-  <si>
-    <t>IM-LISA</t>
-  </si>
-  <si>
-    <t>3.21_b5</t>
-  </si>
-  <si>
-    <t>G2CLINICO</t>
-  </si>
-  <si>
-    <t>G2.0.01.011</t>
-  </si>
-  <si>
-    <t>HCSUITE</t>
-  </si>
-  <si>
-    <t>3.19.23</t>
-  </si>
-  <si>
-    <t>IE-DEA</t>
-  </si>
-  <si>
-    <t>8.112_b13</t>
-  </si>
-  <si>
-    <t>PIESSE</t>
-  </si>
-  <si>
-    <t>8832_b1</t>
-  </si>
-  <si>
-    <t>AMICO</t>
-  </si>
-  <si>
-    <t>2.21.2</t>
-  </si>
-  <si>
-    <t>2.22.0</t>
-  </si>
-  <si>
-    <t>NEOCARE</t>
-  </si>
-  <si>
-    <t>2.42</t>
-  </si>
-  <si>
-    <t>IE-OPERA</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>5.10, 5.11, 5.13, 5.13.3, 5.14, 5.22</t>
-  </si>
-  <si>
-    <t>IE-DEGENTI</t>
-  </si>
-  <si>
-    <t>9.98_b25</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>1.67</t>
-  </si>
-  <si>
-    <t>1.68, 1.69, 1.70, 1.71, 1.72, 1.73, 1.74, 1.75, 1.76, 1.77, 1.78, 1.79, 1.80, 1.81, 1.82</t>
-  </si>
-  <si>
-    <t>IM-PATIDOK</t>
-  </si>
-  <si>
-    <t>IT_10.0.1</t>
-  </si>
-  <si>
-    <t>NGH CCA</t>
-  </si>
-  <si>
-    <t>DEGENZA</t>
-  </si>
-  <si>
-    <t>20.86</t>
-  </si>
-  <si>
-    <t>AIRO</t>
-  </si>
-  <si>
-    <t>SSI</t>
-  </si>
-  <si>
-    <t>ARCA WEB</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>G2 WEB</t>
-  </si>
-  <si>
-    <t>2.7_b1</t>
-  </si>
-  <si>
-    <t>EMOLIFE</t>
-  </si>
-  <si>
-    <t>10.85.0.0</t>
-  </si>
-  <si>
-    <t>EMONET</t>
-  </si>
-  <si>
-    <t>9.6.3</t>
-  </si>
-  <si>
-    <t>PHI KLINIK</t>
-  </si>
-  <si>
-    <t>2.4.3</t>
-  </si>
-  <si>
-    <t>POHEMA</t>
-  </si>
-  <si>
-    <t>2.0.8</t>
-  </si>
-  <si>
-    <t>2.2.0</t>
-  </si>
-  <si>
-    <t>GRUPPOINFORMATICO</t>
-  </si>
-  <si>
-    <t>RESMEDICA</t>
-  </si>
-  <si>
-    <t>10.1.701</t>
-  </si>
-  <si>
-    <t>RSA,LAB,RAD</t>
-  </si>
-  <si>
-    <t>10.1.702</t>
-  </si>
-  <si>
-    <t>RSA,LAB,RAD,LDO</t>
-  </si>
-  <si>
-    <t>GRUPPO MAXED DI DANESI EMANUELE ALESSANDRO FABIO SNC</t>
-  </si>
-  <si>
-    <t>GMSoftFSE</t>
-  </si>
-  <si>
-    <t>V.1.1.0</t>
-  </si>
-  <si>
-    <t>HEALTH INSIDE</t>
-  </si>
-  <si>
-    <t>SADI HEALTH</t>
-  </si>
-  <si>
-    <t>HealthStrategy</t>
-  </si>
-  <si>
-    <t>HEasy</t>
-  </si>
-  <si>
-    <t>49.00.00</t>
-  </si>
-  <si>
-    <t>Health Telematic Network S.r.l.</t>
-  </si>
-  <si>
-    <t>HTN Virtual Hospital</t>
-  </si>
-  <si>
-    <t>HelioSistemiSrls</t>
-  </si>
-  <si>
-    <t>Lido_fse</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>Hi.Tech</t>
-  </si>
-  <si>
-    <t>PS3</t>
-  </si>
-  <si>
-    <t>AcceWeb</t>
-  </si>
-  <si>
-    <t>2.1.0</t>
-  </si>
-  <si>
-    <t>AmbWeb</t>
-  </si>
-  <si>
-    <t>HLT Management</t>
-  </si>
-  <si>
-    <t>HLT Central</t>
-  </si>
-  <si>
-    <t>LDO,RSA,RAD,LAB,VPS</t>
-  </si>
-  <si>
-    <t>HS INFORMATICA</t>
-  </si>
-  <si>
-    <t>HS LABO</t>
-  </si>
-  <si>
-    <t>HTINFORMATICA SRL</t>
-  </si>
-  <si>
-    <t>HTSANg</t>
-  </si>
-  <si>
-    <t>I.T. Svil Srl</t>
-  </si>
-  <si>
-    <t>4Heasy ADT</t>
-  </si>
-  <si>
-    <t>IASI S.r.l</t>
-  </si>
-  <si>
-    <t>SISWeb</t>
-  </si>
-  <si>
-    <t>2.4.8</t>
-  </si>
-  <si>
-    <t>LDO,VPS,RAD,RSA</t>
-  </si>
-  <si>
-    <t>Ianiri Informatica</t>
-  </si>
-  <si>
-    <t>DOCPLANNER, Ianiri_Informatica</t>
-  </si>
-  <si>
-    <t>GipoNext</t>
-  </si>
-  <si>
-    <t>v.5</t>
-  </si>
-  <si>
-    <t>5.87</t>
-  </si>
-  <si>
-    <t>5.114</t>
-  </si>
-  <si>
-    <t>IGCOM</t>
-  </si>
-  <si>
-    <t>IGSUITE</t>
-  </si>
-  <si>
-    <t>RAD,LDO,RSA,LAB</t>
-  </si>
-  <si>
-    <t>IG.PSO</t>
-  </si>
-  <si>
-    <t>IL MELOGRANO DATA SERVICES</t>
-  </si>
-  <si>
-    <t>FSE-VPS</t>
-  </si>
-  <si>
-    <t>FSE-RAD</t>
-  </si>
-  <si>
-    <t>FSE-RSA</t>
-  </si>
-  <si>
-    <t>FSE-LDO</t>
-  </si>
-  <si>
-    <t>ing_simone_scavizzi</t>
-  </si>
-  <si>
-    <t>clinilabNet</t>
-  </si>
-  <si>
-    <t>INFOGRAMMA</t>
-  </si>
-  <si>
-    <t>GALENUS</t>
-  </si>
-  <si>
-    <t>2024.1</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>infomatic.it</t>
-  </si>
-  <si>
-    <t>Demat190</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>Infonext S.r.l.</t>
-  </si>
-  <si>
-    <t>eVac</t>
-  </si>
-  <si>
-    <t>Infordata Digital Health Solutions</t>
-  </si>
-  <si>
-    <t>AstroL@bI/O</t>
-  </si>
-  <si>
-    <t>11.231.650</t>
-  </si>
-  <si>
-    <t>11.252.694</t>
-  </si>
-  <si>
-    <t>INFOSERVICE DI FRANCESCO LEO</t>
-  </si>
-  <si>
-    <t>FLY</t>
-  </si>
-  <si>
-    <t>2.02, WEB, 3.0</t>
-  </si>
-  <si>
-    <t>RAD,RSA,LAB</t>
-  </si>
-  <si>
-    <t>GESCON</t>
-  </si>
-  <si>
-    <t>WEB</t>
-  </si>
-  <si>
-    <t>INFOSYS SRL</t>
-  </si>
-  <si>
-    <t>SIOWEB</t>
-  </si>
-  <si>
-    <t>1.1.2</t>
-  </si>
-  <si>
-    <t>SIOWEB-PAINT</t>
-  </si>
-  <si>
-    <t>Innogea srl</t>
-  </si>
-  <si>
-    <t>CareMed</t>
   </si>
   <si>
     <t>INNOVATION GROUP</t>
@@ -12184,7 +12187,7 @@
         <v>12</v>
       </c>
       <c r="F345" t="s">
-        <v>530</v>
+        <v>702</v>
       </c>
       <c r="G345" t="s">
         <v>14</v>
@@ -12198,13 +12201,13 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C346" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D346" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F346" t="s">
         <v>251</v>
@@ -12221,13 +12224,13 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C347" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D347" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F347" t="s">
         <v>60</v>
@@ -12244,13 +12247,13 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C348" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D348" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F348" t="s">
         <v>19</v>
@@ -12267,16 +12270,16 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C349" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D349" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F349" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G349" t="s">
         <v>14</v>
@@ -12290,13 +12293,13 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C350" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D350" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F350" t="s">
         <v>126</v>
@@ -12313,13 +12316,13 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C351" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D351" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F351" t="s">
         <v>251</v>
@@ -12336,10 +12339,10 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C352" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D352" t="s">
         <v>29</v>
@@ -12359,16 +12362,16 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C353" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D353" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F353" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G353" t="s">
         <v>14</v>
@@ -12382,16 +12385,16 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C354" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D354" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F354" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G354" t="s">
         <v>14</v>
@@ -12405,10 +12408,10 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C355" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D355" t="s">
         <v>12</v>
@@ -12428,10 +12431,10 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C356" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D356" t="s">
         <v>39</v>
@@ -12451,10 +12454,10 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C357" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D357" t="s">
         <v>12</v>
@@ -12474,16 +12477,16 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C358" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D358" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E358" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F358" t="s">
         <v>35</v>
@@ -12500,10 +12503,10 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C359" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D359" t="s">
         <v>12</v>
@@ -12523,13 +12526,13 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C360" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D360" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F360" t="s">
         <v>13</v>
@@ -12546,13 +12549,13 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C361" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D361" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F361" t="s">
         <v>19</v>
@@ -12569,16 +12572,16 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C362" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D362" t="s">
         <v>596</v>
       </c>
       <c r="E362" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F362" t="s">
         <v>42</v>
@@ -12595,16 +12598,16 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C363" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D363" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F363" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G363" t="s">
         <v>14</v>
@@ -12618,10 +12621,10 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C364" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D364" t="s">
         <v>34</v>
@@ -12641,10 +12644,10 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C365" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D365" t="s">
         <v>524</v>
@@ -12664,16 +12667,16 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C366" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D366" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F366" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G366" t="s">
         <v>14</v>
@@ -12687,10 +12690,10 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C367" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D367" t="s">
         <v>12</v>
@@ -12710,13 +12713,13 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C368" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D368" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F368" t="s">
         <v>13</v>
@@ -12733,10 +12736,10 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C369" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D369" t="s">
         <v>12</v>
@@ -12756,10 +12759,10 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C370" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D370" t="s">
         <v>29</v>
@@ -12779,16 +12782,16 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C371" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D371" t="s">
         <v>152</v>
       </c>
       <c r="F371" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G371" t="s">
         <v>14</v>
@@ -12802,16 +12805,16 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C372" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D372" t="s">
         <v>193</v>
       </c>
       <c r="F372" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G372" t="s">
         <v>14</v>
@@ -12825,10 +12828,10 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C373" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D373" t="s">
         <v>101</v>
@@ -12848,10 +12851,10 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C374" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D374" t="s">
         <v>101</v>
@@ -12871,10 +12874,10 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C375" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D375" t="s">
         <v>12</v>
@@ -12894,10 +12897,10 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C376" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D376" t="s">
         <v>12</v>
@@ -12917,10 +12920,10 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C377" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D377" t="s">
         <v>12</v>
@@ -12940,10 +12943,10 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C378" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D378" t="s">
         <v>101</v>
@@ -12966,13 +12969,13 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C379" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D379" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F379" t="s">
         <v>35</v>
@@ -12989,13 +12992,13 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B380" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C380" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D380" t="s">
         <v>101</v>
@@ -13015,16 +13018,16 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C381" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D381" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F381" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G381" t="s">
         <v>14</v>
@@ -13038,13 +13041,13 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C382" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D382" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F382" t="s">
         <v>60</v>
@@ -13061,10 +13064,10 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C383" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D383" t="s">
         <v>544</v>
@@ -13084,10 +13087,10 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C384" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D384" t="s">
         <v>544</v>
@@ -13107,16 +13110,16 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C385" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D385" t="s">
         <v>544</v>
       </c>
       <c r="F385" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G385" t="s">
         <v>14</v>
@@ -13130,10 +13133,10 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C386" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D386" t="s">
         <v>544</v>
@@ -13153,10 +13156,10 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C387" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D387" t="s">
         <v>544</v>
@@ -13176,13 +13179,13 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C388" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D388" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F388" t="s">
         <v>13</v>
@@ -13199,10 +13202,10 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C389" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D389" t="s">
         <v>29</v>
@@ -13222,16 +13225,16 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C390" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D390" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E390" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F390" t="s">
         <v>13</v>
@@ -13248,16 +13251,16 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C391" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D391" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E391" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F391" t="s">
         <v>18</v>
@@ -13274,13 +13277,13 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C392" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D392" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F392" t="s">
         <v>13</v>
@@ -13297,13 +13300,13 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C393" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D393" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F393" t="s">
         <v>13</v>
@@ -13320,10 +13323,10 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C394" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D394" t="s">
         <v>680</v>
@@ -13343,16 +13346,16 @@
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C395" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D395" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F395" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G395" t="s">
         <v>14</v>
@@ -13366,13 +13369,13 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C396" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D396" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F396" t="s">
         <v>35</v>
@@ -13389,10 +13392,10 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C397" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D397" t="s">
         <v>12</v>
@@ -13412,10 +13415,10 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C398" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D398" t="s">
         <v>101</v>
@@ -13435,13 +13438,13 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C399" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D399" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F399" t="s">
         <v>13</v>
@@ -13458,13 +13461,13 @@
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C400" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D400" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F400" t="s">
         <v>366</v>
@@ -13481,13 +13484,13 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C401" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D401" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F401" t="s">
         <v>35</v>
@@ -13504,16 +13507,16 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C402" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D402" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E402" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F402" t="s">
         <v>35</v>
@@ -13530,13 +13533,13 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C403" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D403" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F403" t="s">
         <v>35</v>
@@ -13553,16 +13556,16 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C404" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D404" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F404" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G404" t="s">
         <v>14</v>
@@ -13576,10 +13579,10 @@
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C405" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D405" t="s">
         <v>131</v>
@@ -13599,16 +13602,16 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C406" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D406" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F406" t="s">
-        <v>530</v>
+        <v>702</v>
       </c>
       <c r="G406" t="s">
         <v>14</v>
@@ -13622,16 +13625,16 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C407" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D407" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E407" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F407" t="s">
         <v>13</v>
@@ -13648,19 +13651,19 @@
     </row>
     <row r="408" spans="1:9">
       <c r="A408" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B408" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C408" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D408" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E408" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F408" t="s">
         <v>35</v>
@@ -13677,19 +13680,19 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
+        <v>836</v>
+      </c>
+      <c r="B409" t="s">
         <v>835</v>
       </c>
-      <c r="B409" t="s">
-        <v>834</v>
-      </c>
       <c r="C409" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D409" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E409" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F409" t="s">
         <v>35</v>
@@ -13706,16 +13709,16 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
+        <v>836</v>
+      </c>
+      <c r="B410" t="s">
         <v>835</v>
       </c>
-      <c r="B410" t="s">
-        <v>834</v>
-      </c>
       <c r="C410" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D410" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F410" t="s">
         <v>35</v>
@@ -13732,16 +13735,16 @@
     </row>
     <row r="411" spans="1:9">
       <c r="A411" t="s">
+        <v>836</v>
+      </c>
+      <c r="B411" t="s">
         <v>835</v>
       </c>
-      <c r="B411" t="s">
-        <v>834</v>
-      </c>
       <c r="C411" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D411" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F411" t="s">
         <v>35</v>
@@ -13758,13 +13761,13 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C412" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D412" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F412" t="s">
         <v>24</v>
@@ -13781,13 +13784,13 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C413" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D413" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F413" t="s">
         <v>13</v>
@@ -13804,13 +13807,13 @@
     </row>
     <row r="414" spans="1:9">
       <c r="A414" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C414" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D414" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F414" t="s">
         <v>434</v>
@@ -13827,10 +13830,10 @@
     </row>
     <row r="415" spans="1:9">
       <c r="A415" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C415" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D415" t="s">
         <v>204</v>
@@ -13850,10 +13853,10 @@
     </row>
     <row r="416" spans="1:9">
       <c r="A416" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C416" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D416" t="s">
         <v>12</v>
@@ -13873,19 +13876,19 @@
     </row>
     <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C417" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D417" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E417" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F417" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
@@ -13899,10 +13902,10 @@
     </row>
     <row r="418" spans="1:9">
       <c r="A418" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C418" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D418" t="s">
         <v>101</v>
@@ -13922,10 +13925,10 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C419" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D419" t="s">
         <v>101</v>
@@ -13945,10 +13948,10 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C420" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D420" t="s">
         <v>29</v>
@@ -13968,10 +13971,10 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C421" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D421" t="s">
         <v>12</v>
@@ -13991,10 +13994,10 @@
     </row>
     <row r="422" spans="1:9">
       <c r="A422" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C422" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D422" t="s">
         <v>34</v>
@@ -14014,10 +14017,10 @@
     </row>
     <row r="423" spans="1:9">
       <c r="A423" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C423" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D423" t="s">
         <v>34</v>
@@ -14037,10 +14040,10 @@
     </row>
     <row r="424" spans="1:9">
       <c r="A424" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C424" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D424" t="s">
         <v>12</v>
@@ -14060,13 +14063,13 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C425" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D425" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F425" t="s">
         <v>13</v>
@@ -14083,10 +14086,10 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C426" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D426" t="s">
         <v>101</v>
@@ -14106,13 +14109,13 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C427" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D427" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F427" t="s">
         <v>24</v>
@@ -14129,13 +14132,13 @@
     </row>
     <row r="428" spans="1:9">
       <c r="A428" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C428" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D428" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F428" t="s">
         <v>13</v>
@@ -14152,13 +14155,13 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C429" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D429" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F429" t="s">
         <v>18</v>
@@ -14175,13 +14178,13 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C430" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D430" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F430" t="s">
         <v>22</v>
@@ -14198,16 +14201,16 @@
     </row>
     <row r="431" spans="1:9">
       <c r="A431" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C431" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D431" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E431" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F431" t="s">
         <v>19</v>
@@ -14224,13 +14227,13 @@
     </row>
     <row r="432" spans="1:9">
       <c r="A432" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C432" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D432" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F432" t="s">
         <v>24</v>
@@ -14247,16 +14250,16 @@
     </row>
     <row r="433" spans="1:9">
       <c r="A433" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C433" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D433" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E433" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F433" t="s">
         <v>24</v>
@@ -14273,13 +14276,13 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C434" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D434" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F434" t="s">
         <v>13</v>
@@ -14296,10 +14299,10 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C435" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D435" t="s">
         <v>12</v>
@@ -14319,16 +14322,16 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C436" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D436" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F436" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G436" t="s">
         <v>14</v>
@@ -14342,13 +14345,13 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C437" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D437" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F437" t="s">
         <v>13</v>
@@ -14365,13 +14368,13 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C438" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D438" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F438" t="s">
         <v>141</v>
@@ -14388,16 +14391,16 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C439" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D439" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E439" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F439" t="s">
         <v>141</v>
@@ -14414,16 +14417,16 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C440" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D440" t="s">
         <v>262</v>
       </c>
       <c r="E440" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F440" t="s">
         <v>141</v>
@@ -14440,10 +14443,10 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C441" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D441" t="s">
         <v>262</v>
@@ -14463,10 +14466,10 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C442" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D442" t="s">
         <v>262</v>
@@ -14486,13 +14489,13 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C443" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D443" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F443" t="s">
         <v>251</v>
@@ -14509,13 +14512,13 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C444" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D444" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F444" t="s">
         <v>251</v>
@@ -14532,10 +14535,10 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C445" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D445" t="s">
         <v>12</v>
@@ -14555,10 +14558,10 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C446" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D446" t="s">
         <v>29</v>
@@ -14578,10 +14581,10 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C447" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D447" t="s">
         <v>29</v>
@@ -14601,10 +14604,10 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C448" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D448" t="s">
         <v>29</v>
@@ -14624,13 +14627,13 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C449" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D449" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F449" t="s">
         <v>189</v>
@@ -14647,10 +14650,10 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C450" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D450" t="s">
         <v>12</v>
@@ -14670,10 +14673,10 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C451" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D451" t="s">
         <v>12</v>
@@ -14693,10 +14696,10 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C452" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D452" t="s">
         <v>12</v>
@@ -14716,13 +14719,13 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C453" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D453" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F453" t="s">
         <v>24</v>
@@ -14739,13 +14742,13 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C454" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D454" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F454" t="s">
         <v>18</v>
@@ -14762,10 +14765,10 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C455" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D455" t="s">
         <v>631</v>
@@ -14785,16 +14788,16 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C456" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D456" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F456" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G456" t="s">
         <v>14</v>
@@ -14808,13 +14811,13 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C457" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D457" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F457" t="s">
         <v>205</v>
@@ -14831,16 +14834,16 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C458" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D458" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F458" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G458" t="s">
         <v>14</v>
@@ -14854,16 +14857,16 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C459" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D459" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F459" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G459" t="s">
         <v>14</v>
@@ -14877,13 +14880,13 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C460" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D460" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F460" t="s">
         <v>19</v>
@@ -14900,10 +14903,10 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C461" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D461" t="s">
         <v>596</v>
@@ -14923,10 +14926,10 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C462" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D462" t="s">
         <v>596</v>
@@ -14946,13 +14949,13 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C463" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D463" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F463" t="s">
         <v>35</v>
@@ -14969,10 +14972,10 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C464" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D464" t="s">
         <v>39</v>
@@ -14992,10 +14995,10 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C465" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D465" t="s">
         <v>39</v>
@@ -15015,16 +15018,16 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C466" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D466" t="s">
         <v>39</v>
       </c>
       <c r="F466" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G466" t="s">
         <v>14</v>
@@ -15038,16 +15041,16 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B467" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C467" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D467" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F467" t="s">
         <v>18</v>
@@ -15064,16 +15067,16 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B468" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C468" t="s">
+        <v>959</v>
+      </c>
+      <c r="D468" t="s">
         <v>958</v>
-      </c>
-      <c r="D468" t="s">
-        <v>957</v>
       </c>
       <c r="F468" t="s">
         <v>126</v>
@@ -15090,16 +15093,16 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B469" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C469" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D469" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F469" t="s">
         <v>13</v>
@@ -15116,16 +15119,16 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B470" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C470" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D470" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F470" t="s">
         <v>452</v>
@@ -15142,10 +15145,10 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C471" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D471" t="s">
         <v>105</v>
@@ -15165,16 +15168,16 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C472" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D472" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E472" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F472" t="s">
         <v>13</v>
@@ -15191,10 +15194,10 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C473" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D473" t="s">
         <v>12</v>
@@ -15214,10 +15217,10 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C474" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D474" t="s">
         <v>152</v>
@@ -15237,7 +15240,7 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C475" t="s">
         <v>281</v>
@@ -15260,7 +15263,7 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C476" t="s">
         <v>281</v>
@@ -15269,7 +15272,7 @@
         <v>226</v>
       </c>
       <c r="F476" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G476" t="s">
         <v>14</v>
@@ -15283,7 +15286,7 @@
     </row>
     <row r="477" spans="1:9">
       <c r="A477" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C477" t="s">
         <v>281</v>
@@ -15292,7 +15295,7 @@
         <v>226</v>
       </c>
       <c r="F477" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G477" t="s">
         <v>14</v>
@@ -15306,16 +15309,16 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C478" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D478" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F478" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G478" t="s">
         <v>14</v>
@@ -15329,13 +15332,13 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C479" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D479" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F479" t="s">
         <v>331</v>
@@ -15352,16 +15355,16 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C480" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D480" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F480" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G480" t="s">
         <v>14</v>
@@ -15375,16 +15378,16 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C481" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D481" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F481" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G481" t="s">
         <v>14</v>
@@ -15398,10 +15401,10 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C482" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D482" t="s">
         <v>101</v>
@@ -15421,16 +15424,16 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C483" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D483" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F483" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G483" t="s">
         <v>14</v>
@@ -15444,16 +15447,16 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B484" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C484" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D484" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F484" t="s">
         <v>22</v>
@@ -15470,16 +15473,16 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B485" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C485" t="s">
+        <v>994</v>
+      </c>
+      <c r="D485" t="s">
         <v>993</v>
-      </c>
-      <c r="D485" t="s">
-        <v>992</v>
       </c>
       <c r="F485" t="s">
         <v>30</v>
@@ -15496,10 +15499,10 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C486" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D486" t="s">
         <v>211</v>
@@ -15519,10 +15522,10 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C487" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D487" t="s">
         <v>219</v>
@@ -15542,10 +15545,10 @@
     </row>
     <row r="488" spans="1:9">
       <c r="A488" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C488" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D488" t="s">
         <v>219</v>
@@ -15565,13 +15568,13 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C489" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D489" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F489" t="s">
         <v>24</v>
@@ -15588,16 +15591,16 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B490" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C490" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D490" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F490" t="s">
         <v>22</v>
@@ -15614,10 +15617,10 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C491" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D491" t="s">
         <v>101</v>
@@ -15637,10 +15640,10 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C492" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D492" t="s">
         <v>39</v>
@@ -15660,10 +15663,10 @@
     </row>
     <row r="493" spans="1:9">
       <c r="A493" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C493" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D493" t="s">
         <v>39</v>
@@ -15683,10 +15686,10 @@
     </row>
     <row r="494" spans="1:9">
       <c r="A494" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C494" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D494" t="s">
         <v>39</v>
@@ -15706,10 +15709,10 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C495" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D495" t="s">
         <v>12</v>
@@ -15729,10 +15732,10 @@
     </row>
     <row r="496" spans="1:9">
       <c r="A496" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C496" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D496" t="s">
         <v>493</v>
@@ -15752,16 +15755,16 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C497" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D497" t="s">
         <v>12</v>
       </c>
       <c r="F497" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G497" t="s">
         <v>14</v>
@@ -15775,13 +15778,13 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C498" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D498" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F498" t="s">
         <v>19</v>
@@ -15798,10 +15801,10 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C499" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D499" t="s">
         <v>29</v>
@@ -15821,16 +15824,16 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C500" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D500" t="s">
         <v>12</v>
       </c>
       <c r="F500" t="s">
-        <v>530</v>
+        <v>702</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
@@ -15844,13 +15847,13 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C501" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D501" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F501" t="s">
         <v>13</v>
@@ -15867,10 +15870,10 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C502" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D502" t="s">
         <v>211</v>
@@ -15890,10 +15893,10 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C503" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D503" t="s">
         <v>500</v>
@@ -15913,10 +15916,10 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C504" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D504" t="s">
         <v>500</v>
@@ -15936,13 +15939,13 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C505" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D505" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F505" t="s">
         <v>35</v>
@@ -15959,13 +15962,13 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C506" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D506" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F506" t="s">
         <v>24</v>
@@ -15982,10 +15985,10 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C507" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D507" t="s">
         <v>12</v>
@@ -16005,10 +16008,10 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C508" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D508" t="s">
         <v>34</v>
@@ -16028,10 +16031,10 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C509" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D509" t="s">
         <v>211</v>
@@ -16051,16 +16054,16 @@
     </row>
     <row r="510" spans="1:9">
       <c r="A510" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C510" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D510" t="s">
         <v>211</v>
       </c>
       <c r="F510" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G510" t="s">
         <v>14</v>
@@ -16074,10 +16077,10 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C511" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D511" t="s">
         <v>12</v>
@@ -16097,13 +16100,13 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C512" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D512" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F512" t="s">
         <v>42</v>
@@ -16120,10 +16123,10 @@
     </row>
     <row r="513" spans="1:9">
       <c r="A513" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C513" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D513" t="s">
         <v>377</v>
@@ -16143,13 +16146,13 @@
     </row>
     <row r="514" spans="1:9">
       <c r="A514" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C514" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D514" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F514" t="s">
         <v>22</v>
@@ -16166,16 +16169,16 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C515" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D515" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F515" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G515" t="s">
         <v>14</v>
@@ -16189,10 +16192,10 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C516" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D516" t="s">
         <v>101</v>
@@ -16212,13 +16215,13 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C517" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D517" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F517" t="s">
         <v>24</v>
@@ -16235,13 +16238,13 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C518" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D518" t="s">
         <v>1064</v>
-      </c>
-      <c r="D518" t="s">
-        <v>1063</v>
       </c>
       <c r="F518" t="s">
         <v>13</v>
@@ -16258,16 +16261,16 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C519" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D519" t="s">
         <v>290</v>
       </c>
       <c r="E519" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F519" t="s">
         <v>22</v>
@@ -16284,19 +16287,19 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C520" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D520" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E520" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F520" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G520" t="s">
         <v>14</v>
@@ -16310,16 +16313,16 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C521" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D521" t="s">
         <v>149</v>
       </c>
       <c r="E521" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F521" t="s">
         <v>60</v>
@@ -16336,19 +16339,19 @@
     </row>
     <row r="522" spans="1:9">
       <c r="A522" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C522" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D522" t="s">
         <v>149</v>
       </c>
       <c r="E522" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F522" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
@@ -16362,7 +16365,7 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C523" t="s">
         <v>162</v>
@@ -16388,16 +16391,16 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C524" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D524" t="s">
         <v>101</v>
       </c>
       <c r="E524" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F524" t="s">
         <v>22</v>
@@ -16414,16 +16417,16 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C525" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D525" t="s">
         <v>211</v>
       </c>
       <c r="E525" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F525" t="s">
         <v>13</v>
@@ -16440,16 +16443,16 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C526" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D526" t="s">
         <v>211</v>
       </c>
       <c r="E526" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F526" t="s">
         <v>13</v>
@@ -16466,16 +16469,16 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C527" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D527" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E527" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F527" t="s">
         <v>13</v>
@@ -16492,13 +16495,13 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C528" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D528" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F528" t="s">
         <v>13</v>
@@ -16515,16 +16518,16 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C529" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D529" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E529" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F529" t="s">
         <v>13</v>
@@ -16541,13 +16544,13 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C530" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D530" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F530" t="s">
         <v>13</v>
@@ -16564,16 +16567,16 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C531" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D531" t="s">
         <v>54</v>
       </c>
       <c r="E531" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F531" t="s">
         <v>13</v>
@@ -16590,10 +16593,10 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C532" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D532" t="s">
         <v>334</v>
@@ -16613,13 +16616,13 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C533" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D533" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F533" t="s">
         <v>22</v>
@@ -16636,13 +16639,13 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C534" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D534" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F534" t="s">
         <v>205</v>
@@ -16659,13 +16662,13 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C535" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D535" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F535" t="s">
         <v>13</v>
@@ -16682,10 +16685,10 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C536" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D536" t="s">
         <v>101</v>
@@ -16705,10 +16708,10 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C537" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D537" t="s">
         <v>12</v>
@@ -16728,10 +16731,10 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C538" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D538" t="s">
         <v>12</v>
@@ -16751,10 +16754,10 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C539" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D539" t="s">
         <v>12</v>
@@ -16774,10 +16777,10 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C540" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D540" t="s">
         <v>12</v>
@@ -16797,10 +16800,10 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C541" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D541" t="s">
         <v>12</v>
@@ -16820,10 +16823,10 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C542" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D542" t="s">
         <v>250</v>
@@ -16843,10 +16846,10 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C543" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D543" t="s">
         <v>250</v>
@@ -16866,10 +16869,10 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C544" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D544" t="s">
         <v>80</v>
@@ -16889,13 +16892,13 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C545" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D545" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F545" t="s">
         <v>35</v>
@@ -16912,13 +16915,13 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C546" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D546" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F546" t="s">
         <v>35</v>
@@ -16935,13 +16938,13 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C547" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D547" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F547" t="s">
         <v>35</v>
@@ -16958,13 +16961,13 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C548" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D548" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F548" t="s">
         <v>18</v>
@@ -16981,13 +16984,13 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C549" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D549" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F549" t="s">
         <v>19</v>
@@ -17004,16 +17007,16 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C550" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D550" t="s">
         <v>12</v>
       </c>
       <c r="F550" t="s">
-        <v>530</v>
+        <v>702</v>
       </c>
       <c r="G550" t="s">
         <v>14</v>
@@ -17027,10 +17030,10 @@
     </row>
     <row r="551" spans="1:9">
       <c r="A551" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C551" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D551" t="s">
         <v>12</v>
@@ -17050,10 +17053,10 @@
     </row>
     <row r="552" spans="1:9">
       <c r="A552" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C552" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D552" t="s">
         <v>29</v>
@@ -17073,10 +17076,10 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C553" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D553" t="s">
         <v>29</v>
@@ -17096,10 +17099,10 @@
     </row>
     <row r="554" spans="1:9">
       <c r="A554" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C554" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D554" t="s">
         <v>101</v>
@@ -17119,13 +17122,13 @@
     </row>
     <row r="555" spans="1:9">
       <c r="A555" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C555" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D555" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F555" t="s">
         <v>189</v>
@@ -17142,13 +17145,13 @@
     </row>
     <row r="556" spans="1:9">
       <c r="A556" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C556" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D556" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F556" t="s">
         <v>42</v>
@@ -17165,10 +17168,10 @@
     </row>
     <row r="557" spans="1:9">
       <c r="A557" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C557" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D557" t="s">
         <v>29</v>
@@ -17188,10 +17191,10 @@
     </row>
     <row r="558" spans="1:9">
       <c r="A558" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C558" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D558" t="s">
         <v>101</v>
@@ -17211,10 +17214,10 @@
     </row>
     <row r="559" spans="1:9">
       <c r="A559" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C559" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D559" t="s">
         <v>12</v>
@@ -17234,13 +17237,13 @@
     </row>
     <row r="560" spans="1:9">
       <c r="A560" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C560" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D560" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F560" t="s">
         <v>22</v>
@@ -17257,16 +17260,16 @@
     </row>
     <row r="561" spans="1:9">
       <c r="A561" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C561" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D561" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E561" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F561" t="s">
         <v>13</v>
@@ -17283,16 +17286,16 @@
     </row>
     <row r="562" spans="1:9">
       <c r="A562" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B562" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C562" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D562" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F562" t="s">
         <v>22</v>
@@ -17309,16 +17312,16 @@
     </row>
     <row r="563" spans="1:9">
       <c r="A563" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B563" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C563" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D563" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F563" t="s">
         <v>22</v>
@@ -17335,16 +17338,16 @@
     </row>
     <row r="564" spans="1:9">
       <c r="A564" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B564" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C564" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D564" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F564" t="s">
         <v>60</v>
@@ -17361,13 +17364,13 @@
     </row>
     <row r="565" spans="1:9">
       <c r="A565" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C565" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D565" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F565" t="s">
         <v>18</v>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -2101,7 +2101,7 @@
     <t>GESCON</t>
   </si>
   <si>
-    <t>WEB</t>
+    <t>WEB, lite</t>
   </si>
   <si>
     <t>INFOSYS SRL</t>
@@ -2686,7 +2686,7 @@
     <t>7.0.0</t>
   </si>
   <si>
-    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31</t>
+    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31, 7.51.9, 8.2.32, 8.2.33, 8.2.34</t>
   </si>
   <si>
     <t>cis</t>
@@ -3814,7 +3814,7 @@
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="1035.7109375" customWidth="1"/>
+    <col min="5" max="5" width="1067.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="9" width="16.7109375" customWidth="1"/>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -2113,7 +2113,7 @@
     <t>GESCON</t>
   </si>
   <si>
-    <t>WEB, lite</t>
+    <t>WEB, LITE</t>
   </si>
   <si>
     <t>INFOSYS SRL</t>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -583,7 +583,7 @@
     <t>10.6</t>
   </si>
   <si>
-    <t>10.7, 10.8, 10.9, 12.1, 12.2, 12.3, 12.4, 12.6, 12.7, 12.8</t>
+    <t>10.7, 10.8, 10.9, 12.1, 12.2, 12.3, 12.4, 12.6, 12.7, 12.8, 12.9</t>
   </si>
   <si>
     <t>Blaissed S.r.l.</t>
@@ -1606,10 +1606,10 @@
     <t>1.6</t>
   </si>
   <si>
-    <t>2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1</t>
-  </si>
-  <si>
-    <t>2.0.0, 2.1.0, 2.1.1, 2.1.2, 2.1.2.1, 2.1.2.2, 2.1.2.3, 2.1.3, 2.1.3.1, 2.1.4, 2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1</t>
+    <t>2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1, 2.1.7.2</t>
+  </si>
+  <si>
+    <t>2.0.0, 2.1.0, 2.1.1, 2.1.2, 2.1.2.1, 2.1.2.2, 2.1.2.3, 2.1.3, 2.1.3.1, 2.1.4, 2.1.5, 2.1.5.1, 2.1.6.0, 2.1.7.0, 2.1.7.1, 2.1.7.2</t>
   </si>
   <si>
     <t>Synapse Workflow</t>
@@ -2257,7 +2257,7 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>13.0.0, 13.0.1, 13.0.2, 13.0.3, 13.0.4, 13.0.5, 13.0.6, 13.0.7</t>
+    <t>13.0.0, 13.0.1, 13.0.2, 13.0.3, 13.0.4, 13.0.5, 13.0.6, 13.0.7, 13.0.8</t>
   </si>
   <si>
     <t>KG Partners s.r.l.</t>
@@ -2722,7 +2722,7 @@
     <t>7.0.0</t>
   </si>
   <si>
-    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31, 7.51.9, 8.2.32, 8.2.33, 8.2.34</t>
+    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31, 7.51.9, 8.2.32, 8.2.33, 8.2.34, 8.2.35</t>
   </si>
   <si>
     <t>cis</t>
@@ -3850,7 +3850,7 @@
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="1067.7109375" customWidth="1"/>
+    <col min="5" max="5" width="1075.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="9" width="16.7109375" customWidth="1"/>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -1087,7 +1087,7 @@
     <t>6.4</t>
   </si>
   <si>
-    <t>6.5, 6.6</t>
+    <t>6.5, 6.6, 6.7, 6.8</t>
   </si>
   <si>
     <t>22.1.1</t>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3638" uniqueCount="1167">
   <si>
     <t>Fornitore</t>
   </si>
@@ -2761,6 +2761,9 @@
     <t>OnitGroup</t>
   </si>
   <si>
+    <t>Onit Sanita</t>
+  </si>
+  <si>
     <t>OnVac</t>
   </si>
   <si>
@@ -2788,9 +2791,6 @@
     <t>SIAMA</t>
   </si>
   <si>
-    <t>Onit Sanita</t>
-  </si>
-  <si>
     <t>Klinika</t>
   </si>
   <si>
@@ -3176,6 +3176,9 @@
   </si>
   <si>
     <t>STI srl</t>
+  </si>
+  <si>
+    <t>INSIGHT by NG</t>
   </si>
   <si>
     <t>IGEA</t>
@@ -14547,11 +14550,14 @@
       <c r="A444" t="s">
         <v>914</v>
       </c>
+      <c r="B444" t="s">
+        <v>915</v>
+      </c>
       <c r="C444" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D444" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F444" t="s">
         <v>144</v>
@@ -14570,14 +14576,17 @@
       <c r="A445" t="s">
         <v>914</v>
       </c>
+      <c r="B445" t="s">
+        <v>915</v>
+      </c>
       <c r="C445" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D445" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E445" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F445" t="s">
         <v>144</v>
@@ -14596,14 +14605,17 @@
       <c r="A446" t="s">
         <v>914</v>
       </c>
+      <c r="B446" t="s">
+        <v>915</v>
+      </c>
       <c r="C446" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D446" t="s">
         <v>273</v>
       </c>
       <c r="E446" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F446" t="s">
         <v>144</v>
@@ -14622,8 +14634,11 @@
       <c r="A447" t="s">
         <v>914</v>
       </c>
+      <c r="B447" t="s">
+        <v>915</v>
+      </c>
       <c r="C447" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D447" t="s">
         <v>273</v>
@@ -14645,8 +14660,11 @@
       <c r="A448" t="s">
         <v>914</v>
       </c>
+      <c r="B448" t="s">
+        <v>915</v>
+      </c>
       <c r="C448" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D448" t="s">
         <v>273</v>
@@ -14666,7 +14684,10 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>924</v>
+        <v>915</v>
+      </c>
+      <c r="B449" t="s">
+        <v>914</v>
       </c>
       <c r="C449" t="s">
         <v>925</v>
@@ -14689,7 +14710,10 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>924</v>
+        <v>915</v>
+      </c>
+      <c r="B450" t="s">
+        <v>914</v>
       </c>
       <c r="C450" t="s">
         <v>926</v>
@@ -16210,8 +16234,11 @@
       <c r="A515" t="s">
         <v>1053</v>
       </c>
+      <c r="B515" t="s">
+        <v>1054</v>
+      </c>
       <c r="C515" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D515" t="s">
         <v>34</v>
@@ -16231,10 +16258,10 @@
     </row>
     <row r="516" spans="1:9">
       <c r="A516" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C516" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D516" t="s">
         <v>217</v>
@@ -16254,16 +16281,16 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C517" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D517" t="s">
         <v>217</v>
       </c>
       <c r="F517" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G517" t="s">
         <v>14</v>
@@ -16277,10 +16304,10 @@
     </row>
     <row r="518" spans="1:9">
       <c r="A518" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C518" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D518" t="s">
         <v>12</v>
@@ -16300,13 +16327,13 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C519" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D519" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F519" t="s">
         <v>42</v>
@@ -16323,10 +16350,10 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C520" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D520" t="s">
         <v>388</v>
@@ -16346,13 +16373,13 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C521" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D521" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F521" t="s">
         <v>22</v>
@@ -16369,16 +16396,16 @@
     </row>
     <row r="522" spans="1:9">
       <c r="A522" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C522" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D522" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F522" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
@@ -16392,10 +16419,10 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C523" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D523" t="s">
         <v>104</v>
@@ -16415,13 +16442,13 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C524" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D524" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F524" t="s">
         <v>24</v>
@@ -16438,13 +16465,13 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C525" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D525" t="s">
         <v>1077</v>
-      </c>
-      <c r="D525" t="s">
-        <v>1076</v>
       </c>
       <c r="F525" t="s">
         <v>13</v>
@@ -16461,16 +16488,16 @@
     </row>
     <row r="526" spans="1:9">
       <c r="A526" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C526" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D526" t="s">
         <v>301</v>
       </c>
       <c r="E526" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F526" t="s">
         <v>22</v>
@@ -16487,19 +16514,19 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C527" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D527" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E527" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F527" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
@@ -16513,16 +16540,16 @@
     </row>
     <row r="528" spans="1:9">
       <c r="A528" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C528" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D528" t="s">
         <v>155</v>
       </c>
       <c r="E528" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F528" t="s">
         <v>60</v>
@@ -16539,19 +16566,19 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C529" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D529" t="s">
         <v>155</v>
       </c>
       <c r="E529" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F529" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G529" t="s">
         <v>14</v>
@@ -16565,7 +16592,7 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C530" t="s">
         <v>168</v>
@@ -16591,16 +16618,16 @@
     </row>
     <row r="531" spans="1:9">
       <c r="A531" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C531" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D531" t="s">
         <v>104</v>
       </c>
       <c r="E531" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F531" t="s">
         <v>22</v>
@@ -16617,16 +16644,16 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C532" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D532" t="s">
         <v>217</v>
       </c>
       <c r="E532" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F532" t="s">
         <v>13</v>
@@ -16643,16 +16670,16 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C533" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D533" t="s">
         <v>217</v>
       </c>
       <c r="E533" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F533" t="s">
         <v>13</v>
@@ -16669,16 +16696,16 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C534" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D534" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E534" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F534" t="s">
         <v>13</v>
@@ -16695,13 +16722,13 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C535" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D535" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F535" t="s">
         <v>13</v>
@@ -16718,16 +16745,16 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C536" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D536" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E536" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F536" t="s">
         <v>13</v>
@@ -16744,13 +16771,13 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C537" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D537" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F537" t="s">
         <v>13</v>
@@ -16767,16 +16794,16 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C538" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D538" t="s">
         <v>54</v>
       </c>
       <c r="E538" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F538" t="s">
         <v>13</v>
@@ -16793,10 +16820,10 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C539" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D539" t="s">
         <v>345</v>
@@ -16816,13 +16843,13 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C540" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D540" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F540" t="s">
         <v>22</v>
@@ -16839,13 +16866,13 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C541" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D541" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F541" t="s">
         <v>211</v>
@@ -16862,13 +16889,13 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C542" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D542" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F542" t="s">
         <v>13</v>
@@ -16885,10 +16912,10 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C543" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D543" t="s">
         <v>104</v>
@@ -16908,10 +16935,10 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C544" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D544" t="s">
         <v>12</v>
@@ -16931,10 +16958,10 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C545" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D545" t="s">
         <v>12</v>
@@ -16954,10 +16981,10 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C546" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D546" t="s">
         <v>12</v>
@@ -16977,10 +17004,10 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C547" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D547" t="s">
         <v>12</v>
@@ -17000,10 +17027,10 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C548" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D548" t="s">
         <v>12</v>
@@ -17023,10 +17050,10 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C549" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D549" t="s">
         <v>261</v>
@@ -17046,10 +17073,10 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C550" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D550" t="s">
         <v>261</v>
@@ -17069,10 +17096,10 @@
     </row>
     <row r="551" spans="1:9">
       <c r="A551" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C551" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D551" t="s">
         <v>83</v>
@@ -17092,13 +17119,13 @@
     </row>
     <row r="552" spans="1:9">
       <c r="A552" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C552" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D552" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F552" t="s">
         <v>35</v>
@@ -17115,10 +17142,10 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C553" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D553" t="s">
         <v>388</v>
@@ -17138,13 +17165,13 @@
     </row>
     <row r="554" spans="1:9">
       <c r="A554" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C554" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D554" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F554" t="s">
         <v>35</v>
@@ -17161,13 +17188,13 @@
     </row>
     <row r="555" spans="1:9">
       <c r="A555" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C555" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D555" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F555" t="s">
         <v>35</v>
@@ -17184,13 +17211,13 @@
     </row>
     <row r="556" spans="1:9">
       <c r="A556" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C556" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D556" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F556" t="s">
         <v>18</v>
@@ -17207,13 +17234,13 @@
     </row>
     <row r="557" spans="1:9">
       <c r="A557" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C557" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D557" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F557" t="s">
         <v>19</v>
@@ -17230,10 +17257,10 @@
     </row>
     <row r="558" spans="1:9">
       <c r="A558" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C558" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D558" t="s">
         <v>12</v>
@@ -17253,10 +17280,10 @@
     </row>
     <row r="559" spans="1:9">
       <c r="A559" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C559" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D559" t="s">
         <v>12</v>
@@ -17276,10 +17303,10 @@
     </row>
     <row r="560" spans="1:9">
       <c r="A560" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C560" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D560" t="s">
         <v>29</v>
@@ -17299,10 +17326,10 @@
     </row>
     <row r="561" spans="1:9">
       <c r="A561" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C561" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D561" t="s">
         <v>29</v>
@@ -17322,10 +17349,10 @@
     </row>
     <row r="562" spans="1:9">
       <c r="A562" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C562" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D562" t="s">
         <v>104</v>
@@ -17345,13 +17372,13 @@
     </row>
     <row r="563" spans="1:9">
       <c r="A563" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C563" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D563" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F563" t="s">
         <v>195</v>
@@ -17368,13 +17395,13 @@
     </row>
     <row r="564" spans="1:9">
       <c r="A564" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C564" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D564" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F564" t="s">
         <v>42</v>
@@ -17391,10 +17418,10 @@
     </row>
     <row r="565" spans="1:9">
       <c r="A565" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C565" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D565" t="s">
         <v>29</v>
@@ -17414,10 +17441,10 @@
     </row>
     <row r="566" spans="1:9">
       <c r="A566" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C566" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D566" t="s">
         <v>104</v>
@@ -17437,10 +17464,10 @@
     </row>
     <row r="567" spans="1:9">
       <c r="A567" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C567" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D567" t="s">
         <v>12</v>
@@ -17460,13 +17487,13 @@
     </row>
     <row r="568" spans="1:9">
       <c r="A568" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C568" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D568" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F568" t="s">
         <v>22</v>
@@ -17483,16 +17510,16 @@
     </row>
     <row r="569" spans="1:9">
       <c r="A569" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C569" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D569" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E569" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F569" t="s">
         <v>13</v>
@@ -17509,16 +17536,16 @@
     </row>
     <row r="570" spans="1:9">
       <c r="A570" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B570" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C570" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D570" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="F570" t="s">
         <v>22</v>
@@ -17535,16 +17562,16 @@
     </row>
     <row r="571" spans="1:9">
       <c r="A571" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B571" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C571" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D571" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F571" t="s">
         <v>22</v>
@@ -17561,16 +17588,16 @@
     </row>
     <row r="572" spans="1:9">
       <c r="A572" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B572" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C572" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D572" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F572" t="s">
         <v>60</v>
@@ -17587,13 +17614,13 @@
     </row>
     <row r="573" spans="1:9">
       <c r="A573" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C573" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D573" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F573" t="s">
         <v>18</v>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -2722,7 +2722,7 @@
     <t>7.0.0</t>
   </si>
   <si>
-    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31, 7.51.9, 8.2.32, 8.2.33, 8.2.34, 8.2.35</t>
+    <t>7.37.2, 7.37.3, 7.37.4, 7.38.0, 7.38.1, 7.38.2, 7.38.3, 7.38.4, 7.38.5, 7.38.6, 7.38.7, 7.38.8, 7.39.0, 7.39.1, 7.39.2, 7.39.3, 7.40.0, 7.40.1, 7.41.0, 7.41.1, 7.41.2, 7.41.3, 7.41.4, 7.42.0, 7.42.1, 7.42.2, 7.42.3, 7.42.4, 7.43.0, 7.43.1, 7.43.2, 7.43.3, 7.43.4, 7.43.5, 7.43.6, 7.43.7, 7.44.0, 7.44.1, 7.44.2, 7.45.0, 7.45.1, 7.45.2, 7.45.3, 7.45.4, 7.45.5, 7.46.0, 7.46.1, 7.46.2, 7.46.3, 7.47.0, 7.47.1, 7.47.2, 7.47.3, 8.1.1-pr.1, 7.47.4, 7.48.0, 7.48.1, 7.48.2, 8.1.0, 7.48.3, 8.1.1, 8.1.2, 8.1.3, 8.1.4, 8.1.5, 7.48.4, 8.1.6, 7.48.5, 7.48.6, 7.48.7, 7.48.8, 7.48.9, 7.48.10, 8.1.7, 7.48.11, 8.1.8, 8.1.9, 8.1.10, 7.48.12, 7.48.13, 7.48.14, 7.49.0, 8.1.11, 8.2.0, 8.2.1, 8.2.2, 8.2.3, 8.2.4, 7.49.1, 7.49.2, 7.49.3, 7.49.4, 7.49.5, 7.49.6, 7.50.0, 8.2.5, 7.51.0, 8.2.10, 8.2.6, 8.2.7, 8.2.8, 8.2.9, 7.51.1, 8.2.11, 8.2.12, 8.2.13, 8.2.14, 8.2.15, 8.2.16, 7.51.2, 7.51.3, 7.51.4, 8.2.17, 8.2.18, 8.2.19, 8.2.20, 8.2.21, 8.2.22, 8.2.23, 8.2.24, 7.51.5, 8.2.25, 8.2.26, 8.2.27, 8.2.28, 7.51.6, 8.2.29, 8.2.30, 7.51.7, 7.51.8, 8.2.31, 7.51.9, 8.2.32, 8.2.33, 8.2.34, 8.2.35, 7.52.0, 7.52.1, 8.2.36</t>
   </si>
   <si>
     <t>cis</t>
@@ -3853,7 +3853,7 @@
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="1075.7109375" customWidth="1"/>
+    <col min="5" max="5" width="1099.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="9" width="16.7109375" customWidth="1"/>

--- a/RESULTS/results.xlsx
+++ b/RESULTS/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3681" uniqueCount="1183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3687" uniqueCount="1185">
   <si>
     <t>Fornitore</t>
   </si>
@@ -2258,6 +2258,12 @@
   </si>
   <si>
     <t>CARESTUDIO</t>
+  </si>
+  <si>
+    <t>it.entersrl</t>
+  </si>
+  <si>
+    <t>it.entersrl.extralab</t>
   </si>
   <si>
     <t>Joinsoft Srl</t>
@@ -3894,7 +3900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I580"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -12760,16 +12766,16 @@
         <v>749</v>
       </c>
       <c r="D366" t="s">
-        <v>750</v>
+        <v>174</v>
       </c>
       <c r="F366" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G366" t="s">
         <v>14</v>
       </c>
       <c r="H366">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="I366" t="s">
         <v>12</v>
@@ -12777,22 +12783,22 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
+        <v>750</v>
+      </c>
+      <c r="C367" t="s">
         <v>751</v>
       </c>
-      <c r="C367" t="s">
+      <c r="D367" t="s">
         <v>752</v>
       </c>
-      <c r="D367" t="s">
-        <v>12</v>
-      </c>
       <c r="F367" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G367" t="s">
         <v>14</v>
       </c>
       <c r="H367">
-        <v>45722</v>
+        <v>46148</v>
       </c>
       <c r="I367" t="s">
         <v>12</v>
@@ -12806,19 +12812,16 @@
         <v>754</v>
       </c>
       <c r="D368" t="s">
-        <v>755</v>
-      </c>
-      <c r="E368" t="s">
-        <v>756</v>
+        <v>12</v>
       </c>
       <c r="F368" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G368" t="s">
         <v>14</v>
       </c>
       <c r="H368">
-        <v>45695</v>
+        <v>45722</v>
       </c>
       <c r="I368" t="s">
         <v>12</v>
@@ -12826,22 +12829,25 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
+        <v>755</v>
+      </c>
+      <c r="C369" t="s">
+        <v>756</v>
+      </c>
+      <c r="D369" t="s">
         <v>757</v>
       </c>
-      <c r="C369" t="s">
+      <c r="E369" t="s">
         <v>758</v>
       </c>
-      <c r="D369" t="s">
-        <v>12</v>
-      </c>
       <c r="F369" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G369" t="s">
         <v>14</v>
       </c>
       <c r="H369">
-        <v>45849</v>
+        <v>45695</v>
       </c>
       <c r="I369" t="s">
         <v>12</v>
@@ -12855,16 +12861,16 @@
         <v>760</v>
       </c>
       <c r="D370" t="s">
-        <v>761</v>
+        <v>12</v>
       </c>
       <c r="F370" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="G370" t="s">
         <v>14</v>
       </c>
       <c r="H370">
-        <v>45103</v>
+        <v>45849</v>
       </c>
       <c r="I370" t="s">
         <v>12</v>
@@ -12872,22 +12878,22 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C371" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D371" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F371" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G371" t="s">
         <v>14</v>
       </c>
       <c r="H371">
-        <v>45695</v>
+        <v>45103</v>
       </c>
       <c r="I371" t="s">
         <v>12</v>
@@ -12895,25 +12901,22 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C372" t="s">
+        <v>762</v>
+      </c>
+      <c r="D372" t="s">
         <v>764</v>
       </c>
-      <c r="D372" t="s">
-        <v>610</v>
-      </c>
-      <c r="E372" t="s">
-        <v>765</v>
-      </c>
       <c r="F372" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G372" t="s">
         <v>14</v>
       </c>
       <c r="H372">
-        <v>45764</v>
+        <v>45695</v>
       </c>
       <c r="I372" t="s">
         <v>12</v>
@@ -12921,22 +12924,25 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373" t="s">
+        <v>765</v>
+      </c>
+      <c r="C373" t="s">
         <v>766</v>
       </c>
-      <c r="C373" t="s">
+      <c r="D373" t="s">
+        <v>610</v>
+      </c>
+      <c r="E373" t="s">
         <v>767</v>
       </c>
-      <c r="D373" t="s">
-        <v>768</v>
-      </c>
       <c r="F373" t="s">
-        <v>769</v>
+        <v>42</v>
       </c>
       <c r="G373" t="s">
         <v>14</v>
       </c>
       <c r="H373">
-        <v>45223</v>
+        <v>45764</v>
       </c>
       <c r="I373" t="s">
         <v>12</v>
@@ -12944,22 +12950,22 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374" t="s">
+        <v>768</v>
+      </c>
+      <c r="C374" t="s">
+        <v>769</v>
+      </c>
+      <c r="D374" t="s">
         <v>770</v>
       </c>
-      <c r="C374" t="s">
+      <c r="F374" t="s">
         <v>771</v>
       </c>
-      <c r="D374" t="s">
-        <v>34</v>
-      </c>
-      <c r="F374" t="s">
-        <v>13</v>
-      </c>
       <c r="G374" t="s">
         <v>14</v>
       </c>
       <c r="H374">
-        <v>45559</v>
+        <v>45223</v>
       </c>
       <c r="I374" t="s">
         <v>12</v>
@@ -12973,16 +12979,16 @@
         <v>773</v>
       </c>
       <c r="D375" t="s">
-        <v>536</v>
+        <v>34</v>
       </c>
       <c r="F375" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G375" t="s">
         <v>14</v>
       </c>
       <c r="H375">
-        <v>45411</v>
+        <v>45559</v>
       </c>
       <c r="I375" t="s">
         <v>12</v>
@@ -12990,22 +12996,22 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C376" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D376" t="s">
-        <v>774</v>
+        <v>536</v>
       </c>
       <c r="F376" t="s">
-        <v>740</v>
+        <v>22</v>
       </c>
       <c r="G376" t="s">
         <v>14</v>
       </c>
       <c r="H376">
-        <v>45951</v>
+        <v>45411</v>
       </c>
       <c r="I376" t="s">
         <v>12</v>
@@ -13013,22 +13019,22 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
+        <v>774</v>
+      </c>
+      <c r="C377" t="s">
         <v>775</v>
       </c>
-      <c r="C377" t="s">
+      <c r="D377" t="s">
         <v>776</v>
       </c>
-      <c r="D377" t="s">
-        <v>12</v>
-      </c>
       <c r="F377" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
       <c r="G377" t="s">
         <v>14</v>
       </c>
       <c r="H377">
-        <v>45825</v>
+        <v>45951</v>
       </c>
       <c r="I377" t="s">
         <v>12</v>
@@ -13042,16 +13048,16 @@
         <v>778</v>
       </c>
       <c r="D378" t="s">
-        <v>779</v>
+        <v>12</v>
       </c>
       <c r="F378" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G378" t="s">
         <v>14</v>
       </c>
       <c r="H378">
-        <v>45792</v>
+        <v>45825</v>
       </c>
       <c r="I378" t="s">
         <v>12</v>
@@ -13059,22 +13065,22 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379" t="s">
+        <v>779</v>
+      </c>
+      <c r="C379" t="s">
         <v>780</v>
       </c>
-      <c r="C379" t="s">
+      <c r="D379" t="s">
         <v>781</v>
       </c>
-      <c r="D379" t="s">
-        <v>12</v>
-      </c>
       <c r="F379" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="G379" t="s">
         <v>14</v>
       </c>
       <c r="H379">
-        <v>46049</v>
+        <v>45792</v>
       </c>
       <c r="I379" t="s">
         <v>12</v>
@@ -13088,16 +13094,16 @@
         <v>783</v>
       </c>
       <c r="D380" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F380" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="G380" t="s">
         <v>14</v>
       </c>
       <c r="H380">
-        <v>45322</v>
+        <v>46049</v>
       </c>
       <c r="I380" t="s">
         <v>12</v>
@@ -13105,22 +13111,22 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C381" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D381" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="F381" t="s">
-        <v>785</v>
+        <v>115</v>
       </c>
       <c r="G381" t="s">
         <v>14</v>
       </c>
       <c r="H381">
-        <v>45457</v>
+        <v>45322</v>
       </c>
       <c r="I381" t="s">
         <v>12</v>
@@ -13128,22 +13134,22 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C382" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D382" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="F382" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G382" t="s">
         <v>14</v>
       </c>
       <c r="H382">
-        <v>45582</v>
+        <v>45457</v>
       </c>
       <c r="I382" t="s">
         <v>12</v>
@@ -13151,22 +13157,22 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
+        <v>784</v>
+      </c>
+      <c r="C383" t="s">
         <v>786</v>
       </c>
-      <c r="C383" t="s">
+      <c r="D383" t="s">
+        <v>199</v>
+      </c>
+      <c r="F383" t="s">
         <v>787</v>
       </c>
-      <c r="D383" t="s">
-        <v>104</v>
-      </c>
-      <c r="F383" t="s">
-        <v>211</v>
-      </c>
       <c r="G383" t="s">
         <v>14</v>
       </c>
       <c r="H383">
-        <v>45398</v>
+        <v>45582</v>
       </c>
       <c r="I383" t="s">
         <v>12</v>
@@ -13183,13 +13189,13 @@
         <v>104</v>
       </c>
       <c r="F384" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="G384" t="s">
         <v>14</v>
       </c>
       <c r="H384">
-        <v>45036</v>
+        <v>45398</v>
       </c>
       <c r="I384" t="s">
         <v>12</v>
@@ -13197,13 +13203,13 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C385" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D385" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F385" t="s">
         <v>18</v>
@@ -13212,7 +13218,7 @@
         <v>14</v>
       </c>
       <c r="H385">
-        <v>45048</v>
+        <v>45036</v>
       </c>
       <c r="I385" t="s">
         <v>12</v>
@@ -13220,10 +13226,10 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C386" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D386" t="s">
         <v>12</v>
@@ -13235,7 +13241,7 @@
         <v>14</v>
       </c>
       <c r="H386">
-        <v>45219</v>
+        <v>45048</v>
       </c>
       <c r="I386" t="s">
         <v>12</v>
@@ -13243,22 +13249,22 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C387" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D387" t="s">
         <v>12</v>
       </c>
       <c r="F387" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G387" t="s">
         <v>14</v>
       </c>
       <c r="H387">
-        <v>46010</v>
+        <v>45219</v>
       </c>
       <c r="I387" t="s">
         <v>12</v>
@@ -13266,16 +13272,13 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C388" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D388" t="s">
-        <v>104</v>
-      </c>
-      <c r="E388" t="s">
-        <v>233</v>
+        <v>12</v>
       </c>
       <c r="F388" t="s">
         <v>19</v>
@@ -13284,7 +13287,7 @@
         <v>14</v>
       </c>
       <c r="H388">
-        <v>45279</v>
+        <v>46010</v>
       </c>
       <c r="I388" t="s">
         <v>12</v>
@@ -13292,22 +13295,25 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
+        <v>790</v>
+      </c>
+      <c r="C389" t="s">
         <v>791</v>
       </c>
-      <c r="C389" t="s">
-        <v>792</v>
-      </c>
       <c r="D389" t="s">
-        <v>793</v>
+        <v>104</v>
+      </c>
+      <c r="E389" t="s">
+        <v>233</v>
       </c>
       <c r="F389" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G389" t="s">
         <v>14</v>
       </c>
       <c r="H389">
-        <v>46065</v>
+        <v>45279</v>
       </c>
       <c r="I389" t="s">
         <v>12</v>
@@ -13315,25 +13321,22 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390" t="s">
+        <v>793</v>
+      </c>
+      <c r="C390" t="s">
         <v>794</v>
       </c>
-      <c r="B390" t="s">
+      <c r="D390" t="s">
         <v>795</v>
       </c>
-      <c r="C390" t="s">
-        <v>796</v>
-      </c>
-      <c r="D390" t="s">
-        <v>104</v>
-      </c>
       <c r="F390" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G390" t="s">
         <v>14</v>
       </c>
       <c r="H390">
-        <v>45219</v>
+        <v>46065</v>
       </c>
       <c r="I390" t="s">
         <v>12</v>
@@ -13341,22 +13344,25 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
+        <v>796</v>
+      </c>
+      <c r="B391" t="s">
         <v>797</v>
       </c>
       <c r="C391" t="s">
         <v>798</v>
       </c>
       <c r="D391" t="s">
-        <v>799</v>
+        <v>104</v>
       </c>
       <c r="F391" t="s">
-        <v>740</v>
+        <v>22</v>
       </c>
       <c r="G391" t="s">
         <v>14</v>
       </c>
       <c r="H391">
-        <v>45974</v>
+        <v>45219</v>
       </c>
       <c r="I391" t="s">
         <v>12</v>
@@ -13364,22 +13370,22 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
+        <v>799</v>
+      </c>
+      <c r="C392" t="s">
         <v>800</v>
       </c>
-      <c r="C392" t="s">
+      <c r="D392" t="s">
         <v>801</v>
       </c>
-      <c r="D392" t="s">
-        <v>802</v>
-      </c>
       <c r="F392" t="s">
-        <v>60</v>
+        <v>740</v>
       </c>
       <c r="G392" t="s">
         <v>14</v>
       </c>
       <c r="H392">
-        <v>45980</v>
+        <v>45974</v>
       </c>
       <c r="I392" t="s">
         <v>12</v>
@@ -13387,22 +13393,22 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
+        <v>802</v>
+      </c>
+      <c r="C393" t="s">
         <v>803</v>
       </c>
-      <c r="C393" t="s">
+      <c r="D393" t="s">
         <v>804</v>
       </c>
-      <c r="D393" t="s">
-        <v>556</v>
-      </c>
       <c r="F393" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G393" t="s">
         <v>14</v>
       </c>
       <c r="H393">
-        <v>45061</v>
+        <v>45980</v>
       </c>
       <c r="I393" t="s">
         <v>12</v>
@@ -13410,22 +13416,22 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C394" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D394" t="s">
         <v>556</v>
       </c>
       <c r="F394" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G394" t="s">
         <v>14</v>
       </c>
       <c r="H394">
-        <v>45238</v>
+        <v>45061</v>
       </c>
       <c r="I394" t="s">
         <v>12</v>
@@ -13433,22 +13439,22 @@
     </row>
     <row r="395" spans="1:9">
       <c r="A395" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C395" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D395" t="s">
         <v>556</v>
       </c>
       <c r="F395" t="s">
-        <v>805</v>
+        <v>19</v>
       </c>
       <c r="G395" t="s">
         <v>14</v>
       </c>
       <c r="H395">
-        <v>46052</v>
+        <v>45238</v>
       </c>
       <c r="I395" t="s">
         <v>12</v>
@@ -13456,7 +13462,7 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C396" t="s">
         <v>806</v>
@@ -13465,13 +13471,13 @@
         <v>556</v>
       </c>
       <c r="F396" t="s">
-        <v>22</v>
+        <v>807</v>
       </c>
       <c r="G396" t="s">
         <v>14</v>
       </c>
       <c r="H396">
-        <v>45359</v>
+        <v>46052</v>
       </c>
       <c r="I396" t="s">
         <v>12</v>
@@ -13479,22 +13485,22 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C397" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D397" t="s">
         <v>556</v>
       </c>
       <c r="F397" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G397" t="s">
         <v>14</v>
       </c>
       <c r="H397">
-        <v>45477</v>
+        <v>45359</v>
       </c>
       <c r="I397" t="s">
         <v>12</v>
@@ -13502,22 +13508,22 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C398" t="s">
         <v>809</v>
       </c>
       <c r="D398" t="s">
-        <v>810</v>
+        <v>556</v>
       </c>
       <c r="F398" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G398" t="s">
         <v>14</v>
       </c>
       <c r="H398">
-        <v>45385</v>
+        <v>45477</v>
       </c>
       <c r="I398" t="s">
         <v>12</v>
@@ -13525,22 +13531,22 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C399" t="s">
         <v>811</v>
       </c>
       <c r="D399" t="s">
-        <v>29</v>
+        <v>812</v>
       </c>
       <c r="F399" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G399" t="s">
         <v>14</v>
       </c>
       <c r="H399">
-        <v>45390</v>
+        <v>45385</v>
       </c>
       <c r="I399" t="s">
         <v>12</v>
@@ -13548,25 +13554,22 @@
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C400" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D400" t="s">
-        <v>813</v>
-      </c>
-      <c r="E400" t="s">
-        <v>814</v>
+        <v>29</v>
       </c>
       <c r="F400" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G400" t="s">
         <v>14</v>
       </c>
       <c r="H400">
-        <v>45446</v>
+        <v>45390</v>
       </c>
       <c r="I400" t="s">
         <v>12</v>
@@ -13574,25 +13577,25 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
+        <v>810</v>
+      </c>
+      <c r="C401" t="s">
+        <v>814</v>
+      </c>
+      <c r="D401" t="s">
         <v>815</v>
       </c>
-      <c r="C401" t="s">
+      <c r="E401" t="s">
         <v>816</v>
       </c>
-      <c r="D401" t="s">
-        <v>817</v>
-      </c>
-      <c r="E401" t="s">
-        <v>818</v>
-      </c>
       <c r="F401" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G401" t="s">
         <v>14</v>
       </c>
       <c r="H401">
-        <v>45008</v>
+        <v>45446</v>
       </c>
       <c r="I401" t="s">
         <v>12</v>
@@ -13600,22 +13603,25 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
+        <v>817</v>
+      </c>
+      <c r="C402" t="s">
+        <v>818</v>
+      </c>
+      <c r="D402" t="s">
         <v>819</v>
       </c>
-      <c r="C402" t="s">
+      <c r="E402" t="s">
         <v>820</v>
       </c>
-      <c r="D402" t="s">
-        <v>821</v>
-      </c>
       <c r="F402" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G402" t="s">
         <v>14</v>
       </c>
       <c r="H402">
-        <v>45411</v>
+        <v>45008</v>
       </c>
       <c r="I402" t="s">
         <v>12</v>
@@ -13623,13 +13629,13 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
+        <v>821</v>
+      </c>
+      <c r="C403" t="s">
         <v>822</v>
       </c>
-      <c r="C403" t="s">
+      <c r="D403" t="s">
         <v>823</v>
-      </c>
-      <c r="D403" t="s">
-        <v>824</v>
       </c>
       <c r="F403" t="s">
         <v>13</v>
@@ -13638,7 +13644,7 @@
         <v>14</v>
       </c>
       <c r="H403">
-        <v>45468</v>
+        <v>45411</v>
       </c>
       <c r="I403" t="s">
         <v>12</v>
@@ -13646,22 +13652,22 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
+        <v>824</v>
+      </c>
+      <c r="C404" t="s">
         <v>825</v>
       </c>
-      <c r="C404" t="s">
+      <c r="D404" t="s">
         <v>826</v>
       </c>
-      <c r="D404" t="s">
-        <v>699</v>
-      </c>
       <c r="F404" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G404" t="s">
         <v>14</v>
       </c>
       <c r="H404">
-        <v>45728</v>
+        <v>45468</v>
       </c>
       <c r="I404" t="s">
         <v>12</v>
@@ -13669,22 +13675,22 @@
     </row>
     <row r="405" spans="1:9">
       <c r="A405" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C405" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D405" t="s">
-        <v>827</v>
+        <v>699</v>
       </c>
       <c r="F405" t="s">
-        <v>828</v>
+        <v>35</v>
       </c>
       <c r="G405" t="s">
         <v>14</v>
       </c>
       <c r="H405">
-        <v>46099</v>
+        <v>45728</v>
       </c>
       <c r="I405" t="s">
         <v>12</v>
@@ -13692,22 +13698,22 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
+        <v>827</v>
+      </c>
+      <c r="C406" t="s">
+        <v>828</v>
+      </c>
+      <c r="D406" t="s">
         <v>829</v>
       </c>
-      <c r="C406" t="s">
+      <c r="F406" t="s">
         <v>830</v>
       </c>
-      <c r="D406" t="s">
-        <v>831</v>
-      </c>
-      <c r="F406" t="s">
-        <v>35</v>
-      </c>
       <c r="G406" t="s">
         <v>14</v>
       </c>
       <c r="H406">
-        <v>45254</v>
+        <v>46099</v>
       </c>
       <c r="I406" t="s">
         <v>12</v>
@@ -13715,22 +13721,22 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
+        <v>831</v>
+      </c>
+      <c r="C407" t="s">
         <v>832</v>
       </c>
-      <c r="C407" t="s">
+      <c r="D407" t="s">
         <v>833</v>
       </c>
-      <c r="D407" t="s">
-        <v>12</v>
-      </c>
       <c r="F407" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G407" t="s">
         <v>14</v>
       </c>
       <c r="H407">
-        <v>45807</v>
+        <v>45254</v>
       </c>
       <c r="I407" t="s">
         <v>12</v>
@@ -13741,19 +13747,19 @@
         <v>834</v>
       </c>
       <c r="C408" t="s">
-        <v>149</v>
+        <v>835</v>
       </c>
       <c r="D408" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="F408" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G408" t="s">
         <v>14</v>
       </c>
       <c r="H408">
-        <v>45909</v>
+        <v>45807</v>
       </c>
       <c r="I408" t="s">
         <v>12</v>
@@ -13761,22 +13767,22 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C409" t="s">
-        <v>836</v>
+        <v>149</v>
       </c>
       <c r="D409" t="s">
-        <v>837</v>
+        <v>104</v>
       </c>
       <c r="F409" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G409" t="s">
         <v>14</v>
       </c>
       <c r="H409">
-        <v>45477</v>
+        <v>45909</v>
       </c>
       <c r="I409" t="s">
         <v>12</v>
@@ -13784,22 +13790,22 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
+        <v>837</v>
+      </c>
+      <c r="C410" t="s">
         <v>838</v>
       </c>
-      <c r="C410" t="s">
+      <c r="D410" t="s">
         <v>839</v>
       </c>
-      <c r="D410" t="s">
-        <v>840</v>
-      </c>
       <c r="F410" t="s">
-        <v>378</v>
+        <v>13</v>
       </c>
       <c r="G410" t="s">
         <v>14</v>
       </c>
       <c r="H410">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="I410" t="s">
         <v>12</v>
@@ -13807,22 +13813,22 @@
     </row>
     <row r="411" spans="1:9">
       <c r="A411" t="s">
+        <v>840</v>
+      </c>
+      <c r="C411" t="s">
         <v>841</v>
       </c>
-      <c r="C411" t="s">
+      <c r="D411" t="s">
         <v>842</v>
       </c>
-      <c r="D411" t="s">
-        <v>843</v>
-      </c>
       <c r="F411" t="s">
-        <v>35</v>
+        <v>378</v>
       </c>
       <c r="G411" t="s">
         <v>14</v>
       </c>
       <c r="H411">
-        <v>45337</v>
+        <v>45415</v>
       </c>
       <c r="I411" t="s">
         <v>12</v>
@@ -13830,15 +13836,12 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C412" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D412" t="s">
-        <v>844</v>
-      </c>
-      <c r="E412" t="s">
         <v>845</v>
       </c>
       <c r="F412" t="s">
@@ -13848,7 +13851,7 @@
         <v>14</v>
       </c>
       <c r="H412">
-        <v>45722</v>
+        <v>45337</v>
       </c>
       <c r="I412" t="s">
         <v>12</v>
@@ -13856,13 +13859,16 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C413" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D413" t="s">
-        <v>845</v>
+        <v>846</v>
+      </c>
+      <c r="E413" t="s">
+        <v>847</v>
       </c>
       <c r="F413" t="s">
         <v>35</v>
@@ -13871,7 +13877,7 @@
         <v>14</v>
       </c>
       <c r="H413">
-        <v>46044</v>
+        <v>45722</v>
       </c>
       <c r="I413" t="s">
         <v>12</v>
@@ -13879,22 +13885,22 @@
     </row>
     <row r="414" spans="1:9">
       <c r="A414" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C414" t="s">
+        <v>844</v>
+      </c>
+      <c r="D414" t="s">
         <v>847</v>
       </c>
-      <c r="D414" t="s">
-        <v>848</v>
-      </c>
       <c r="F414" t="s">
-        <v>849</v>
+        <v>35</v>
       </c>
       <c r="G414" t="s">
         <v>14</v>
       </c>
       <c r="H414">
-        <v>45833</v>
+        <v>46044</v>
       </c>
       <c r="I414" t="s">
         <v>12</v>
@@ -13902,22 +13908,22 @@
     </row>
     <row r="415" spans="1:9">
       <c r="A415" t="s">
+        <v>848</v>
+      </c>
+      <c r="C415" t="s">
+        <v>849</v>
+      </c>
+      <c r="D415" t="s">
         <v>850</v>
       </c>
-      <c r="C415" t="s">
+      <c r="F415" t="s">
         <v>851</v>
       </c>
-      <c r="D415" t="s">
-        <v>104</v>
-      </c>
-      <c r="F415" t="s">
-        <v>24</v>
-      </c>
       <c r="G415" t="s">
         <v>14</v>
       </c>
       <c r="H415">
-        <v>46148</v>
+        <v>45833</v>
       </c>
       <c r="I415" t="s">
         <v>12</v>
@@ -13931,16 +13937,16 @@
         <v>853</v>
       </c>
       <c r="D416" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="F416" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G416" t="s">
         <v>14</v>
       </c>
       <c r="H416">
-        <v>45124</v>
+        <v>46148</v>
       </c>
       <c r="I416" t="s">
         <v>12</v>
@@ -13948,22 +13954,22 @@
     </row>
     <row r="417" spans="1:9">
       <c r="A417" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C417" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D417" t="s">
-        <v>848</v>
+        <v>134</v>
       </c>
       <c r="F417" t="s">
-        <v>721</v>
+        <v>22</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
       </c>
       <c r="H417">
-        <v>45807</v>
+        <v>45124</v>
       </c>
       <c r="I417" t="s">
         <v>12</v>
@@ -13977,19 +13983,16 @@
         <v>855</v>
       </c>
       <c r="D418" t="s">
-        <v>856</v>
-      </c>
-      <c r="E418" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="F418" t="s">
-        <v>13</v>
+        <v>721</v>
       </c>
       <c r="G418" t="s">
         <v>14</v>
       </c>
       <c r="H418">
-        <v>45072</v>
+        <v>45807</v>
       </c>
       <c r="I418" t="s">
         <v>12</v>
@@ -13997,28 +14000,25 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" t="s">
+        <v>856</v>
+      </c>
+      <c r="C419" t="s">
+        <v>857</v>
+      </c>
+      <c r="D419" t="s">
         <v>858</v>
       </c>
-      <c r="B419" t="s">
+      <c r="E419" t="s">
         <v>859</v>
       </c>
-      <c r="C419" t="s">
-        <v>860</v>
-      </c>
-      <c r="D419" t="s">
-        <v>861</v>
-      </c>
-      <c r="E419" t="s">
-        <v>862</v>
-      </c>
       <c r="F419" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
       </c>
       <c r="H419">
-        <v>45314</v>
+        <v>45072</v>
       </c>
       <c r="I419" t="s">
         <v>12</v>
@@ -14026,13 +14026,13 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B420" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C420" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D420" t="s">
         <v>863</v>
@@ -14047,7 +14047,7 @@
         <v>14</v>
       </c>
       <c r="H420">
-        <v>45723</v>
+        <v>45314</v>
       </c>
       <c r="I420" t="s">
         <v>12</v>
@@ -14055,17 +14055,20 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B421" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C421" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D421" t="s">
         <v>865</v>
       </c>
+      <c r="E421" t="s">
+        <v>866</v>
+      </c>
       <c r="F421" t="s">
         <v>35</v>
       </c>
@@ -14073,7 +14076,7 @@
         <v>14</v>
       </c>
       <c r="H421">
-        <v>46093</v>
+        <v>45723</v>
       </c>
       <c r="I421" t="s">
         <v>12</v>
@@ -14081,13 +14084,13 @@
     </row>
     <row r="422" spans="1:9">
       <c r="A422" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B422" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C422" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D422" t="s">
         <v>867</v>
@@ -14099,7 +14102,7 @@
         <v>14</v>
       </c>
       <c r="H422">
-        <v>45839</v>
+        <v>46093</v>
       </c>
       <c r="I422" t="s">
         <v>12</v>
@@ -14107,22 +14110,25 @@
     </row>
     <row r="423" spans="1:9">
       <c r="A423" t="s">
+        <v>861</v>
+      </c>
+      <c r="B423" t="s">
+        <v>860</v>
+      </c>
+      <c r="C423" t="s">
         <v>868</v>
-      </c>
-      <c r="C423" t="s">
-        <v>869</v>
       </c>
       <c r="D423" t="s">
         <v>869</v>
       </c>
       <c r="F423" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G423" t="s">
         <v>14</v>
       </c>
       <c r="H423">
-        <v>45014</v>
+        <v>45839</v>
       </c>
       <c r="I423" t="s">
         <v>12</v>
@@ -14130,22 +14136,22 @@
     </row>
     <row r="424" spans="1:9">
       <c r="A424" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C424" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D424" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F424" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G424" t="s">
         <v>14</v>
       </c>
       <c r="H424">
-        <v>46042</v>
+        <v>45014</v>
       </c>
       <c r="I424" t="s">
         <v>12</v>
@@ -14153,22 +14159,22 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425" t="s">
+        <v>870</v>
+      </c>
+      <c r="C425" t="s">
         <v>871</v>
       </c>
-      <c r="C425" t="s">
+      <c r="D425" t="s">
         <v>872</v>
       </c>
-      <c r="D425" t="s">
-        <v>873</v>
-      </c>
       <c r="F425" t="s">
-        <v>446</v>
+        <v>13</v>
       </c>
       <c r="G425" t="s">
         <v>14</v>
       </c>
       <c r="H425">
-        <v>45198</v>
+        <v>46042</v>
       </c>
       <c r="I425" t="s">
         <v>12</v>
@@ -14176,22 +14182,22 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C426" t="s">
         <v>874</v>
       </c>
       <c r="D426" t="s">
-        <v>210</v>
+        <v>875</v>
       </c>
       <c r="F426" t="s">
-        <v>60</v>
+        <v>446</v>
       </c>
       <c r="G426" t="s">
         <v>14</v>
       </c>
       <c r="H426">
-        <v>46035</v>
+        <v>45198</v>
       </c>
       <c r="I426" t="s">
         <v>12</v>
@@ -14199,22 +14205,22 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C427" t="s">
         <v>876</v>
       </c>
       <c r="D427" t="s">
-        <v>12</v>
+        <v>210</v>
       </c>
       <c r="F427" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="G427" t="s">
         <v>14</v>
       </c>
       <c r="H427">
-        <v>45617</v>
+        <v>46035</v>
       </c>
       <c r="I427" t="s">
         <v>12</v>
@@ -14228,19 +14234,16 @@
         <v>878</v>
       </c>
       <c r="D428" t="s">
-        <v>879</v>
-      </c>
-      <c r="E428" t="s">
-        <v>880</v>
+        <v>12</v>
       </c>
       <c r="F428" t="s">
-        <v>881</v>
+        <v>22</v>
       </c>
       <c r="G428" t="s">
         <v>14</v>
       </c>
       <c r="H428">
-        <v>45119</v>
+        <v>45617</v>
       </c>
       <c r="I428" t="s">
         <v>12</v>
@@ -14248,22 +14251,25 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
+        <v>879</v>
+      </c>
+      <c r="C429" t="s">
+        <v>880</v>
+      </c>
+      <c r="D429" t="s">
+        <v>881</v>
+      </c>
+      <c r="E429" t="s">
         <v>882</v>
       </c>
-      <c r="C429" t="s">
+      <c r="F429" t="s">
         <v>883</v>
       </c>
-      <c r="D429" t="s">
-        <v>104</v>
-      </c>
-      <c r="F429" t="s">
-        <v>22</v>
-      </c>
       <c r="G429" t="s">
         <v>14</v>
       </c>
       <c r="H429">
-        <v>45671</v>
+        <v>45119</v>
       </c>
       <c r="I429" t="s">
         <v>12</v>
@@ -14271,22 +14277,22 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C430" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D430" t="s">
         <v>104</v>
       </c>
       <c r="F430" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="G430" t="s">
         <v>14</v>
       </c>
       <c r="H430">
-        <v>45807</v>
+        <v>45671</v>
       </c>
       <c r="I430" t="s">
         <v>12</v>
@@ -14300,16 +14306,16 @@
         <v>885</v>
       </c>
       <c r="D431" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="F431" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="G431" t="s">
         <v>14</v>
       </c>
       <c r="H431">
-        <v>46105</v>
+        <v>45807</v>
       </c>
       <c r="I431" t="s">
         <v>12</v>
@@ -14323,16 +14329,16 @@
         <v>887</v>
       </c>
       <c r="D432" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F432" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G432" t="s">
         <v>14</v>
       </c>
       <c r="H432">
-        <v>45792</v>
+        <v>46105</v>
       </c>
       <c r="I432" t="s">
         <v>12</v>
@@ -14346,16 +14352,16 @@
         <v>889</v>
       </c>
       <c r="D433" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F433" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G433" t="s">
         <v>14</v>
       </c>
       <c r="H433">
-        <v>45072</v>
+        <v>45792</v>
       </c>
       <c r="I433" t="s">
         <v>12</v>
@@ -14363,22 +14369,22 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C434" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D434" t="s">
         <v>34</v>
       </c>
       <c r="F434" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G434" t="s">
         <v>14</v>
       </c>
       <c r="H434">
-        <v>45439</v>
+        <v>45072</v>
       </c>
       <c r="I434" t="s">
         <v>12</v>
@@ -14386,22 +14392,22 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C435" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D435" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F435" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G435" t="s">
         <v>14</v>
       </c>
       <c r="H435">
-        <v>45072</v>
+        <v>45439</v>
       </c>
       <c r="I435" t="s">
         <v>12</v>
@@ -14409,22 +14415,22 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C436" t="s">
         <v>892</v>
       </c>
       <c r="D436" t="s">
-        <v>893</v>
+        <v>12</v>
       </c>
       <c r="F436" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G436" t="s">
         <v>14</v>
       </c>
       <c r="H436">
-        <v>45722</v>
+        <v>45072</v>
       </c>
       <c r="I436" t="s">
         <v>12</v>
@@ -14432,13 +14438,13 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
+        <v>893</v>
+      </c>
+      <c r="C437" t="s">
         <v>894</v>
       </c>
-      <c r="C437" t="s">
+      <c r="D437" t="s">
         <v>895</v>
-      </c>
-      <c r="D437" t="s">
-        <v>896</v>
       </c>
       <c r="F437" t="s">
         <v>13</v>
@@ -14447,7 +14453,7 @@
         <v>14</v>
       </c>
       <c r="H437">
-        <v>46148</v>
+        <v>45722</v>
       </c>
       <c r="I437" t="s">
         <v>12</v>
@@ -14455,22 +14461,22 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
+        <v>896</v>
+      </c>
+      <c r="C438" t="s">
         <v>897</v>
       </c>
-      <c r="C438" t="s">
+      <c r="D438" t="s">
         <v>898</v>
       </c>
-      <c r="D438" t="s">
-        <v>104</v>
-      </c>
       <c r="F438" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G438" t="s">
         <v>14</v>
       </c>
       <c r="H438">
-        <v>45433</v>
+        <v>46148</v>
       </c>
       <c r="I438" t="s">
         <v>12</v>
@@ -14484,16 +14490,16 @@
         <v>900</v>
       </c>
       <c r="D439" t="s">
-        <v>901</v>
+        <v>104</v>
       </c>
       <c r="F439" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G439" t="s">
         <v>14</v>
       </c>
       <c r="H439">
-        <v>45072</v>
+        <v>45433</v>
       </c>
       <c r="I439" t="s">
         <v>12</v>
@@ -14501,7 +14507,7 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C440" t="s">
         <v>902</v>
@@ -14510,7 +14516,7 @@
         <v>903</v>
       </c>
       <c r="F440" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G440" t="s">
         <v>14</v>
@@ -14524,7 +14530,7 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C441" t="s">
         <v>904</v>
@@ -14533,13 +14539,13 @@
         <v>905</v>
       </c>
       <c r="F441" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G441" t="s">
         <v>14</v>
       </c>
       <c r="H441">
-        <v>45082</v>
+        <v>45072</v>
       </c>
       <c r="I441" t="s">
         <v>12</v>
@@ -14547,7 +14553,7 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C442" t="s">
         <v>906</v>
@@ -14556,13 +14562,13 @@
         <v>907</v>
       </c>
       <c r="F442" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G442" t="s">
         <v>14</v>
       </c>
       <c r="H442">
-        <v>45083</v>
+        <v>45082</v>
       </c>
       <c r="I442" t="s">
         <v>12</v>
@@ -14570,25 +14576,22 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
+        <v>901</v>
+      </c>
+      <c r="C443" t="s">
         <v>908</v>
       </c>
-      <c r="C443" t="s">
+      <c r="D443" t="s">
         <v>909</v>
       </c>
-      <c r="D443" t="s">
-        <v>910</v>
-      </c>
-      <c r="E443" t="s">
-        <v>911</v>
-      </c>
       <c r="F443" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G443" t="s">
         <v>14</v>
       </c>
       <c r="H443">
-        <v>45051</v>
+        <v>45083</v>
       </c>
       <c r="I443" t="s">
         <v>12</v>
@@ -14596,22 +14599,25 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
+        <v>910</v>
+      </c>
+      <c r="C444" t="s">
+        <v>911</v>
+      </c>
+      <c r="D444" t="s">
         <v>912</v>
       </c>
-      <c r="C444" t="s">
+      <c r="E444" t="s">
         <v>913</v>
       </c>
-      <c r="D444" t="s">
-        <v>810</v>
-      </c>
       <c r="F444" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G444" t="s">
         <v>14</v>
       </c>
       <c r="H444">
-        <v>45216</v>
+        <v>45051</v>
       </c>
       <c r="I444" t="s">
         <v>12</v>
@@ -14619,16 +14625,13 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C445" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D445" t="s">
-        <v>915</v>
-      </c>
-      <c r="E445" t="s">
-        <v>916</v>
+        <v>812</v>
       </c>
       <c r="F445" t="s">
         <v>24</v>
@@ -14645,22 +14648,25 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C446" t="s">
+        <v>916</v>
+      </c>
+      <c r="D446" t="s">
         <v>917</v>
       </c>
-      <c r="D446" t="s">
+      <c r="E446" t="s">
         <v>918</v>
       </c>
       <c r="F446" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G446" t="s">
         <v>14</v>
       </c>
       <c r="H446">
-        <v>45538</v>
+        <v>45216</v>
       </c>
       <c r="I446" t="s">
         <v>12</v>
@@ -14668,22 +14674,22 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
+        <v>914</v>
+      </c>
+      <c r="C447" t="s">
         <v>919</v>
       </c>
-      <c r="C447" t="s">
+      <c r="D447" t="s">
         <v>920</v>
       </c>
-      <c r="D447" t="s">
-        <v>12</v>
-      </c>
       <c r="F447" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G447" t="s">
         <v>14</v>
       </c>
       <c r="H447">
-        <v>45825</v>
+        <v>45538</v>
       </c>
       <c r="I447" t="s">
         <v>12</v>
@@ -14697,16 +14703,16 @@
         <v>922</v>
       </c>
       <c r="D448" t="s">
-        <v>923</v>
+        <v>12</v>
       </c>
       <c r="F448" t="s">
-        <v>924</v>
+        <v>18</v>
       </c>
       <c r="G448" t="s">
         <v>14</v>
       </c>
       <c r="H448">
-        <v>45103</v>
+        <v>45825</v>
       </c>
       <c r="I448" t="s">
         <v>12</v>
@@ -14714,22 +14720,22 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
+        <v>923</v>
+      </c>
+      <c r="C449" t="s">
+        <v>924</v>
+      </c>
+      <c r="D449" t="s">
         <v>925</v>
       </c>
-      <c r="C449" t="s">
+      <c r="F449" t="s">
         <v>926</v>
       </c>
-      <c r="D449" t="s">
-        <v>927</v>
-      </c>
-      <c r="F449" t="s">
-        <v>13</v>
-      </c>
       <c r="G449" t="s">
         <v>14</v>
       </c>
       <c r="H449">
-        <v>45337</v>
+        <v>45103</v>
       </c>
       <c r="I449" t="s">
         <v>12</v>
@@ -14737,25 +14743,22 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
+        <v>927</v>
+      </c>
+      <c r="C450" t="s">
         <v>928</v>
       </c>
-      <c r="B450" t="s">
+      <c r="D450" t="s">
         <v>929</v>
       </c>
-      <c r="C450" t="s">
-        <v>930</v>
-      </c>
-      <c r="D450" t="s">
-        <v>931</v>
-      </c>
       <c r="F450" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="G450" t="s">
         <v>14</v>
       </c>
       <c r="H450">
-        <v>45014</v>
+        <v>45337</v>
       </c>
       <c r="I450" t="s">
         <v>12</v>
@@ -14763,10 +14766,10 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B451" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C451" t="s">
         <v>932</v>
@@ -14774,9 +14777,6 @@
       <c r="D451" t="s">
         <v>933</v>
       </c>
-      <c r="E451" t="s">
-        <v>934</v>
-      </c>
       <c r="F451" t="s">
         <v>144</v>
       </c>
@@ -14792,16 +14792,16 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B452" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C452" t="s">
+        <v>934</v>
+      </c>
+      <c r="D452" t="s">
         <v>935</v>
-      </c>
-      <c r="D452" t="s">
-        <v>274</v>
       </c>
       <c r="E452" t="s">
         <v>936</v>
@@ -14813,7 +14813,7 @@
         <v>14</v>
       </c>
       <c r="H452">
-        <v>45028</v>
+        <v>45014</v>
       </c>
       <c r="I452" t="s">
         <v>12</v>
@@ -14821,10 +14821,10 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B453" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C453" t="s">
         <v>937</v>
@@ -14832,6 +14832,9 @@
       <c r="D453" t="s">
         <v>274</v>
       </c>
+      <c r="E453" t="s">
+        <v>938</v>
+      </c>
       <c r="F453" t="s">
         <v>144</v>
       </c>
@@ -14847,13 +14850,13 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B454" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C454" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D454" t="s">
         <v>274</v>
@@ -14865,7 +14868,7 @@
         <v>14</v>
       </c>
       <c r="H454">
-        <v>45103</v>
+        <v>45028</v>
       </c>
       <c r="I454" t="s">
         <v>12</v>
@@ -14873,25 +14876,25 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B455" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C455" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D455" t="s">
-        <v>774</v>
+        <v>274</v>
       </c>
       <c r="F455" t="s">
-        <v>263</v>
+        <v>144</v>
       </c>
       <c r="G455" t="s">
         <v>14</v>
       </c>
       <c r="H455">
-        <v>45671</v>
+        <v>45103</v>
       </c>
       <c r="I455" t="s">
         <v>12</v>
@@ -14899,16 +14902,16 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B456" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C456" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D456" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F456" t="s">
         <v>263</v>
@@ -14925,22 +14928,25 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" t="s">
-        <v>941</v>
+        <v>931</v>
+      </c>
+      <c r="B457" t="s">
+        <v>930</v>
       </c>
       <c r="C457" t="s">
         <v>942</v>
       </c>
       <c r="D457" t="s">
-        <v>12</v>
+        <v>776</v>
       </c>
       <c r="F457" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="G457" t="s">
         <v>14</v>
       </c>
       <c r="H457">
-        <v>45985</v>
+        <v>45671</v>
       </c>
       <c r="I457" t="s">
         <v>12</v>
@@ -14954,16 +14960,16 @@
         <v>944</v>
       </c>
       <c r="D458" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F458" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="G458" t="s">
         <v>14</v>
       </c>
       <c r="H458">
-        <v>45820</v>
+        <v>45985</v>
       </c>
       <c r="I458" t="s">
         <v>12</v>
@@ -14971,16 +14977,16 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C459" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D459" t="s">
         <v>29</v>
       </c>
       <c r="F459" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G459" t="s">
         <v>14</v>
@@ -14994,22 +15000,22 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C460" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D460" t="s">
         <v>29</v>
       </c>
       <c r="F460" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G460" t="s">
         <v>14</v>
       </c>
       <c r="H460">
-        <v>46006</v>
+        <v>45820</v>
       </c>
       <c r="I460" t="s">
         <v>12</v>
@@ -15017,22 +15023,22 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C461" t="s">
         <v>948</v>
       </c>
       <c r="D461" t="s">
-        <v>949</v>
+        <v>29</v>
       </c>
       <c r="F461" t="s">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="G461" t="s">
         <v>14</v>
       </c>
       <c r="H461">
-        <v>45103</v>
+        <v>46006</v>
       </c>
       <c r="I461" t="s">
         <v>12</v>
@@ -15040,22 +15046,22 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C462" t="s">
         <v>950</v>
       </c>
       <c r="D462" t="s">
-        <v>12</v>
+        <v>951</v>
       </c>
       <c r="F462" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="G462" t="s">
         <v>14</v>
       </c>
       <c r="H462">
-        <v>45385</v>
+        <v>45103</v>
       </c>
       <c r="I462" t="s">
         <v>12</v>
@@ -15063,7 +15069,7 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C463" t="s">
         <v>952</v>
@@ -15072,13 +15078,13 @@
         <v>12</v>
       </c>
       <c r="F463" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G463" t="s">
         <v>14</v>
       </c>
       <c r="H463">
-        <v>45093</v>
+        <v>45385</v>
       </c>
       <c r="I463" t="s">
         <v>12</v>
@@ -15086,10 +15092,10 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C464" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D464" t="s">
         <v>12</v>
@@ -15101,7 +15107,7 @@
         <v>14</v>
       </c>
       <c r="H464">
-        <v>45174</v>
+        <v>45093</v>
       </c>
       <c r="I464" t="s">
         <v>12</v>
@@ -15109,13 +15115,13 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C465" t="s">
         <v>955</v>
       </c>
       <c r="D465" t="s">
-        <v>956</v>
+        <v>12</v>
       </c>
       <c r="F465" t="s">
         <v>24</v>
@@ -15124,7 +15130,7 @@
         <v>14</v>
       </c>
       <c r="H465">
-        <v>45435</v>
+        <v>45174</v>
       </c>
       <c r="I465" t="s">
         <v>12</v>
@@ -15132,22 +15138,22 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" t="s">
+        <v>956</v>
+      </c>
+      <c r="C466" t="s">
         <v>957</v>
       </c>
-      <c r="C466" t="s">
+      <c r="D466" t="s">
         <v>958</v>
       </c>
-      <c r="D466" t="s">
-        <v>959</v>
-      </c>
       <c r="F466" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G466" t="s">
         <v>14</v>
       </c>
       <c r="H466">
-        <v>45128</v>
+        <v>45435</v>
       </c>
       <c r="I466" t="s">
         <v>12</v>
@@ -15155,22 +15161,22 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C467" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D467" t="s">
-        <v>645</v>
+        <v>961</v>
       </c>
       <c r="F467" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G467" t="s">
         <v>14</v>
       </c>
       <c r="H467">
-        <v>46036</v>
+        <v>45128</v>
       </c>
       <c r="I467" t="s">
         <v>12</v>
@@ -15178,22 +15184,22 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468" t="s">
+        <v>959</v>
+      </c>
+      <c r="C468" t="s">
         <v>960</v>
       </c>
-      <c r="C468" t="s">
-        <v>961</v>
-      </c>
       <c r="D468" t="s">
-        <v>962</v>
+        <v>645</v>
       </c>
       <c r="F468" t="s">
-        <v>740</v>
+        <v>19</v>
       </c>
       <c r="G468" t="s">
         <v>14</v>
       </c>
       <c r="H468">
-        <v>46006</v>
+        <v>46036</v>
       </c>
       <c r="I468" t="s">
         <v>12</v>
@@ -15201,22 +15207,22 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C469" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D469" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F469" t="s">
-        <v>211</v>
+        <v>740</v>
       </c>
       <c r="G469" t="s">
         <v>14</v>
       </c>
       <c r="H469">
-        <v>46035</v>
+        <v>46006</v>
       </c>
       <c r="I469" t="s">
         <v>12</v>
@@ -15224,22 +15230,22 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C470" t="s">
+        <v>963</v>
+      </c>
+      <c r="D470" t="s">
         <v>965</v>
       </c>
-      <c r="D470" t="s">
-        <v>966</v>
-      </c>
       <c r="F470" t="s">
-        <v>967</v>
+        <v>211</v>
       </c>
       <c r="G470" t="s">
         <v>14</v>
       </c>
       <c r="H470">
-        <v>45085</v>
+        <v>46035</v>
       </c>
       <c r="I470" t="s">
         <v>12</v>
@@ -15247,22 +15253,22 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C471" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D471" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F471" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G471" t="s">
         <v>14</v>
       </c>
       <c r="H471">
-        <v>45617</v>
+        <v>45085</v>
       </c>
       <c r="I471" t="s">
         <v>12</v>
@@ -15270,22 +15276,22 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C472" t="s">
+        <v>967</v>
+      </c>
+      <c r="D472" t="s">
+        <v>968</v>
+      </c>
+      <c r="F472" t="s">
         <v>970</v>
       </c>
-      <c r="D472" t="s">
-        <v>971</v>
-      </c>
-      <c r="F472" t="s">
-        <v>19</v>
-      </c>
       <c r="G472" t="s">
         <v>14</v>
       </c>
       <c r="H472">
-        <v>45118</v>
+        <v>45617</v>
       </c>
       <c r="I472" t="s">
         <v>12</v>
@@ -15293,22 +15299,22 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473" t="s">
+        <v>971</v>
+      </c>
+      <c r="C473" t="s">
         <v>972</v>
       </c>
-      <c r="C473" t="s">
+      <c r="D473" t="s">
         <v>973</v>
       </c>
-      <c r="D473" t="s">
-        <v>610</v>
-      </c>
       <c r="F473" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
       </c>
       <c r="H473">
-        <v>45308</v>
+        <v>45118</v>
       </c>
       <c r="I473" t="s">
         <v>12</v>
@@ -15316,22 +15322,22 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C474" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D474" t="s">
         <v>610</v>
       </c>
       <c r="F474" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="G474" t="s">
         <v>14</v>
       </c>
       <c r="H474">
-        <v>45317</v>
+        <v>45308</v>
       </c>
       <c r="I474" t="s">
         <v>12</v>
@@ -15345,16 +15351,16 @@
         <v>975</v>
       </c>
       <c r="D475" t="s">
-        <v>976</v>
+        <v>610</v>
       </c>
       <c r="F475" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="G475" t="s">
         <v>14</v>
       </c>
       <c r="H475">
-        <v>45877</v>
+        <v>45317</v>
       </c>
       <c r="I475" t="s">
         <v>12</v>
@@ -15362,22 +15368,22 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" t="s">
+        <v>976</v>
+      </c>
+      <c r="C476" t="s">
         <v>977</v>
       </c>
-      <c r="C476" t="s">
+      <c r="D476" t="s">
         <v>978</v>
       </c>
-      <c r="D476" t="s">
-        <v>488</v>
-      </c>
       <c r="F476" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G476" t="s">
         <v>14</v>
       </c>
       <c r="H476">
-        <v>46148</v>
+        <v>45877</v>
       </c>
       <c r="I476" t="s">
         <v>12</v>
@@ -15391,16 +15397,16 @@
         <v>980</v>
       </c>
       <c r="D477" t="s">
-        <v>39</v>
+        <v>488</v>
       </c>
       <c r="F477" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G477" t="s">
         <v>14</v>
       </c>
       <c r="H477">
-        <v>45308</v>
+        <v>46148</v>
       </c>
       <c r="I477" t="s">
         <v>12</v>
@@ -15408,22 +15414,22 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C478" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D478" t="s">
         <v>39</v>
       </c>
       <c r="F478" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="G478" t="s">
         <v>14</v>
       </c>
       <c r="H478">
-        <v>45980</v>
+        <v>45308</v>
       </c>
       <c r="I478" t="s">
         <v>12</v>
@@ -15440,13 +15446,13 @@
         <v>39</v>
       </c>
       <c r="F479" t="s">
-        <v>769</v>
+        <v>211</v>
       </c>
       <c r="G479" t="s">
         <v>14</v>
       </c>
       <c r="H479">
-        <v>45103</v>
+        <v>45980</v>
       </c>
       <c r="I479" t="s">
         <v>12</v>
@@ -15456,23 +15462,20 @@
       <c r="A480" t="s">
         <v>983</v>
       </c>
-      <c r="B480" t="s">
+      <c r="C480" t="s">
         <v>984</v>
       </c>
-      <c r="C480" t="s">
-        <v>985</v>
-      </c>
       <c r="D480" t="s">
-        <v>986</v>
+        <v>39</v>
       </c>
       <c r="F480" t="s">
-        <v>18</v>
+        <v>771</v>
       </c>
       <c r="G480" t="s">
         <v>14</v>
       </c>
       <c r="H480">
-        <v>45278</v>
+        <v>45103</v>
       </c>
       <c r="I480" t="s">
         <v>12</v>
@@ -15480,19 +15483,19 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B481" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C481" t="s">
         <v>987</v>
       </c>
       <c r="D481" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F481" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="G481" t="s">
         <v>14</v>
@@ -15506,25 +15509,25 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B482" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C482" t="s">
+        <v>989</v>
+      </c>
+      <c r="D482" t="s">
         <v>988</v>
       </c>
-      <c r="D482" t="s">
-        <v>986</v>
-      </c>
       <c r="F482" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="G482" t="s">
         <v>14</v>
       </c>
       <c r="H482">
-        <v>45279</v>
+        <v>45278</v>
       </c>
       <c r="I482" t="s">
         <v>12</v>
@@ -15532,25 +15535,25 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B483" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C483" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D483" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F483" t="s">
-        <v>464</v>
+        <v>13</v>
       </c>
       <c r="G483" t="s">
         <v>14</v>
       </c>
       <c r="H483">
-        <v>45376</v>
+        <v>45279</v>
       </c>
       <c r="I483" t="s">
         <v>12</v>
@@ -15558,22 +15561,25 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" t="s">
+        <v>985</v>
+      </c>
+      <c r="B484" t="s">
+        <v>986</v>
+      </c>
+      <c r="C484" t="s">
         <v>991</v>
       </c>
-      <c r="C484" t="s">
+      <c r="D484" t="s">
         <v>992</v>
       </c>
-      <c r="D484" t="s">
-        <v>108</v>
-      </c>
       <c r="F484" t="s">
-        <v>13</v>
+        <v>464</v>
       </c>
       <c r="G484" t="s">
         <v>14</v>
       </c>
       <c r="H484">
-        <v>45939</v>
+        <v>45376</v>
       </c>
       <c r="I484" t="s">
         <v>12</v>
@@ -15587,10 +15593,7 @@
         <v>994</v>
       </c>
       <c r="D485" t="s">
-        <v>995</v>
-      </c>
-      <c r="E485" t="s">
-        <v>996</v>
+        <v>108</v>
       </c>
       <c r="F485" t="s">
         <v>13</v>
@@ -15599,7 +15602,7 @@
         <v>14</v>
       </c>
       <c r="H485">
-        <v>45803</v>
+        <v>45939</v>
       </c>
       <c r="I485" t="s">
         <v>12</v>
@@ -15607,22 +15610,25 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" t="s">
+        <v>995</v>
+      </c>
+      <c r="C486" t="s">
+        <v>996</v>
+      </c>
+      <c r="D486" t="s">
         <v>997</v>
       </c>
-      <c r="C486" t="s">
+      <c r="E486" t="s">
         <v>998</v>
       </c>
-      <c r="D486" t="s">
-        <v>12</v>
-      </c>
       <c r="F486" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G486" t="s">
         <v>14</v>
       </c>
       <c r="H486">
-        <v>45113</v>
+        <v>45803</v>
       </c>
       <c r="I486" t="s">
         <v>12</v>
@@ -15636,16 +15642,16 @@
         <v>1000</v>
       </c>
       <c r="D487" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="F487" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G487" t="s">
         <v>14</v>
       </c>
       <c r="H487">
-        <v>46035</v>
+        <v>45113</v>
       </c>
       <c r="I487" t="s">
         <v>12</v>
@@ -15656,19 +15662,19 @@
         <v>1001</v>
       </c>
       <c r="C488" t="s">
-        <v>293</v>
+        <v>1002</v>
       </c>
       <c r="D488" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="F488" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G488" t="s">
         <v>14</v>
       </c>
       <c r="H488">
-        <v>45378</v>
+        <v>46035</v>
       </c>
       <c r="I488" t="s">
         <v>12</v>
@@ -15676,7 +15682,7 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C489" t="s">
         <v>293</v>
@@ -15685,13 +15691,13 @@
         <v>233</v>
       </c>
       <c r="F489" t="s">
-        <v>740</v>
+        <v>22</v>
       </c>
       <c r="G489" t="s">
         <v>14</v>
       </c>
       <c r="H489">
-        <v>45856</v>
+        <v>45378</v>
       </c>
       <c r="I489" t="s">
         <v>12</v>
@@ -15699,7 +15705,7 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C490" t="s">
         <v>293</v>
@@ -15708,13 +15714,13 @@
         <v>233</v>
       </c>
       <c r="F490" t="s">
-        <v>1002</v>
+        <v>740</v>
       </c>
       <c r="G490" t="s">
         <v>14</v>
       </c>
       <c r="H490">
-        <v>45971</v>
+        <v>45856</v>
       </c>
       <c r="I490" t="s">
         <v>12</v>
@@ -15725,19 +15731,19 @@
         <v>1003</v>
       </c>
       <c r="C491" t="s">
+        <v>293</v>
+      </c>
+      <c r="D491" t="s">
+        <v>233</v>
+      </c>
+      <c r="F491" t="s">
         <v>1004</v>
       </c>
-      <c r="D491" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F491" t="s">
-        <v>967</v>
-      </c>
       <c r="G491" t="s">
         <v>14</v>
       </c>
       <c r="H491">
-        <v>45082</v>
+        <v>45971</v>
       </c>
       <c r="I491" t="s">
         <v>12</v>
@@ -15745,22 +15751,22 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C492" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D492" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F492" t="s">
-        <v>343</v>
+        <v>969</v>
       </c>
       <c r="G492" t="s">
         <v>14</v>
       </c>
       <c r="H492">
-        <v>45334</v>
+        <v>45082</v>
       </c>
       <c r="I492" t="s">
         <v>12</v>
@@ -15768,22 +15774,22 @@
     </row>
     <row r="493" spans="1:9">
       <c r="A493" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C493" t="s">
         <v>1006</v>
       </c>
-      <c r="C493" t="s">
+      <c r="D493" t="s">
         <v>1007</v>
       </c>
-      <c r="D493" t="s">
-        <v>1008</v>
-      </c>
       <c r="F493" t="s">
-        <v>740</v>
+        <v>343</v>
       </c>
       <c r="G493" t="s">
         <v>14</v>
       </c>
       <c r="H493">
-        <v>45909</v>
+        <v>45334</v>
       </c>
       <c r="I493" t="s">
         <v>12</v>
@@ -15791,22 +15797,22 @@
     </row>
     <row r="494" spans="1:9">
       <c r="A494" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C494" t="s">
         <v>1009</v>
       </c>
-      <c r="C494" t="s">
+      <c r="D494" t="s">
         <v>1010</v>
       </c>
-      <c r="D494" t="s">
-        <v>1011</v>
-      </c>
       <c r="F494" t="s">
-        <v>924</v>
+        <v>740</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
       </c>
       <c r="H494">
-        <v>45219</v>
+        <v>45909</v>
       </c>
       <c r="I494" t="s">
         <v>12</v>
@@ -15814,22 +15820,22 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C495" t="s">
         <v>1012</v>
       </c>
-      <c r="C495" t="s">
+      <c r="D495" t="s">
         <v>1013</v>
       </c>
-      <c r="D495" t="s">
-        <v>104</v>
-      </c>
       <c r="F495" t="s">
-        <v>13</v>
+        <v>926</v>
       </c>
       <c r="G495" t="s">
         <v>14</v>
       </c>
       <c r="H495">
-        <v>45415</v>
+        <v>45219</v>
       </c>
       <c r="I495" t="s">
         <v>12</v>
@@ -15843,16 +15849,16 @@
         <v>1015</v>
       </c>
       <c r="D496" t="s">
-        <v>1016</v>
+        <v>104</v>
       </c>
       <c r="F496" t="s">
-        <v>1017</v>
+        <v>13</v>
       </c>
       <c r="G496" t="s">
         <v>14</v>
       </c>
       <c r="H496">
-        <v>45387</v>
+        <v>45415</v>
       </c>
       <c r="I496" t="s">
         <v>12</v>
@@ -15860,25 +15866,22 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D497" t="s">
         <v>1018</v>
       </c>
-      <c r="B497" t="s">
+      <c r="F497" t="s">
         <v>1019</v>
       </c>
-      <c r="C497" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D497" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F497" t="s">
-        <v>22</v>
-      </c>
       <c r="G497" t="s">
         <v>14</v>
       </c>
       <c r="H497">
-        <v>44974</v>
+        <v>45387</v>
       </c>
       <c r="I497" t="s">
         <v>12</v>
@@ -15886,25 +15889,25 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B498" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C498" t="s">
         <v>1022</v>
       </c>
       <c r="D498" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="F498" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G498" t="s">
         <v>14</v>
       </c>
       <c r="H498">
-        <v>45271</v>
+        <v>44974</v>
       </c>
       <c r="I498" t="s">
         <v>12</v>
@@ -15912,22 +15915,25 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499" t="s">
-        <v>1023</v>
+        <v>1020</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1021</v>
       </c>
       <c r="C499" t="s">
         <v>1024</v>
       </c>
       <c r="D499" t="s">
-        <v>217</v>
+        <v>1023</v>
       </c>
       <c r="F499" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G499" t="s">
         <v>14</v>
       </c>
       <c r="H499">
-        <v>46079</v>
+        <v>45271</v>
       </c>
       <c r="I499" t="s">
         <v>12</v>
@@ -15941,16 +15947,16 @@
         <v>1026</v>
       </c>
       <c r="D500" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F500" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
       </c>
       <c r="H500">
-        <v>45061</v>
+        <v>46079</v>
       </c>
       <c r="I500" t="s">
         <v>12</v>
@@ -15958,22 +15964,22 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C501" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D501" t="s">
         <v>225</v>
       </c>
       <c r="F501" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G501" t="s">
         <v>14</v>
       </c>
       <c r="H501">
-        <v>45638</v>
+        <v>45061</v>
       </c>
       <c r="I501" t="s">
         <v>12</v>
@@ -15987,16 +15993,16 @@
         <v>1028</v>
       </c>
       <c r="D502" t="s">
-        <v>1029</v>
+        <v>225</v>
       </c>
       <c r="F502" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
       </c>
       <c r="H502">
-        <v>45016</v>
+        <v>45638</v>
       </c>
       <c r="I502" t="s">
         <v>12</v>
@@ -16004,25 +16010,22 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C503" t="s">
         <v>1030</v>
       </c>
-      <c r="B503" t="s">
+      <c r="D503" t="s">
         <v>1031</v>
       </c>
-      <c r="C503" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D503" t="s">
-        <v>1033</v>
-      </c>
       <c r="F503" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G503" t="s">
         <v>14</v>
       </c>
       <c r="H503">
-        <v>45051</v>
+        <v>45016</v>
       </c>
       <c r="I503" t="s">
         <v>12</v>
@@ -16030,22 +16033,25 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C504" t="s">
         <v>1034</v>
       </c>
-      <c r="C504" t="s">
+      <c r="D504" t="s">
         <v>1035</v>
       </c>
-      <c r="D504" t="s">
-        <v>104</v>
-      </c>
       <c r="F504" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G504" t="s">
         <v>14</v>
       </c>
       <c r="H504">
-        <v>45093</v>
+        <v>45051</v>
       </c>
       <c r="I504" t="s">
         <v>12</v>
@@ -16059,16 +16065,16 @@
         <v>1037</v>
       </c>
       <c r="D505" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F505" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
       </c>
       <c r="H505">
-        <v>45376</v>
+        <v>45093</v>
       </c>
       <c r="I505" t="s">
         <v>12</v>
@@ -16076,22 +16082,22 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C506" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D506" t="s">
         <v>39</v>
       </c>
       <c r="F506" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
       </c>
       <c r="H506">
-        <v>45400</v>
+        <v>45376</v>
       </c>
       <c r="I506" t="s">
         <v>12</v>
@@ -16099,7 +16105,7 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C507" t="s">
         <v>1040</v>
@@ -16108,13 +16114,13 @@
         <v>39</v>
       </c>
       <c r="F507" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="G507" t="s">
         <v>14</v>
       </c>
       <c r="H507">
-        <v>45133</v>
+        <v>45400</v>
       </c>
       <c r="I507" t="s">
         <v>12</v>
@@ -16122,22 +16128,22 @@
     </row>
     <row r="508" spans="1:9">
       <c r="A508" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C508" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D508" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F508" t="s">
-        <v>378</v>
+        <v>129</v>
       </c>
       <c r="G508" t="s">
         <v>14</v>
       </c>
       <c r="H508">
-        <v>45443</v>
+        <v>45133</v>
       </c>
       <c r="I508" t="s">
         <v>12</v>
@@ -16145,22 +16151,22 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C509" t="s">
         <v>1043</v>
       </c>
       <c r="D509" t="s">
-        <v>505</v>
+        <v>12</v>
       </c>
       <c r="F509" t="s">
-        <v>144</v>
+        <v>378</v>
       </c>
       <c r="G509" t="s">
         <v>14</v>
       </c>
       <c r="H509">
-        <v>45126</v>
+        <v>45443</v>
       </c>
       <c r="I509" t="s">
         <v>12</v>
@@ -16174,16 +16180,16 @@
         <v>1045</v>
       </c>
       <c r="D510" t="s">
-        <v>12</v>
+        <v>505</v>
       </c>
       <c r="F510" t="s">
-        <v>1046</v>
+        <v>144</v>
       </c>
       <c r="G510" t="s">
         <v>14</v>
       </c>
       <c r="H510">
-        <v>45317</v>
+        <v>45126</v>
       </c>
       <c r="I510" t="s">
         <v>12</v>
@@ -16191,22 +16197,22 @@
     </row>
     <row r="511" spans="1:9">
       <c r="A511" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C511" t="s">
         <v>1047</v>
       </c>
-      <c r="C511" t="s">
+      <c r="D511" t="s">
+        <v>12</v>
+      </c>
+      <c r="F511" t="s">
         <v>1048</v>
       </c>
-      <c r="D511" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F511" t="s">
-        <v>19</v>
-      </c>
       <c r="G511" t="s">
         <v>14</v>
       </c>
       <c r="H511">
-        <v>45404</v>
+        <v>45317</v>
       </c>
       <c r="I511" t="s">
         <v>12</v>
@@ -16214,22 +16220,22 @@
     </row>
     <row r="512" spans="1:9">
       <c r="A512" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C512" t="s">
         <v>1050</v>
       </c>
-      <c r="C512" t="s">
+      <c r="D512" t="s">
         <v>1051</v>
       </c>
-      <c r="D512" t="s">
-        <v>29</v>
-      </c>
       <c r="F512" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G512" t="s">
         <v>14</v>
       </c>
       <c r="H512">
-        <v>46010</v>
+        <v>45404</v>
       </c>
       <c r="I512" t="s">
         <v>12</v>
@@ -16243,16 +16249,16 @@
         <v>1053</v>
       </c>
       <c r="D513" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F513" t="s">
-        <v>721</v>
+        <v>42</v>
       </c>
       <c r="G513" t="s">
         <v>14</v>
       </c>
       <c r="H513">
-        <v>46105</v>
+        <v>46010</v>
       </c>
       <c r="I513" t="s">
         <v>12</v>
@@ -16266,16 +16272,16 @@
         <v>1055</v>
       </c>
       <c r="D514" t="s">
-        <v>1056</v>
+        <v>12</v>
       </c>
       <c r="F514" t="s">
-        <v>13</v>
+        <v>721</v>
       </c>
       <c r="G514" t="s">
         <v>14</v>
       </c>
       <c r="H514">
-        <v>45593</v>
+        <v>46105</v>
       </c>
       <c r="I514" t="s">
         <v>12</v>
@@ -16283,13 +16289,13 @@
     </row>
     <row r="515" spans="1:9">
       <c r="A515" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C515" t="s">
         <v>1057</v>
       </c>
-      <c r="C515" t="s">
+      <c r="D515" t="s">
         <v>1058</v>
-      </c>
-      <c r="D515" t="s">
-        <v>217</v>
       </c>
       <c r="F515" t="s">
         <v>13</v>
@@ -16298,7 +16304,7 @@
         <v>14</v>
       </c>
       <c r="H515">
-        <v>46101</v>
+        <v>45593</v>
       </c>
       <c r="I515" t="s">
         <v>12</v>
@@ -16312,16 +16318,16 @@
         <v>1060</v>
       </c>
       <c r="D516" t="s">
-        <v>512</v>
+        <v>217</v>
       </c>
       <c r="F516" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
       </c>
       <c r="H516">
-        <v>45329</v>
+        <v>46101</v>
       </c>
       <c r="I516" t="s">
         <v>12</v>
@@ -16329,10 +16335,10 @@
     </row>
     <row r="517" spans="1:9">
       <c r="A517" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C517" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D517" t="s">
         <v>512</v>
@@ -16344,7 +16350,7 @@
         <v>14</v>
       </c>
       <c r="H517">
-        <v>46065</v>
+        <v>45329</v>
       </c>
       <c r="I517" t="s">
         <v>12</v>
@@ -16358,7 +16364,7 @@
         <v>1062</v>
       </c>
       <c r="D518" t="s">
-        <v>1063</v>
+        <v>512</v>
       </c>
       <c r="F518" t="s">
         <v>35</v>
@@ -16367,7 +16373,7 @@
         <v>14</v>
       </c>
       <c r="H518">
-        <v>45720</v>
+        <v>46065</v>
       </c>
       <c r="I518" t="s">
         <v>12</v>
@@ -16375,13 +16381,13 @@
     </row>
     <row r="519" spans="1:9">
       <c r="A519" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C519" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D519" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F519" t="s">
         <v>35</v>
@@ -16390,7 +16396,7 @@
         <v>14</v>
       </c>
       <c r="H519">
-        <v>46112</v>
+        <v>45720</v>
       </c>
       <c r="I519" t="s">
         <v>12</v>
@@ -16398,22 +16404,22 @@
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C520" t="s">
         <v>1064</v>
       </c>
-      <c r="C520" t="s">
+      <c r="D520" t="s">
         <v>1065</v>
       </c>
-      <c r="D520" t="s">
-        <v>1066</v>
-      </c>
       <c r="F520" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G520" t="s">
         <v>14</v>
       </c>
       <c r="H520">
-        <v>46097</v>
+        <v>46112</v>
       </c>
       <c r="I520" t="s">
         <v>12</v>
@@ -16421,22 +16427,22 @@
     </row>
     <row r="521" spans="1:9">
       <c r="A521" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C521" t="s">
         <v>1067</v>
       </c>
-      <c r="C521" t="s">
+      <c r="D521" t="s">
         <v>1068</v>
       </c>
-      <c r="D521" t="s">
-        <v>12</v>
-      </c>
       <c r="F521" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="G521" t="s">
         <v>14</v>
       </c>
       <c r="H521">
-        <v>45190</v>
+        <v>46097</v>
       </c>
       <c r="I521" t="s">
         <v>12</v>
@@ -16446,23 +16452,20 @@
       <c r="A522" t="s">
         <v>1069</v>
       </c>
-      <c r="B522" t="s">
+      <c r="C522" t="s">
         <v>1070</v>
       </c>
-      <c r="C522" t="s">
-        <v>1071</v>
-      </c>
       <c r="D522" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F522" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="G522" t="s">
         <v>14</v>
       </c>
       <c r="H522">
-        <v>45565</v>
+        <v>45190</v>
       </c>
       <c r="I522" t="s">
         <v>12</v>
@@ -16470,22 +16473,25 @@
     </row>
     <row r="523" spans="1:9">
       <c r="A523" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B523" t="s">
         <v>1072</v>
       </c>
       <c r="C523" t="s">
         <v>1073</v>
       </c>
       <c r="D523" t="s">
-        <v>217</v>
+        <v>34</v>
       </c>
       <c r="F523" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="G523" t="s">
         <v>14</v>
       </c>
       <c r="H523">
-        <v>46000</v>
+        <v>45565</v>
       </c>
       <c r="I523" t="s">
         <v>12</v>
@@ -16493,22 +16499,22 @@
     </row>
     <row r="524" spans="1:9">
       <c r="A524" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C524" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D524" t="s">
         <v>217</v>
       </c>
       <c r="F524" t="s">
-        <v>1074</v>
+        <v>211</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
       </c>
       <c r="H524">
-        <v>46044</v>
+        <v>46000</v>
       </c>
       <c r="I524" t="s">
         <v>12</v>
@@ -16516,22 +16522,22 @@
     </row>
     <row r="525" spans="1:9">
       <c r="A525" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C525" t="s">
         <v>1075</v>
       </c>
-      <c r="C525" t="s">
+      <c r="D525" t="s">
+        <v>217</v>
+      </c>
+      <c r="F525" t="s">
         <v>1076</v>
       </c>
-      <c r="D525" t="s">
-        <v>12</v>
-      </c>
-      <c r="F525" t="s">
-        <v>35</v>
-      </c>
       <c r="G525" t="s">
         <v>14</v>
       </c>
       <c r="H525">
-        <v>46059</v>
+        <v>46044</v>
       </c>
       <c r="I525" t="s">
         <v>12</v>
@@ -16545,16 +16551,16 @@
         <v>1078</v>
       </c>
       <c r="D526" t="s">
-        <v>1079</v>
+        <v>12</v>
       </c>
       <c r="F526" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G526" t="s">
         <v>14</v>
       </c>
       <c r="H526">
-        <v>45083</v>
+        <v>46059</v>
       </c>
       <c r="I526" t="s">
         <v>12</v>
@@ -16562,22 +16568,22 @@
     </row>
     <row r="527" spans="1:9">
       <c r="A527" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C527" t="s">
         <v>1080</v>
       </c>
-      <c r="C527" t="s">
+      <c r="D527" t="s">
         <v>1081</v>
       </c>
-      <c r="D527" t="s">
-        <v>389</v>
-      </c>
       <c r="F527" t="s">
-        <v>263</v>
+        <v>42</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
       </c>
       <c r="H527">
-        <v>45593</v>
+        <v>45083</v>
       </c>
       <c r="I527" t="s">
         <v>12</v>
@@ -16591,16 +16597,16 @@
         <v>1083</v>
       </c>
       <c r="D528" t="s">
-        <v>1084</v>
+        <v>389</v>
       </c>
       <c r="F528" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
       </c>
       <c r="H528">
-        <v>46006</v>
+        <v>45593</v>
       </c>
       <c r="I528" t="s">
         <v>12</v>
@@ -16608,22 +16614,22 @@
     </row>
     <row r="529" spans="1:9">
       <c r="A529" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C529" t="s">
         <v>1085</v>
       </c>
-      <c r="C529" t="s">
+      <c r="D529" t="s">
         <v>1086</v>
       </c>
-      <c r="D529" t="s">
-        <v>1087</v>
-      </c>
       <c r="F529" t="s">
-        <v>1088</v>
+        <v>22</v>
       </c>
       <c r="G529" t="s">
         <v>14</v>
       </c>
       <c r="H529">
-        <v>45573</v>
+        <v>46006</v>
       </c>
       <c r="I529" t="s">
         <v>12</v>
@@ -16631,22 +16637,22 @@
     </row>
     <row r="530" spans="1:9">
       <c r="A530" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D530" t="s">
         <v>1089</v>
       </c>
-      <c r="C530" t="s">
+      <c r="F530" t="s">
         <v>1090</v>
       </c>
-      <c r="D530" t="s">
-        <v>104</v>
-      </c>
-      <c r="F530" t="s">
-        <v>42</v>
-      </c>
       <c r="G530" t="s">
         <v>14</v>
       </c>
       <c r="H530">
-        <v>46080</v>
+        <v>45573</v>
       </c>
       <c r="I530" t="s">
         <v>12</v>
@@ -16660,16 +16666,16 @@
         <v>1092</v>
       </c>
       <c r="D531" t="s">
-        <v>1093</v>
+        <v>104</v>
       </c>
       <c r="F531" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
       </c>
       <c r="H531">
-        <v>45049</v>
+        <v>46080</v>
       </c>
       <c r="I531" t="s">
         <v>12</v>
@@ -16677,22 +16683,22 @@
     </row>
     <row r="532" spans="1:9">
       <c r="A532" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C532" t="s">
         <v>1094</v>
       </c>
       <c r="D532" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F532" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G532" t="s">
         <v>14</v>
       </c>
       <c r="H532">
-        <v>45114</v>
+        <v>45049</v>
       </c>
       <c r="I532" t="s">
         <v>12</v>
@@ -16700,25 +16706,22 @@
     </row>
     <row r="533" spans="1:9">
       <c r="A533" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C533" t="s">
         <v>1096</v>
       </c>
       <c r="D533" t="s">
-        <v>302</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F533" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G533" t="s">
         <v>14</v>
       </c>
       <c r="H533">
-        <v>45727</v>
+        <v>45114</v>
       </c>
       <c r="I533" t="s">
         <v>12</v>
@@ -16726,25 +16729,25 @@
     </row>
     <row r="534" spans="1:9">
       <c r="A534" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C534" t="s">
         <v>1098</v>
       </c>
       <c r="D534" t="s">
+        <v>302</v>
+      </c>
+      <c r="E534" t="s">
         <v>1099</v>
       </c>
-      <c r="E534" t="s">
-        <v>1100</v>
-      </c>
       <c r="F534" t="s">
-        <v>1101</v>
+        <v>22</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
       </c>
       <c r="H534">
-        <v>45797</v>
+        <v>45727</v>
       </c>
       <c r="I534" t="s">
         <v>12</v>
@@ -16752,25 +16755,25 @@
     </row>
     <row r="535" spans="1:9">
       <c r="A535" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C535" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E535" t="s">
         <v>1102</v>
       </c>
-      <c r="D535" t="s">
-        <v>155</v>
-      </c>
-      <c r="E535" t="s">
+      <c r="F535" t="s">
         <v>1103</v>
       </c>
-      <c r="F535" t="s">
-        <v>60</v>
-      </c>
       <c r="G535" t="s">
         <v>14</v>
       </c>
       <c r="H535">
-        <v>45747</v>
+        <v>45797</v>
       </c>
       <c r="I535" t="s">
         <v>12</v>
@@ -16778,25 +16781,25 @@
     </row>
     <row r="536" spans="1:9">
       <c r="A536" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C536" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D536" t="s">
         <v>155</v>
       </c>
       <c r="E536" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F536" t="s">
-        <v>1104</v>
+        <v>60</v>
       </c>
       <c r="G536" t="s">
         <v>14</v>
       </c>
       <c r="H536">
-        <v>45813</v>
+        <v>45747</v>
       </c>
       <c r="I536" t="s">
         <v>12</v>
@@ -16804,25 +16807,25 @@
     </row>
     <row r="537" spans="1:9">
       <c r="A537" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C537" t="s">
-        <v>168</v>
+        <v>1104</v>
       </c>
       <c r="D537" t="s">
-        <v>610</v>
+        <v>155</v>
       </c>
       <c r="E537" t="s">
-        <v>182</v>
+        <v>1105</v>
       </c>
       <c r="F537" t="s">
-        <v>22</v>
+        <v>1106</v>
       </c>
       <c r="G537" t="s">
         <v>14</v>
       </c>
       <c r="H537">
-        <v>45043</v>
+        <v>45813</v>
       </c>
       <c r="I537" t="s">
         <v>12</v>
@@ -16830,16 +16833,16 @@
     </row>
     <row r="538" spans="1:9">
       <c r="A538" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C538" t="s">
-        <v>1105</v>
+        <v>168</v>
       </c>
       <c r="D538" t="s">
-        <v>104</v>
+        <v>610</v>
       </c>
       <c r="E538" t="s">
-        <v>1106</v>
+        <v>182</v>
       </c>
       <c r="F538" t="s">
         <v>22</v>
@@ -16856,25 +16859,25 @@
     </row>
     <row r="539" spans="1:9">
       <c r="A539" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C539" t="s">
         <v>1107</v>
       </c>
       <c r="D539" t="s">
-        <v>217</v>
+        <v>104</v>
       </c>
       <c r="E539" t="s">
         <v>1108</v>
       </c>
       <c r="F539" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G539" t="s">
         <v>14</v>
       </c>
       <c r="H539">
-        <v>45184</v>
+        <v>45043</v>
       </c>
       <c r="I539" t="s">
         <v>12</v>
@@ -16882,7 +16885,7 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C540" t="s">
         <v>1109</v>
@@ -16891,7 +16894,7 @@
         <v>217</v>
       </c>
       <c r="E540" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="F540" t="s">
         <v>13</v>
@@ -16900,7 +16903,7 @@
         <v>14</v>
       </c>
       <c r="H540">
-        <v>45219</v>
+        <v>45184</v>
       </c>
       <c r="I540" t="s">
         <v>12</v>
@@ -16908,16 +16911,16 @@
     </row>
     <row r="541" spans="1:9">
       <c r="A541" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C541" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D541" t="s">
+        <v>217</v>
+      </c>
+      <c r="E541" t="s">
         <v>1110</v>
-      </c>
-      <c r="D541" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1112</v>
       </c>
       <c r="F541" t="s">
         <v>13</v>
@@ -16926,7 +16929,7 @@
         <v>14</v>
       </c>
       <c r="H541">
-        <v>45303</v>
+        <v>45219</v>
       </c>
       <c r="I541" t="s">
         <v>12</v>
@@ -16934,12 +16937,15 @@
     </row>
     <row r="542" spans="1:9">
       <c r="A542" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C542" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D542" t="s">
         <v>1113</v>
       </c>
-      <c r="D542" t="s">
+      <c r="E542" t="s">
         <v>1114</v>
       </c>
       <c r="F542" t="s">
@@ -16949,7 +16955,7 @@
         <v>14</v>
       </c>
       <c r="H542">
-        <v>45327</v>
+        <v>45303</v>
       </c>
       <c r="I542" t="s">
         <v>12</v>
@@ -16957,16 +16963,13 @@
     </row>
     <row r="543" spans="1:9">
       <c r="A543" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C543" t="s">
         <v>1115</v>
       </c>
       <c r="D543" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F543" t="s">
         <v>13</v>
@@ -16983,12 +16986,15 @@
     </row>
     <row r="544" spans="1:9">
       <c r="A544" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C544" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D544" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E544" t="s">
         <v>1114</v>
       </c>
       <c r="F544" t="s">
@@ -17006,16 +17012,13 @@
     </row>
     <row r="545" spans="1:9">
       <c r="A545" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C545" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D545" t="s">
-        <v>54</v>
-      </c>
-      <c r="E545" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -17024,7 +17027,7 @@
         <v>14</v>
       </c>
       <c r="H545">
-        <v>45439</v>
+        <v>45327</v>
       </c>
       <c r="I545" t="s">
         <v>12</v>
@@ -17032,22 +17035,25 @@
     </row>
     <row r="546" spans="1:9">
       <c r="A546" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C546" t="s">
         <v>1119</v>
       </c>
       <c r="D546" t="s">
-        <v>346</v>
+        <v>54</v>
+      </c>
+      <c r="E546" t="s">
+        <v>1120</v>
       </c>
       <c r="F546" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G546" t="s">
         <v>14</v>
       </c>
       <c r="H546">
-        <v>45951</v>
+        <v>45439</v>
       </c>
       <c r="I546" t="s">
         <v>12</v>
@@ -17055,22 +17061,22 @@
     </row>
     <row r="547" spans="1:9">
       <c r="A547" t="s">
-        <v>1120</v>
+        <v>1097</v>
       </c>
       <c r="C547" t="s">
         <v>1121</v>
       </c>
       <c r="D547" t="s">
-        <v>1122</v>
+        <v>346</v>
       </c>
       <c r="F547" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G547" t="s">
         <v>14</v>
       </c>
       <c r="H547">
-        <v>45022</v>
+        <v>45951</v>
       </c>
       <c r="I547" t="s">
         <v>12</v>
@@ -17078,22 +17084,22 @@
     </row>
     <row r="548" spans="1:9">
       <c r="A548" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C548" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="D548" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F548" t="s">
-        <v>211</v>
+        <v>22</v>
       </c>
       <c r="G548" t="s">
         <v>14</v>
       </c>
       <c r="H548">
-        <v>45275</v>
+        <v>45022</v>
       </c>
       <c r="I548" t="s">
         <v>12</v>
@@ -17101,22 +17107,22 @@
     </row>
     <row r="549" spans="1:9">
       <c r="A549" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C549" t="s">
         <v>1123</v>
       </c>
-      <c r="C549" t="s">
+      <c r="D549" t="s">
         <v>1124</v>
       </c>
-      <c r="D549" t="s">
-        <v>1125</v>
-      </c>
       <c r="F549" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="G549" t="s">
         <v>14</v>
       </c>
       <c r="H549">
-        <v>45792</v>
+        <v>45275</v>
       </c>
       <c r="I549" t="s">
         <v>12</v>
@@ -17124,13 +17130,13 @@
     </row>
     <row r="550" spans="1:9">
       <c r="A550" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C550" t="s">
         <v>1126</v>
       </c>
-      <c r="C550" t="s">
+      <c r="D550" t="s">
         <v>1127</v>
-      </c>
-      <c r="D550" t="s">
-        <v>104</v>
       </c>
       <c r="F550" t="s">
         <v>13</v>
@@ -17139,7 +17145,7 @@
         <v>14</v>
       </c>
       <c r="H550">
-        <v>45722</v>
+        <v>45792</v>
       </c>
       <c r="I550" t="s">
         <v>12</v>
@@ -17153,16 +17159,16 @@
         <v>1129</v>
       </c>
       <c r="D551" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F551" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G551" t="s">
         <v>14</v>
       </c>
       <c r="H551">
-        <v>45107</v>
+        <v>45722</v>
       </c>
       <c r="I551" t="s">
         <v>12</v>
@@ -17179,13 +17185,13 @@
         <v>12</v>
       </c>
       <c r="F552" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G552" t="s">
         <v>14</v>
       </c>
       <c r="H552">
-        <v>45356</v>
+        <v>45107</v>
       </c>
       <c r="I552" t="s">
         <v>12</v>
@@ -17193,22 +17199,22 @@
     </row>
     <row r="553" spans="1:9">
       <c r="A553" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C553" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D553" t="s">
         <v>12</v>
       </c>
       <c r="F553" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="G553" t="s">
         <v>14</v>
       </c>
       <c r="H553">
-        <v>45107</v>
+        <v>45356</v>
       </c>
       <c r="I553" t="s">
         <v>12</v>
@@ -17216,22 +17222,22 @@
     </row>
     <row r="554" spans="1:9">
       <c r="A554" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C554" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D554" t="s">
         <v>12</v>
       </c>
       <c r="F554" t="s">
-        <v>375</v>
+        <v>111</v>
       </c>
       <c r="G554" t="s">
         <v>14</v>
       </c>
       <c r="H554">
-        <v>45141</v>
+        <v>45107</v>
       </c>
       <c r="I554" t="s">
         <v>12</v>
@@ -17239,22 +17245,22 @@
     </row>
     <row r="555" spans="1:9">
       <c r="A555" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C555" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D555" t="s">
         <v>12</v>
       </c>
       <c r="F555" t="s">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="G555" t="s">
         <v>14</v>
       </c>
       <c r="H555">
-        <v>45194</v>
+        <v>45141</v>
       </c>
       <c r="I555" t="s">
         <v>12</v>
@@ -17262,22 +17268,22 @@
     </row>
     <row r="556" spans="1:9">
       <c r="A556" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="C556" t="s">
         <v>1135</v>
       </c>
       <c r="D556" t="s">
-        <v>262</v>
+        <v>12</v>
       </c>
       <c r="F556" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="G556" t="s">
         <v>14</v>
       </c>
       <c r="H556">
-        <v>45856</v>
+        <v>45194</v>
       </c>
       <c r="I556" t="s">
         <v>12</v>
@@ -17285,16 +17291,16 @@
     </row>
     <row r="557" spans="1:9">
       <c r="A557" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C557" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D557" t="s">
         <v>262</v>
       </c>
       <c r="F557" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="G557" t="s">
         <v>14</v>
@@ -17308,22 +17314,22 @@
     </row>
     <row r="558" spans="1:9">
       <c r="A558" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C558" t="s">
         <v>1138</v>
       </c>
       <c r="D558" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="F558" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G558" t="s">
         <v>14</v>
       </c>
       <c r="H558">
-        <v>45392</v>
+        <v>45856</v>
       </c>
       <c r="I558" t="s">
         <v>12</v>
@@ -17331,13 +17337,13 @@
     </row>
     <row r="559" spans="1:9">
       <c r="A559" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C559" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D559" t="s">
-        <v>1139</v>
+        <v>83</v>
       </c>
       <c r="F559" t="s">
         <v>35</v>
@@ -17346,7 +17352,7 @@
         <v>14</v>
       </c>
       <c r="H559">
-        <v>45792</v>
+        <v>45392</v>
       </c>
       <c r="I559" t="s">
         <v>12</v>
@@ -17354,13 +17360,13 @@
     </row>
     <row r="560" spans="1:9">
       <c r="A560" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C560" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D560" t="s">
-        <v>389</v>
+        <v>1141</v>
       </c>
       <c r="F560" t="s">
         <v>35</v>
@@ -17369,7 +17375,7 @@
         <v>14</v>
       </c>
       <c r="H560">
-        <v>46107</v>
+        <v>45792</v>
       </c>
       <c r="I560" t="s">
         <v>12</v>
@@ -17377,13 +17383,13 @@
     </row>
     <row r="561" spans="1:9">
       <c r="A561" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C561" t="s">
         <v>1140</v>
       </c>
-      <c r="C561" t="s">
-        <v>1141</v>
-      </c>
       <c r="D561" t="s">
-        <v>1142</v>
+        <v>389</v>
       </c>
       <c r="F561" t="s">
         <v>35</v>
@@ -17392,7 +17398,7 @@
         <v>14</v>
       </c>
       <c r="H561">
-        <v>45495</v>
+        <v>46107</v>
       </c>
       <c r="I561" t="s">
         <v>12</v>
@@ -17400,13 +17406,13 @@
     </row>
     <row r="562" spans="1:9">
       <c r="A562" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C562" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D562" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="F562" t="s">
         <v>35</v>
@@ -17415,7 +17421,7 @@
         <v>14</v>
       </c>
       <c r="H562">
-        <v>46097</v>
+        <v>45495</v>
       </c>
       <c r="I562" t="s">
         <v>12</v>
@@ -17423,22 +17429,22 @@
     </row>
     <row r="563" spans="1:9">
       <c r="A563" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C563" t="s">
         <v>1143</v>
       </c>
-      <c r="C563" t="s">
+      <c r="D563" t="s">
         <v>1144</v>
       </c>
-      <c r="D563" t="s">
-        <v>1145</v>
-      </c>
       <c r="F563" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G563" t="s">
         <v>14</v>
       </c>
       <c r="H563">
-        <v>45223</v>
+        <v>46097</v>
       </c>
       <c r="I563" t="s">
         <v>12</v>
@@ -17446,22 +17452,22 @@
     </row>
     <row r="564" spans="1:9">
       <c r="A564" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="C564" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D564" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="F564" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G564" t="s">
         <v>14</v>
       </c>
       <c r="H564">
-        <v>45254</v>
+        <v>45223</v>
       </c>
       <c r="I564" t="s">
         <v>12</v>
@@ -17469,22 +17475,22 @@
     </row>
     <row r="565" spans="1:9">
       <c r="A565" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C565" t="s">
         <v>1146</v>
       </c>
-      <c r="C565" t="s">
+      <c r="D565" t="s">
         <v>1147</v>
       </c>
-      <c r="D565" t="s">
-        <v>12</v>
-      </c>
       <c r="F565" t="s">
-        <v>721</v>
+        <v>19</v>
       </c>
       <c r="G565" t="s">
         <v>14</v>
       </c>
       <c r="H565">
-        <v>45807</v>
+        <v>45254</v>
       </c>
       <c r="I565" t="s">
         <v>12</v>
@@ -17501,13 +17507,13 @@
         <v>12</v>
       </c>
       <c r="F566" t="s">
-        <v>13</v>
+        <v>721</v>
       </c>
       <c r="G566" t="s">
         <v>14</v>
       </c>
       <c r="H566">
-        <v>45849</v>
+        <v>45807</v>
       </c>
       <c r="I566" t="s">
         <v>12</v>
@@ -17521,7 +17527,7 @@
         <v>1151</v>
       </c>
       <c r="D567" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F567" t="s">
         <v>13</v>
@@ -17530,7 +17536,7 @@
         <v>14</v>
       </c>
       <c r="H567">
-        <v>46000</v>
+        <v>45849</v>
       </c>
       <c r="I567" t="s">
         <v>12</v>
@@ -17538,10 +17544,10 @@
     </row>
     <row r="568" spans="1:9">
       <c r="A568" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C568" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D568" t="s">
         <v>29</v>
@@ -17553,7 +17559,7 @@
         <v>14</v>
       </c>
       <c r="H568">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="I568" t="s">
         <v>12</v>
@@ -17561,22 +17567,22 @@
     </row>
     <row r="569" spans="1:9">
       <c r="A569" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C569" t="s">
         <v>1154</v>
       </c>
       <c r="D569" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="F569" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G569" t="s">
         <v>14</v>
       </c>
       <c r="H569">
-        <v>45825</v>
+        <v>46010</v>
       </c>
       <c r="I569" t="s">
         <v>12</v>
@@ -17584,22 +17590,22 @@
     </row>
     <row r="570" spans="1:9">
       <c r="A570" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C570" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D570" t="s">
-        <v>1155</v>
+        <v>104</v>
       </c>
       <c r="F570" t="s">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="G570" t="s">
         <v>14</v>
       </c>
       <c r="H570">
-        <v>46078</v>
+        <v>45825</v>
       </c>
       <c r="I570" t="s">
         <v>12</v>
@@ -17607,22 +17613,22 @@
     </row>
     <row r="571" spans="1:9">
       <c r="A571" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C571" t="s">
         <v>1156</v>
       </c>
-      <c r="C571" t="s">
+      <c r="D571" t="s">
         <v>1157</v>
       </c>
-      <c r="D571" t="s">
-        <v>1158</v>
-      </c>
       <c r="F571" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="G571" t="s">
         <v>14</v>
       </c>
       <c r="H571">
-        <v>46035</v>
+        <v>46078</v>
       </c>
       <c r="I571" t="s">
         <v>12</v>
@@ -17630,22 +17636,22 @@
     </row>
     <row r="572" spans="1:9">
       <c r="A572" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C572" t="s">
         <v>1159</v>
       </c>
-      <c r="C572" t="s">
+      <c r="D572" t="s">
         <v>1160</v>
       </c>
-      <c r="D572" t="s">
-        <v>29</v>
-      </c>
       <c r="F572" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G572" t="s">
         <v>14</v>
       </c>
       <c r="H572">
-        <v>46101</v>
+        <v>46035</v>
       </c>
       <c r="I572" t="s">
         <v>12</v>
@@ -17659,16 +17665,16 @@
         <v>1162</v>
       </c>
       <c r="D573" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="F573" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G573" t="s">
         <v>14</v>
       </c>
       <c r="H573">
-        <v>45985</v>
+        <v>46101</v>
       </c>
       <c r="I573" t="s">
         <v>12</v>
@@ -17682,16 +17688,16 @@
         <v>1164</v>
       </c>
       <c r="D574" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F574" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G574" t="s">
         <v>14</v>
       </c>
       <c r="H574">
-        <v>45190</v>
+        <v>45985</v>
       </c>
       <c r="I574" t="s">
         <v>12</v>
@@ -17705,16 +17711,16 @@
         <v>1166</v>
       </c>
       <c r="D575" t="s">
-        <v>1167</v>
+        <v>12</v>
       </c>
       <c r="F575" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G575" t="s">
         <v>14</v>
       </c>
       <c r="H575">
-        <v>45029</v>
+        <v>45190</v>
       </c>
       <c r="I575" t="s">
         <v>12</v>
@@ -17722,25 +17728,22 @@
     </row>
     <row r="576" spans="1:9">
       <c r="A576" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C576" t="s">
         <v>1168</v>
       </c>
-      <c r="C576" t="s">
+      <c r="D576" t="s">
         <v>1169</v>
       </c>
-      <c r="D576" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1171</v>
-      </c>
       <c r="F576" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G576" t="s">
         <v>14</v>
       </c>
       <c r="H576">
-        <v>45376</v>
+        <v>45029</v>
       </c>
       <c r="I576" t="s">
         <v>12</v>
@@ -17748,25 +17751,25 @@
     </row>
     <row r="577" spans="1:9">
       <c r="A577" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C577" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D577" t="s">
         <v>1172</v>
       </c>
-      <c r="B577" t="s">
+      <c r="E577" t="s">
         <v>1173</v>
       </c>
-      <c r="C577" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D577" t="s">
-        <v>1175</v>
-      </c>
       <c r="F577" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G577" t="s">
         <v>14</v>
       </c>
       <c r="H577">
-        <v>45085</v>
+        <v>45376</v>
       </c>
       <c r="I577" t="s">
         <v>12</v>
@@ -17774,10 +17777,10 @@
     </row>
     <row r="578" spans="1:9">
       <c r="A578" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B578" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C578" t="s">
         <v>1176</v>
@@ -17792,7 +17795,7 @@
         <v>14</v>
       </c>
       <c r="H578">
-        <v>45387</v>
+        <v>45085</v>
       </c>
       <c r="I578" t="s">
         <v>12</v>
@@ -17800,10 +17803,10 @@
     </row>
     <row r="579" spans="1:9">
       <c r="A579" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B579" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C579" t="s">
         <v>1178</v>
@@ -17812,13 +17815,13 @@
         <v>1179</v>
       </c>
       <c r="F579" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G579" t="s">
         <v>14</v>
       </c>
       <c r="H579">
-        <v>45764</v>
+        <v>45387</v>
       </c>
       <c r="I579" t="s">
         <v>12</v>
@@ -17826,24 +17829,50 @@
     </row>
     <row r="580" spans="1:9">
       <c r="A580" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C580" t="s">
         <v>1180</v>
       </c>
-      <c r="C580" t="s">
+      <c r="D580" t="s">
         <v>1181</v>
       </c>
-      <c r="D580" t="s">
+      <c r="F580" t="s">
+        <v>60</v>
+      </c>
+      <c r="G580" t="s">
+        <v>14</v>
+      </c>
+      <c r="H580">
+        <v>45764</v>
+      </c>
+      <c r="I580" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="581" spans="1:9">
+      <c r="A581" t="s">
         <v>1182</v>
       </c>
-      <c r="F580" t="s">
+      <c r="C581" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D581" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F581" t="s">
         <v>18</v>
       </c>
-      <c r="G580" t="s">
-        <v>14</v>
-      </c>
-      <c r="H580">
+      <c r="G581" t="s">
+        <v>14</v>
+      </c>
+      <c r="H581">
         <v>45477</v>
       </c>
-      <c r="I580" t="s">
+      <c r="I581" t="s">
         <v>12</v>
       </c>
     </row>
